--- a/argus/kship/models/382900_model.xlsx
+++ b/argus/kship/models/382900_model.xlsx
@@ -21,7 +21,7 @@
     <definedName name="변수H">변수!$C$1:$AL$1</definedName>
     <definedName name="환율">변수!$C$6:$AL$13</definedName>
     <definedName name="BS연결H">BS연결!$C$1:$AL$1</definedName>
-    <definedName name="BS연결">BS연결!$C$5:$AL$86</definedName>
+    <definedName name="BS연결">BS연결!$C$5:$AL$87</definedName>
     <definedName name="BS별도H">BS별도!$C$1:$AL$1</definedName>
     <definedName name="BS별도">BS별도!$C$5:$AL$86</definedName>
     <definedName name="SUBQH">subQ!$A$1:$AL$1</definedName>
@@ -888,61 +888,61 @@
     <comment ref="Z25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 297억 × 5.69% − 총차입금 0억 × 2.94% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 297억 × 5.69% − 총차입금 0억 × 2.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AA25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 302억 × 5.69% − 총차입금 0억 × 2.94% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 302억 × 5.69% − 총차입금 0억 × 2.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AC25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 308억 × 5.69% − 총차입금 0억 × 2.94% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 308억 × 5.69% − 총차입금 0억 × 2.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AD25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 312억 × 5.69% − 총차입금 0억 × 2.94% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 312억 × 5.69% − 총차입금 0억 × 2.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AE25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 318억 × 5.69% − 총차입금 0억 × 2.94% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 318억 × 5.69% − 총차입금 0억 × 2.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AF25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 323억 × 5.69% − 총차입금 0억 × 2.94% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 323억 × 5.69% − 총차입금 0억 × 2.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AH25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 329억 × 5.69% − 총차입금 0억 × 2.94% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 329억 × 5.69% − 총차입금 0억 × 2.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AI25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 334억 × 5.69% − 총차입금 0억 × 2.94% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 334억 × 5.69% − 총차입금 0억 × 2.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AJ25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 340억 × 5.69% − 총차입금 0억 × 2.94% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 340억 × 5.69% − 총차입금 0억 × 2.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AK25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 346억 × 5.69% − 총차입금 0억 × 2.94% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 346억 × 5.69% − 총차입금 0억 × 2.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="Z26" authorId="0" shapeId="0">
@@ -2200,61 +2200,61 @@
     </comment>
     <comment ref="Z11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 297억 × 5.69% − 총차입금 0억 × 2.94% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 297억 × 5.69% − 총차입금 0억 × 2.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AA11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 302억 × 5.69% − 총차입금 0억 × 2.94% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 302억 × 5.69% − 총차입금 0억 × 2.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AC11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 308억 × 5.69% − 총차입금 0억 × 2.94% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 308억 × 5.69% − 총차입금 0억 × 2.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AD11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 312억 × 5.69% − 총차입금 0억 × 2.94% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 312억 × 5.69% − 총차입금 0억 × 2.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AE11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 318억 × 5.69% − 총차입금 0억 × 2.94% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 318억 × 5.69% − 총차입금 0억 × 2.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AF11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 323억 × 5.69% − 총차입금 0억 × 2.94% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 323억 × 5.69% − 총차입금 0억 × 2.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 329억 × 5.69% − 총차입금 0억 × 2.94% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 329억 × 5.69% − 총차입금 0억 × 2.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 334억 × 5.69% − 총차입금 0억 × 2.94% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 334억 × 5.69% − 총차입금 0억 × 2.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AJ11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 340억 × 5.69% − 총차입금 0억 × 2.94% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 340억 × 5.69% − 총차입금 0억 × 2.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 346억 × 5.69% − 총차입금 0억 × 2.94% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 346억 × 5.69% − 총차입금 0억 × 2.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
@@ -4310,7 +4310,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-09-30</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -4438,7 +4438,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 51.1, "op_wape_pct": 104.4, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "trend_seasonal", "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식", "detail": [{"q": "2025Q3", "rev_pred": 152.12, "rev_act": 103.99, "op_pred": 2.16, "op_act": 8.42}, {"q": "2025Q4", "rev_pred": 128.35, "rev_act": 154.55, "op_pred": 1.82, "op_act": -8.21}, {"q": "2026Q1", "rev_pred": 144.47, "rev_act": 50.54, "op_pred": 2.05, "op_act": -21.45}, {"q": "2026Q2", "rev_pred": 97.65, "rev_act": 178.25, "op_pred": 1.39, "op_act": -32.33}]}</t>
+          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 51.1, "op_wape_pct": 104.4, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "trend_seasonal", "selection_oos_at_freeze": null, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 152.12, "rev_act": 103.99, "op_pred": 2.16, "op_act": 8.42}, {"q": "2025Q4", "rev_pred": 128.35, "rev_act": 154.55, "op_pred": 1.82, "op_act": -8.21}, {"q": "2026Q1", "rev_pred": 144.47, "rev_act": 50.54, "op_pred": 2.05, "op_act": -21.45}, {"q": "2026Q2", "rev_pred": 97.65, "rev_act": 178.25, "op_pred": 1.39, "op_act": -32.33}]}</t>
         </is>
       </c>
     </row>
@@ -9593,7 +9593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL86"/>
+  <dimension ref="A1:AL87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -9825,7 +9825,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -12809,10 +12809,10 @@
         <v>114809.57</v>
       </c>
       <c r="V46" s="18" t="n">
-        <v>123410.7</v>
+        <v>134731.4</v>
       </c>
       <c r="W46" s="34" t="n">
-        <v>123410.7</v>
+        <v>134731.4</v>
       </c>
       <c r="X46" s="18" t="n">
         <v>127363.51</v>
@@ -12873,10 +12873,10 @@
         <v>104171.99</v>
       </c>
       <c r="V47" s="18" t="n">
-        <v>74905.37</v>
+        <v>86226.07000000001</v>
       </c>
       <c r="W47" s="34" t="n">
-        <v>74905.37</v>
+        <v>86226.07000000001</v>
       </c>
       <c r="X47" s="18" t="n">
         <v>98597.61</v>
@@ -13106,50 +13106,19 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>매출액(수익)</t>
+          <t>사채</t>
         </is>
       </c>
       <c r="H52" s="9" t="n"/>
-      <c r="L52" s="18" t="n">
-        <v>7450.42</v>
-      </c>
       <c r="M52" s="9" t="n"/>
-      <c r="N52" s="18" t="n">
-        <v>6719.84</v>
-      </c>
-      <c r="O52" s="18" t="n">
-        <v>9194.01</v>
-      </c>
-      <c r="P52" s="18" t="n">
-        <v>11000.03</v>
-      </c>
-      <c r="Q52" s="18" t="n">
-        <v>9280.799999999999</v>
-      </c>
-      <c r="R52" s="34" t="n">
-        <v>36194.68</v>
-      </c>
-      <c r="S52" s="18" t="n">
-        <v>10446.45</v>
-      </c>
-      <c r="T52" s="18" t="n">
-        <v>7061.17</v>
-      </c>
-      <c r="U52" s="18" t="n">
-        <v>10398.92</v>
-      </c>
+      <c r="R52" s="9" t="n"/>
       <c r="V52" s="18" t="n">
-        <v>15454.55</v>
+        <v>11320.7</v>
       </c>
       <c r="W52" s="34" t="n">
-        <v>43361.09</v>
-      </c>
-      <c r="X52" s="18" t="n">
-        <v>5053.88</v>
-      </c>
-      <c r="Y52" s="19" t="n">
-        <v>17824.99</v>
-      </c>
+        <v>11320.7</v>
+      </c>
+      <c r="Y52" s="5" t="n"/>
       <c r="Z52" s="10" t="n"/>
       <c r="AA52" s="10" t="n"/>
       <c r="AB52" s="11" t="n"/>
@@ -13170,49 +13139,49 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>매출원가</t>
+          <t>매출액(수익)</t>
         </is>
       </c>
       <c r="H53" s="9" t="n"/>
       <c r="L53" s="18" t="n">
-        <v>8731.35</v>
+        <v>7450.42</v>
       </c>
       <c r="M53" s="9" t="n"/>
       <c r="N53" s="18" t="n">
-        <v>6447.46</v>
+        <v>6719.84</v>
       </c>
       <c r="O53" s="18" t="n">
-        <v>6693.01</v>
+        <v>9194.01</v>
       </c>
       <c r="P53" s="18" t="n">
-        <v>8828.98</v>
+        <v>11000.03</v>
       </c>
       <c r="Q53" s="18" t="n">
-        <v>7973.61</v>
+        <v>9280.799999999999</v>
       </c>
       <c r="R53" s="34" t="n">
-        <v>29943.06</v>
+        <v>36194.68</v>
       </c>
       <c r="S53" s="18" t="n">
-        <v>8736.040000000001</v>
+        <v>10446.45</v>
       </c>
       <c r="T53" s="18" t="n">
-        <v>5738.35</v>
+        <v>7061.17</v>
       </c>
       <c r="U53" s="18" t="n">
-        <v>8500.41</v>
+        <v>10398.92</v>
       </c>
       <c r="V53" s="18" t="n">
-        <v>14952.79</v>
+        <v>15454.55</v>
       </c>
       <c r="W53" s="34" t="n">
-        <v>37927.59</v>
+        <v>43361.09</v>
       </c>
       <c r="X53" s="18" t="n">
-        <v>6362.33</v>
+        <v>5053.88</v>
       </c>
       <c r="Y53" s="19" t="n">
-        <v>19527.47</v>
+        <v>17824.99</v>
       </c>
       <c r="Z53" s="10" t="n"/>
       <c r="AA53" s="10" t="n"/>
@@ -13234,49 +13203,49 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>매출총이익</t>
+          <t>매출원가</t>
         </is>
       </c>
       <c r="H54" s="9" t="n"/>
       <c r="L54" s="18" t="n">
-        <v>-1280.93</v>
+        <v>8731.35</v>
       </c>
       <c r="M54" s="9" t="n"/>
       <c r="N54" s="18" t="n">
-        <v>272.38</v>
+        <v>6447.46</v>
       </c>
       <c r="O54" s="18" t="n">
-        <v>2500.99</v>
+        <v>6693.01</v>
       </c>
       <c r="P54" s="18" t="n">
-        <v>2171.05</v>
+        <v>8828.98</v>
       </c>
       <c r="Q54" s="18" t="n">
-        <v>1307.2</v>
+        <v>7973.61</v>
       </c>
       <c r="R54" s="34" t="n">
-        <v>6251.62</v>
+        <v>29943.06</v>
       </c>
       <c r="S54" s="18" t="n">
-        <v>1710.41</v>
+        <v>8736.040000000001</v>
       </c>
       <c r="T54" s="18" t="n">
-        <v>1322.81</v>
+        <v>5738.35</v>
       </c>
       <c r="U54" s="18" t="n">
-        <v>1898.51</v>
+        <v>8500.41</v>
       </c>
       <c r="V54" s="18" t="n">
-        <v>501.76</v>
+        <v>14952.79</v>
       </c>
       <c r="W54" s="34" t="n">
-        <v>5433.49</v>
+        <v>37927.59</v>
       </c>
       <c r="X54" s="18" t="n">
-        <v>-1308.45</v>
+        <v>6362.33</v>
       </c>
       <c r="Y54" s="19" t="n">
-        <v>-1702.47</v>
+        <v>19527.47</v>
       </c>
       <c r="Z54" s="10" t="n"/>
       <c r="AA54" s="10" t="n"/>
@@ -13298,49 +13267,49 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>판관비</t>
+          <t>매출총이익</t>
         </is>
       </c>
       <c r="H55" s="9" t="n"/>
       <c r="L55" s="18" t="n">
-        <v>765.54</v>
+        <v>-1280.93</v>
       </c>
       <c r="M55" s="9" t="n"/>
       <c r="N55" s="18" t="n">
-        <v>907.8099999999999</v>
+        <v>272.38</v>
       </c>
       <c r="O55" s="18" t="n">
-        <v>850.8099999999999</v>
+        <v>2500.99</v>
       </c>
       <c r="P55" s="18" t="n">
-        <v>832.6900000000001</v>
+        <v>2171.05</v>
       </c>
       <c r="Q55" s="18" t="n">
-        <v>1249.17</v>
+        <v>1307.2</v>
       </c>
       <c r="R55" s="34" t="n">
-        <v>3840.48</v>
+        <v>6251.62</v>
       </c>
       <c r="S55" s="18" t="n">
-        <v>1030.14</v>
+        <v>1710.41</v>
       </c>
       <c r="T55" s="18" t="n">
-        <v>1166.39</v>
+        <v>1322.81</v>
       </c>
       <c r="U55" s="18" t="n">
-        <v>1056.59</v>
+        <v>1898.51</v>
       </c>
       <c r="V55" s="18" t="n">
-        <v>1322.54</v>
+        <v>501.76</v>
       </c>
       <c r="W55" s="34" t="n">
-        <v>4575.66</v>
+        <v>5433.49</v>
       </c>
       <c r="X55" s="18" t="n">
-        <v>836.67</v>
+        <v>-1308.45</v>
       </c>
       <c r="Y55" s="19" t="n">
-        <v>1530.79</v>
+        <v>-1702.47</v>
       </c>
       <c r="Z55" s="10" t="n"/>
       <c r="AA55" s="10" t="n"/>
@@ -13362,49 +13331,49 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>영업이익</t>
+          <t>판관비</t>
         </is>
       </c>
       <c r="H56" s="9" t="n"/>
       <c r="L56" s="18" t="n">
-        <v>-2046.47</v>
+        <v>765.54</v>
       </c>
       <c r="M56" s="9" t="n"/>
       <c r="N56" s="18" t="n">
-        <v>-635.4299999999999</v>
+        <v>907.8099999999999</v>
       </c>
       <c r="O56" s="18" t="n">
-        <v>1650.18</v>
+        <v>850.8099999999999</v>
       </c>
       <c r="P56" s="18" t="n">
-        <v>1338.36</v>
+        <v>832.6900000000001</v>
       </c>
       <c r="Q56" s="18" t="n">
-        <v>58.03</v>
+        <v>1249.17</v>
       </c>
       <c r="R56" s="34" t="n">
-        <v>2411.14</v>
+        <v>3840.48</v>
       </c>
       <c r="S56" s="18" t="n">
-        <v>680.28</v>
+        <v>1030.14</v>
       </c>
       <c r="T56" s="18" t="n">
-        <v>156.43</v>
+        <v>1166.39</v>
       </c>
       <c r="U56" s="18" t="n">
-        <v>841.9299999999999</v>
+        <v>1056.59</v>
       </c>
       <c r="V56" s="18" t="n">
-        <v>-820.78</v>
+        <v>1322.54</v>
       </c>
       <c r="W56" s="34" t="n">
-        <v>857.86</v>
+        <v>4575.66</v>
       </c>
       <c r="X56" s="18" t="n">
-        <v>-2145.12</v>
+        <v>836.67</v>
       </c>
       <c r="Y56" s="19" t="n">
-        <v>-3233.27</v>
+        <v>1530.79</v>
       </c>
       <c r="Z56" s="10" t="n"/>
       <c r="AA56" s="10" t="n"/>
@@ -13426,49 +13395,49 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>금융수익</t>
+          <t>영업이익</t>
         </is>
       </c>
       <c r="H57" s="9" t="n"/>
       <c r="L57" s="18" t="n">
-        <v>513.77</v>
+        <v>-2046.47</v>
       </c>
       <c r="M57" s="9" t="n"/>
       <c r="N57" s="18" t="n">
-        <v>387.04</v>
+        <v>-635.4299999999999</v>
       </c>
       <c r="O57" s="18" t="n">
-        <v>333.56</v>
+        <v>1650.18</v>
       </c>
       <c r="P57" s="18" t="n">
-        <v>353.3</v>
+        <v>1338.36</v>
       </c>
       <c r="Q57" s="18" t="n">
-        <v>762.24</v>
+        <v>58.03</v>
       </c>
       <c r="R57" s="34" t="n">
-        <v>1836.14</v>
+        <v>2411.14</v>
       </c>
       <c r="S57" s="18" t="n">
-        <v>540.38</v>
+        <v>680.28</v>
       </c>
       <c r="T57" s="18" t="n">
-        <v>566.9</v>
+        <v>156.43</v>
       </c>
       <c r="U57" s="18" t="n">
-        <v>517.03</v>
+        <v>841.9299999999999</v>
       </c>
       <c r="V57" s="18" t="n">
-        <v>6312.34</v>
+        <v>-820.78</v>
       </c>
       <c r="W57" s="34" t="n">
-        <v>7936.65</v>
+        <v>857.86</v>
       </c>
       <c r="X57" s="18" t="n">
-        <v>562.11</v>
+        <v>-2145.12</v>
       </c>
       <c r="Y57" s="19" t="n">
-        <v>1106.75</v>
+        <v>-3233.27</v>
       </c>
       <c r="Z57" s="10" t="n"/>
       <c r="AA57" s="10" t="n"/>
@@ -13490,49 +13459,49 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>금융비용</t>
+          <t>금융수익</t>
         </is>
       </c>
       <c r="H58" s="9" t="n"/>
       <c r="L58" s="18" t="n">
-        <v>100.24</v>
+        <v>513.77</v>
       </c>
       <c r="M58" s="9" t="n"/>
       <c r="N58" s="18" t="n">
-        <v>405.09</v>
+        <v>387.04</v>
       </c>
       <c r="O58" s="18" t="n">
-        <v>968.38</v>
+        <v>333.56</v>
       </c>
       <c r="P58" s="18" t="n">
-        <v>983.92</v>
+        <v>353.3</v>
       </c>
       <c r="Q58" s="18" t="n">
-        <v>1709.99</v>
+        <v>762.24</v>
       </c>
       <c r="R58" s="34" t="n">
-        <v>4067.38</v>
+        <v>1836.14</v>
       </c>
       <c r="S58" s="18" t="n">
-        <v>1238.07</v>
+        <v>540.38</v>
       </c>
       <c r="T58" s="18" t="n">
-        <v>1156.32</v>
+        <v>566.9</v>
       </c>
       <c r="U58" s="18" t="n">
-        <v>1101.3</v>
+        <v>517.03</v>
       </c>
       <c r="V58" s="18" t="n">
-        <v>4036.32</v>
+        <v>6312.34</v>
       </c>
       <c r="W58" s="34" t="n">
-        <v>7532.01</v>
+        <v>7936.65</v>
       </c>
       <c r="X58" s="18" t="n">
-        <v>1608.56</v>
+        <v>562.11</v>
       </c>
       <c r="Y58" s="19" t="n">
-        <v>1885.98</v>
+        <v>1106.75</v>
       </c>
       <c r="Z58" s="10" t="n"/>
       <c r="AA58" s="10" t="n"/>
@@ -13554,49 +13523,49 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>기타영업외수익</t>
+          <t>금융비용</t>
         </is>
       </c>
       <c r="H59" s="9" t="n"/>
       <c r="L59" s="18" t="n">
-        <v>29.37</v>
+        <v>100.24</v>
       </c>
       <c r="M59" s="9" t="n"/>
       <c r="N59" s="18" t="n">
-        <v>33.33</v>
+        <v>405.09</v>
       </c>
       <c r="O59" s="18" t="n">
-        <v>73.16</v>
+        <v>968.38</v>
       </c>
       <c r="P59" s="18" t="n">
-        <v>15.09</v>
+        <v>983.92</v>
       </c>
       <c r="Q59" s="18" t="n">
-        <v>87.13</v>
+        <v>1709.99</v>
       </c>
       <c r="R59" s="34" t="n">
-        <v>208.71</v>
+        <v>4067.38</v>
       </c>
       <c r="S59" s="18" t="n">
-        <v>6.5</v>
+        <v>1238.07</v>
       </c>
       <c r="T59" s="18" t="n">
-        <v>64.59</v>
+        <v>1156.32</v>
       </c>
       <c r="U59" s="18" t="n">
-        <v>17.48</v>
+        <v>1101.3</v>
       </c>
       <c r="V59" s="18" t="n">
-        <v>22.46</v>
+        <v>4036.32</v>
       </c>
       <c r="W59" s="34" t="n">
-        <v>111.03</v>
+        <v>7532.01</v>
       </c>
       <c r="X59" s="18" t="n">
-        <v>1611.05</v>
+        <v>1608.56</v>
       </c>
       <c r="Y59" s="19" t="n">
-        <v>-1144.06</v>
+        <v>1885.98</v>
       </c>
       <c r="Z59" s="10" t="n"/>
       <c r="AA59" s="10" t="n"/>
@@ -13618,49 +13587,49 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>기타영업외비용</t>
+          <t>기타영업외수익</t>
         </is>
       </c>
       <c r="H60" s="9" t="n"/>
       <c r="L60" s="18" t="n">
-        <v>84.97</v>
+        <v>29.37</v>
       </c>
       <c r="M60" s="9" t="n"/>
       <c r="N60" s="18" t="n">
-        <v>16.99</v>
+        <v>33.33</v>
       </c>
       <c r="O60" s="18" t="n">
-        <v>59.28</v>
+        <v>73.16</v>
       </c>
       <c r="P60" s="18" t="n">
-        <v>18</v>
+        <v>15.09</v>
       </c>
       <c r="Q60" s="18" t="n">
-        <v>15.11</v>
+        <v>87.13</v>
       </c>
       <c r="R60" s="34" t="n">
-        <v>109.38</v>
+        <v>208.71</v>
       </c>
       <c r="S60" s="18" t="n">
-        <v>61.82</v>
+        <v>6.5</v>
       </c>
       <c r="T60" s="18" t="n">
-        <v>24.04</v>
+        <v>64.59</v>
       </c>
       <c r="U60" s="18" t="n">
-        <v>45.79</v>
+        <v>17.48</v>
       </c>
       <c r="V60" s="18" t="n">
-        <v>94.84999999999999</v>
+        <v>22.46</v>
       </c>
       <c r="W60" s="34" t="n">
-        <v>226.5</v>
+        <v>111.03</v>
       </c>
       <c r="X60" s="18" t="n">
-        <v>88.63</v>
+        <v>1611.05</v>
       </c>
       <c r="Y60" s="19" t="n">
-        <v>30.2</v>
+        <v>-1144.06</v>
       </c>
       <c r="Z60" s="10" t="n"/>
       <c r="AA60" s="10" t="n"/>
@@ -13682,49 +13651,49 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>법인세비용차감전계속사업이익</t>
+          <t>기타영업외비용</t>
         </is>
       </c>
       <c r="H61" s="9" t="n"/>
       <c r="L61" s="18" t="n">
-        <v>-1688.54</v>
+        <v>84.97</v>
       </c>
       <c r="M61" s="9" t="n"/>
       <c r="N61" s="18" t="n">
-        <v>-637.14</v>
+        <v>16.99</v>
       </c>
       <c r="O61" s="18" t="n">
-        <v>1029.24</v>
+        <v>59.28</v>
       </c>
       <c r="P61" s="18" t="n">
-        <v>704.83</v>
+        <v>18</v>
       </c>
       <c r="Q61" s="18" t="n">
-        <v>-817.7</v>
+        <v>15.11</v>
       </c>
       <c r="R61" s="34" t="n">
-        <v>279.23</v>
+        <v>109.38</v>
       </c>
       <c r="S61" s="18" t="n">
-        <v>-72.73</v>
+        <v>61.82</v>
       </c>
       <c r="T61" s="18" t="n">
-        <v>-392.45</v>
+        <v>24.04</v>
       </c>
       <c r="U61" s="18" t="n">
-        <v>229.36</v>
+        <v>45.79</v>
       </c>
       <c r="V61" s="18" t="n">
-        <v>1382.85</v>
+        <v>94.84999999999999</v>
       </c>
       <c r="W61" s="34" t="n">
-        <v>1147.03</v>
+        <v>226.5</v>
       </c>
       <c r="X61" s="18" t="n">
-        <v>-1669.15</v>
+        <v>88.63</v>
       </c>
       <c r="Y61" s="19" t="n">
-        <v>-5186.75</v>
+        <v>30.2</v>
       </c>
       <c r="Z61" s="10" t="n"/>
       <c r="AA61" s="10" t="n"/>
@@ -13746,49 +13715,49 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>법인세비용</t>
+          <t>법인세비용차감전계속사업이익</t>
         </is>
       </c>
       <c r="H62" s="9" t="n"/>
       <c r="L62" s="18" t="n">
-        <v>-542.73</v>
+        <v>-1688.54</v>
       </c>
       <c r="M62" s="9" t="n"/>
       <c r="N62" s="18" t="n">
-        <v>0</v>
+        <v>-637.14</v>
       </c>
       <c r="O62" s="18" t="n">
-        <v>133.04</v>
+        <v>1029.24</v>
       </c>
       <c r="P62" s="18" t="n">
-        <v>0</v>
+        <v>704.83</v>
       </c>
       <c r="Q62" s="18" t="n">
-        <v>-478.9</v>
+        <v>-817.7</v>
       </c>
       <c r="R62" s="34" t="n">
-        <v>-345.86</v>
+        <v>279.23</v>
       </c>
       <c r="S62" s="18" t="n">
-        <v>0</v>
+        <v>-72.73</v>
       </c>
       <c r="T62" s="18" t="n">
-        <v>74.37</v>
+        <v>-392.45</v>
       </c>
       <c r="U62" s="18" t="n">
-        <v>0</v>
+        <v>229.36</v>
       </c>
       <c r="V62" s="18" t="n">
-        <v>-109.42</v>
+        <v>1382.85</v>
       </c>
       <c r="W62" s="34" t="n">
-        <v>-35.05</v>
+        <v>1147.03</v>
       </c>
       <c r="X62" s="18" t="n">
-        <v>0</v>
+        <v>-1669.15</v>
       </c>
       <c r="Y62" s="19" t="n">
-        <v>-1198.64</v>
+        <v>-5186.75</v>
       </c>
       <c r="Z62" s="10" t="n"/>
       <c r="AA62" s="10" t="n"/>
@@ -13810,49 +13779,49 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>당기순이익</t>
+          <t>법인세비용</t>
         </is>
       </c>
       <c r="H63" s="9" t="n"/>
       <c r="L63" s="18" t="n">
-        <v>-1145.81</v>
+        <v>-542.73</v>
       </c>
       <c r="M63" s="9" t="n"/>
       <c r="N63" s="18" t="n">
-        <v>-637.14</v>
+        <v>0</v>
       </c>
       <c r="O63" s="18" t="n">
-        <v>896.2</v>
+        <v>133.04</v>
       </c>
       <c r="P63" s="18" t="n">
-        <v>704.83</v>
+        <v>0</v>
       </c>
       <c r="Q63" s="18" t="n">
-        <v>-338.8</v>
+        <v>-478.9</v>
       </c>
       <c r="R63" s="34" t="n">
-        <v>625.09</v>
+        <v>-345.86</v>
       </c>
       <c r="S63" s="18" t="n">
-        <v>-72.73</v>
+        <v>0</v>
       </c>
       <c r="T63" s="18" t="n">
-        <v>-466.82</v>
+        <v>74.37</v>
       </c>
       <c r="U63" s="18" t="n">
-        <v>229.36</v>
+        <v>0</v>
       </c>
       <c r="V63" s="18" t="n">
-        <v>1492.27</v>
+        <v>-109.42</v>
       </c>
       <c r="W63" s="34" t="n">
-        <v>1182.08</v>
+        <v>-35.05</v>
       </c>
       <c r="X63" s="18" t="n">
-        <v>-1669.15</v>
+        <v>0</v>
       </c>
       <c r="Y63" s="19" t="n">
-        <v>-3988.11</v>
+        <v>-1198.64</v>
       </c>
       <c r="Z63" s="10" t="n"/>
       <c r="AA63" s="10" t="n"/>
@@ -13874,12 +13843,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>총포괄손익</t>
+          <t>당기순이익</t>
         </is>
       </c>
       <c r="H64" s="9" t="n"/>
       <c r="L64" s="18" t="n">
-        <v>-1188.63</v>
+        <v>-1145.81</v>
       </c>
       <c r="M64" s="9" t="n"/>
       <c r="N64" s="18" t="n">
@@ -13892,10 +13861,10 @@
         <v>704.83</v>
       </c>
       <c r="Q64" s="18" t="n">
-        <v>58967.13</v>
+        <v>-338.8</v>
       </c>
       <c r="R64" s="34" t="n">
-        <v>59931.02</v>
+        <v>625.09</v>
       </c>
       <c r="S64" s="18" t="n">
         <v>-72.73</v>
@@ -13907,10 +13876,10 @@
         <v>229.36</v>
       </c>
       <c r="V64" s="18" t="n">
-        <v>-2864.07</v>
+        <v>1492.27</v>
       </c>
       <c r="W64" s="34" t="n">
-        <v>-3174.26</v>
+        <v>1182.08</v>
       </c>
       <c r="X64" s="18" t="n">
         <v>-1669.15</v>
@@ -13938,49 +13907,49 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>(지배주주지분)당기순이익</t>
+          <t>총포괄손익</t>
         </is>
       </c>
       <c r="H65" s="9" t="n"/>
       <c r="L65" s="18" t="n">
-        <v>-1090.6</v>
+        <v>-1188.63</v>
       </c>
       <c r="M65" s="9" t="n"/>
       <c r="N65" s="18" t="n">
-        <v>-596.77</v>
+        <v>-637.14</v>
       </c>
       <c r="O65" s="18" t="n">
-        <v>911.4299999999999</v>
+        <v>896.2</v>
       </c>
       <c r="P65" s="18" t="n">
-        <v>775.21</v>
+        <v>704.83</v>
       </c>
       <c r="Q65" s="18" t="n">
-        <v>-255.33</v>
+        <v>58967.13</v>
       </c>
       <c r="R65" s="34" t="n">
-        <v>834.54</v>
+        <v>59931.02</v>
       </c>
       <c r="S65" s="18" t="n">
-        <v>4.84</v>
+        <v>-72.73</v>
       </c>
       <c r="T65" s="18" t="n">
-        <v>-377.74</v>
+        <v>-466.82</v>
       </c>
       <c r="U65" s="18" t="n">
-        <v>336.55</v>
+        <v>229.36</v>
       </c>
       <c r="V65" s="18" t="n">
-        <v>1626.51</v>
+        <v>-2864.07</v>
       </c>
       <c r="W65" s="34" t="n">
-        <v>1590.16</v>
+        <v>-3174.26</v>
       </c>
       <c r="X65" s="18" t="n">
-        <v>-1645.99</v>
+        <v>-1669.15</v>
       </c>
       <c r="Y65" s="19" t="n">
-        <v>-3786.59</v>
+        <v>-3988.11</v>
       </c>
       <c r="Z65" s="10" t="n"/>
       <c r="AA65" s="10" t="n"/>
@@ -14002,49 +13971,49 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>(비지배주주지분)당기순이익</t>
+          <t>(지배주주지분)당기순이익</t>
         </is>
       </c>
       <c r="H66" s="9" t="n"/>
       <c r="L66" s="18" t="n">
-        <v>-55.21</v>
+        <v>-1090.6</v>
       </c>
       <c r="M66" s="9" t="n"/>
       <c r="N66" s="18" t="n">
-        <v>-40.38</v>
+        <v>-596.77</v>
       </c>
       <c r="O66" s="18" t="n">
-        <v>-15.23</v>
+        <v>911.4299999999999</v>
       </c>
       <c r="P66" s="18" t="n">
-        <v>-70.38</v>
+        <v>775.21</v>
       </c>
       <c r="Q66" s="18" t="n">
-        <v>-83.47</v>
+        <v>-255.33</v>
       </c>
       <c r="R66" s="34" t="n">
-        <v>-209.46</v>
+        <v>834.54</v>
       </c>
       <c r="S66" s="18" t="n">
-        <v>-77.56999999999999</v>
+        <v>4.84</v>
       </c>
       <c r="T66" s="18" t="n">
-        <v>-89.08</v>
+        <v>-377.74</v>
       </c>
       <c r="U66" s="18" t="n">
-        <v>-107.19</v>
+        <v>336.55</v>
       </c>
       <c r="V66" s="18" t="n">
-        <v>-134.24</v>
+        <v>1626.51</v>
       </c>
       <c r="W66" s="34" t="n">
-        <v>-408.08</v>
+        <v>1590.16</v>
       </c>
       <c r="X66" s="18" t="n">
-        <v>-23.16</v>
+        <v>-1645.99</v>
       </c>
       <c r="Y66" s="19" t="n">
-        <v>-201.52</v>
+        <v>-3786.59</v>
       </c>
       <c r="Z66" s="10" t="n"/>
       <c r="AA66" s="10" t="n"/>
@@ -14066,49 +14035,49 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>금융손익</t>
+          <t>(비지배주주지분)당기순이익</t>
         </is>
       </c>
       <c r="H67" s="9" t="n"/>
       <c r="L67" s="18" t="n">
-        <v>413.53</v>
+        <v>-55.21</v>
       </c>
       <c r="M67" s="9" t="n"/>
       <c r="N67" s="18" t="n">
-        <v>-18.05</v>
+        <v>-40.38</v>
       </c>
       <c r="O67" s="18" t="n">
-        <v>-634.8200000000001</v>
+        <v>-15.23</v>
       </c>
       <c r="P67" s="18" t="n">
-        <v>-630.62</v>
+        <v>-70.38</v>
       </c>
       <c r="Q67" s="18" t="n">
-        <v>-947.75</v>
+        <v>-83.47</v>
       </c>
       <c r="R67" s="34" t="n">
-        <v>-2231.24</v>
+        <v>-209.46</v>
       </c>
       <c r="S67" s="18" t="n">
-        <v>-697.6900000000001</v>
+        <v>-77.56999999999999</v>
       </c>
       <c r="T67" s="18" t="n">
-        <v>-589.42</v>
+        <v>-89.08</v>
       </c>
       <c r="U67" s="18" t="n">
-        <v>-584.27</v>
+        <v>-107.19</v>
       </c>
       <c r="V67" s="18" t="n">
-        <v>2276.02</v>
+        <v>-134.24</v>
       </c>
       <c r="W67" s="34" t="n">
-        <v>404.64</v>
+        <v>-408.08</v>
       </c>
       <c r="X67" s="18" t="n">
-        <v>-1046.45</v>
+        <v>-23.16</v>
       </c>
       <c r="Y67" s="19" t="n">
-        <v>-779.23</v>
+        <v>-201.52</v>
       </c>
       <c r="Z67" s="10" t="n"/>
       <c r="AA67" s="10" t="n"/>
@@ -14130,49 +14099,49 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>기타영업외손익</t>
+          <t>금융손익</t>
         </is>
       </c>
       <c r="H68" s="9" t="n"/>
       <c r="L68" s="18" t="n">
-        <v>-55.6</v>
+        <v>413.53</v>
       </c>
       <c r="M68" s="9" t="n"/>
       <c r="N68" s="18" t="n">
-        <v>16.34</v>
+        <v>-18.05</v>
       </c>
       <c r="O68" s="18" t="n">
-        <v>13.88</v>
+        <v>-634.8200000000001</v>
       </c>
       <c r="P68" s="18" t="n">
-        <v>-2.91</v>
+        <v>-630.62</v>
       </c>
       <c r="Q68" s="18" t="n">
-        <v>72.02</v>
+        <v>-947.75</v>
       </c>
       <c r="R68" s="34" t="n">
-        <v>99.33</v>
+        <v>-2231.24</v>
       </c>
       <c r="S68" s="18" t="n">
-        <v>-55.32</v>
+        <v>-697.6900000000001</v>
       </c>
       <c r="T68" s="18" t="n">
-        <v>40.55</v>
+        <v>-589.42</v>
       </c>
       <c r="U68" s="18" t="n">
-        <v>-28.31</v>
+        <v>-584.27</v>
       </c>
       <c r="V68" s="18" t="n">
-        <v>-72.39</v>
+        <v>2276.02</v>
       </c>
       <c r="W68" s="34" t="n">
-        <v>-115.47</v>
+        <v>404.64</v>
       </c>
       <c r="X68" s="18" t="n">
-        <v>1522.42</v>
+        <v>-1046.45</v>
       </c>
       <c r="Y68" s="19" t="n">
-        <v>-1174.26</v>
+        <v>-779.23</v>
       </c>
       <c r="Z68" s="10" t="n"/>
       <c r="AA68" s="10" t="n"/>
@@ -14194,49 +14163,49 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>계속사업이익</t>
+          <t>기타영업외손익</t>
         </is>
       </c>
       <c r="H69" s="9" t="n"/>
       <c r="L69" s="18" t="n">
-        <v>-1145.81</v>
+        <v>-55.6</v>
       </c>
       <c r="M69" s="9" t="n"/>
       <c r="N69" s="18" t="n">
-        <v>-637.14</v>
+        <v>16.34</v>
       </c>
       <c r="O69" s="18" t="n">
-        <v>896.2</v>
+        <v>13.88</v>
       </c>
       <c r="P69" s="18" t="n">
-        <v>704.83</v>
+        <v>-2.91</v>
       </c>
       <c r="Q69" s="18" t="n">
-        <v>-338.8</v>
+        <v>72.02</v>
       </c>
       <c r="R69" s="34" t="n">
-        <v>625.09</v>
+        <v>99.33</v>
       </c>
       <c r="S69" s="18" t="n">
-        <v>-72.73</v>
+        <v>-55.32</v>
       </c>
       <c r="T69" s="18" t="n">
-        <v>-466.82</v>
+        <v>40.55</v>
       </c>
       <c r="U69" s="18" t="n">
-        <v>229.36</v>
+        <v>-28.31</v>
       </c>
       <c r="V69" s="18" t="n">
-        <v>1492.27</v>
+        <v>-72.39</v>
       </c>
       <c r="W69" s="34" t="n">
-        <v>1182.08</v>
+        <v>-115.47</v>
       </c>
       <c r="X69" s="18" t="n">
-        <v>-1669.15</v>
+        <v>1522.42</v>
       </c>
       <c r="Y69" s="19" t="n">
-        <v>-3988.11</v>
+        <v>-1174.26</v>
       </c>
       <c r="Z69" s="10" t="n"/>
       <c r="AA69" s="10" t="n"/>
@@ -14258,49 +14227,49 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>영업활동으로인한현금흐름</t>
+          <t>계속사업이익</t>
         </is>
       </c>
       <c r="H70" s="9" t="n"/>
       <c r="L70" s="18" t="n">
-        <v>3190.35</v>
+        <v>-1145.81</v>
       </c>
       <c r="M70" s="9" t="n"/>
       <c r="N70" s="18" t="n">
-        <v>-5439.91</v>
+        <v>-637.14</v>
       </c>
       <c r="O70" s="18" t="n">
-        <v>18754.8</v>
+        <v>896.2</v>
       </c>
       <c r="P70" s="18" t="n">
-        <v>-7021.01</v>
+        <v>704.83</v>
       </c>
       <c r="Q70" s="18" t="n">
-        <v>2612.06</v>
+        <v>-338.8</v>
       </c>
       <c r="R70" s="34" t="n">
-        <v>8905.940000000001</v>
+        <v>625.09</v>
       </c>
       <c r="S70" s="18" t="n">
-        <v>1393.17</v>
+        <v>-72.73</v>
       </c>
       <c r="T70" s="18" t="n">
-        <v>367.76</v>
+        <v>-466.82</v>
       </c>
       <c r="U70" s="18" t="n">
-        <v>-1381.07</v>
+        <v>229.36</v>
       </c>
       <c r="V70" s="18" t="n">
-        <v>21303.26</v>
+        <v>1492.27</v>
       </c>
       <c r="W70" s="34" t="n">
-        <v>21683.12</v>
+        <v>1182.08</v>
       </c>
       <c r="X70" s="18" t="n">
-        <v>-15326.48</v>
+        <v>-1669.15</v>
       </c>
       <c r="Y70" s="19" t="n">
-        <v>-4061.11</v>
+        <v>-3988.11</v>
       </c>
       <c r="Z70" s="10" t="n"/>
       <c r="AA70" s="10" t="n"/>
@@ -14322,49 +14291,49 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>감가상각비</t>
+          <t>영업활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="H71" s="9" t="n"/>
       <c r="L71" s="18" t="n">
-        <v>340.45</v>
+        <v>3190.35</v>
       </c>
       <c r="M71" s="9" t="n"/>
       <c r="N71" s="18" t="n">
-        <v>405.32</v>
+        <v>-5439.91</v>
       </c>
       <c r="O71" s="18" t="n">
-        <v>446.48</v>
+        <v>18754.8</v>
       </c>
       <c r="P71" s="18" t="n">
-        <v>444.16</v>
+        <v>-7021.01</v>
       </c>
       <c r="Q71" s="18" t="n">
-        <v>437.22</v>
+        <v>2612.06</v>
       </c>
       <c r="R71" s="34" t="n">
-        <v>1733.18</v>
+        <v>8905.940000000001</v>
       </c>
       <c r="S71" s="18" t="n">
-        <v>441.4</v>
+        <v>1393.17</v>
       </c>
       <c r="T71" s="18" t="n">
-        <v>460.01</v>
+        <v>367.76</v>
       </c>
       <c r="U71" s="18" t="n">
-        <v>481.48</v>
+        <v>-1381.07</v>
       </c>
       <c r="V71" s="18" t="n">
-        <v>515.9400000000001</v>
+        <v>21303.26</v>
       </c>
       <c r="W71" s="34" t="n">
-        <v>1898.83</v>
+        <v>21683.12</v>
       </c>
       <c r="X71" s="18" t="n">
-        <v>515.92</v>
+        <v>-15326.48</v>
       </c>
       <c r="Y71" s="19" t="n">
-        <v>537.61</v>
+        <v>-4061.11</v>
       </c>
       <c r="Z71" s="10" t="n"/>
       <c r="AA71" s="10" t="n"/>
@@ -14386,49 +14355,49 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>무형자산상각비</t>
+          <t>감가상각비</t>
         </is>
       </c>
       <c r="H72" s="9" t="n"/>
       <c r="L72" s="18" t="n">
-        <v>66.12</v>
+        <v>340.45</v>
       </c>
       <c r="M72" s="9" t="n"/>
       <c r="N72" s="18" t="n">
-        <v>66.39</v>
+        <v>405.32</v>
       </c>
       <c r="O72" s="18" t="n">
-        <v>68.03</v>
+        <v>446.48</v>
       </c>
       <c r="P72" s="18" t="n">
-        <v>111.05</v>
+        <v>444.16</v>
       </c>
       <c r="Q72" s="18" t="n">
-        <v>225.38</v>
+        <v>437.22</v>
       </c>
       <c r="R72" s="34" t="n">
-        <v>470.85</v>
+        <v>1733.18</v>
       </c>
       <c r="S72" s="18" t="n">
-        <v>189.29</v>
+        <v>441.4</v>
       </c>
       <c r="T72" s="18" t="n">
-        <v>179.99</v>
+        <v>460.01</v>
       </c>
       <c r="U72" s="18" t="n">
-        <v>170.78</v>
+        <v>481.48</v>
       </c>
       <c r="V72" s="18" t="n">
-        <v>170.03</v>
+        <v>515.9400000000001</v>
       </c>
       <c r="W72" s="34" t="n">
-        <v>710.09</v>
+        <v>1898.83</v>
       </c>
       <c r="X72" s="18" t="n">
-        <v>170.03</v>
+        <v>515.92</v>
       </c>
       <c r="Y72" s="19" t="n">
-        <v>169.37</v>
+        <v>537.61</v>
       </c>
       <c r="Z72" s="10" t="n"/>
       <c r="AA72" s="10" t="n"/>
@@ -14450,49 +14419,49 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>이자수취(CF)</t>
+          <t>무형자산상각비</t>
         </is>
       </c>
       <c r="H73" s="9" t="n"/>
       <c r="L73" s="18" t="n">
-        <v>299.44</v>
+        <v>66.12</v>
       </c>
       <c r="M73" s="9" t="n"/>
       <c r="N73" s="18" t="n">
-        <v>271</v>
+        <v>66.39</v>
       </c>
       <c r="O73" s="18" t="n">
-        <v>396</v>
+        <v>68.03</v>
       </c>
       <c r="P73" s="18" t="n">
-        <v>362.39</v>
+        <v>111.05</v>
       </c>
       <c r="Q73" s="18" t="n">
-        <v>172.35</v>
+        <v>225.38</v>
       </c>
       <c r="R73" s="34" t="n">
-        <v>1201.74</v>
+        <v>470.85</v>
       </c>
       <c r="S73" s="18" t="n">
-        <v>165.34</v>
+        <v>189.29</v>
       </c>
       <c r="T73" s="18" t="n">
-        <v>508.18</v>
+        <v>179.99</v>
       </c>
       <c r="U73" s="18" t="n">
-        <v>279.27</v>
+        <v>170.78</v>
       </c>
       <c r="V73" s="18" t="n">
-        <v>879.38</v>
+        <v>170.03</v>
       </c>
       <c r="W73" s="34" t="n">
-        <v>1832.17</v>
+        <v>710.09</v>
       </c>
       <c r="X73" s="18" t="n">
-        <v>69.93000000000001</v>
+        <v>170.03</v>
       </c>
       <c r="Y73" s="19" t="n">
-        <v>778.64</v>
+        <v>169.37</v>
       </c>
       <c r="Z73" s="10" t="n"/>
       <c r="AA73" s="10" t="n"/>
@@ -14514,49 +14483,49 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>이자지급(CF)</t>
+          <t>이자수취(CF)</t>
         </is>
       </c>
       <c r="H74" s="9" t="n"/>
       <c r="L74" s="18" t="n">
-        <v>-131.95</v>
+        <v>299.44</v>
       </c>
       <c r="M74" s="9" t="n"/>
       <c r="N74" s="18" t="n">
-        <v>-374.72</v>
+        <v>271</v>
       </c>
       <c r="O74" s="18" t="n">
-        <v>-980.23</v>
+        <v>396</v>
       </c>
       <c r="P74" s="18" t="n">
-        <v>-991.25</v>
+        <v>362.39</v>
       </c>
       <c r="Q74" s="18" t="n">
-        <v>-1004.01</v>
+        <v>172.35</v>
       </c>
       <c r="R74" s="34" t="n">
-        <v>-3350.21</v>
+        <v>1201.74</v>
       </c>
       <c r="S74" s="18" t="n">
-        <v>-1013.81</v>
+        <v>165.34</v>
       </c>
       <c r="T74" s="18" t="n">
-        <v>-945.74</v>
+        <v>508.18</v>
       </c>
       <c r="U74" s="18" t="n">
-        <v>-870.3200000000001</v>
+        <v>279.27</v>
       </c>
       <c r="V74" s="18" t="n">
-        <v>-877.87</v>
+        <v>879.38</v>
       </c>
       <c r="W74" s="34" t="n">
-        <v>-3707.74</v>
+        <v>1832.17</v>
       </c>
       <c r="X74" s="18" t="n">
-        <v>-939.9400000000001</v>
+        <v>69.93000000000001</v>
       </c>
       <c r="Y74" s="19" t="n">
-        <v>-952.52</v>
+        <v>778.64</v>
       </c>
       <c r="Z74" s="10" t="n"/>
       <c r="AA74" s="10" t="n"/>
@@ -14578,49 +14547,49 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>법인세납부(CF)</t>
+          <t>이자지급(CF)</t>
         </is>
       </c>
       <c r="H75" s="9" t="n"/>
       <c r="L75" s="18" t="n">
-        <v>-56.89</v>
+        <v>-131.95</v>
       </c>
       <c r="M75" s="9" t="n"/>
       <c r="N75" s="18" t="n">
-        <v>-41.59</v>
+        <v>-374.72</v>
       </c>
       <c r="O75" s="18" t="n">
-        <v>383.95</v>
+        <v>-980.23</v>
       </c>
       <c r="P75" s="18" t="n">
-        <v>-56.61</v>
+        <v>-991.25</v>
       </c>
       <c r="Q75" s="18" t="n">
-        <v>-21.3</v>
+        <v>-1004.01</v>
       </c>
       <c r="R75" s="34" t="n">
-        <v>264.45</v>
+        <v>-3350.21</v>
       </c>
       <c r="S75" s="18" t="n">
-        <v>-28.43</v>
+        <v>-1013.81</v>
       </c>
       <c r="T75" s="18" t="n">
-        <v>92.64</v>
+        <v>-945.74</v>
       </c>
       <c r="U75" s="18" t="n">
-        <v>-74.31</v>
+        <v>-870.3200000000001</v>
       </c>
       <c r="V75" s="18" t="n">
-        <v>-101.96</v>
+        <v>-877.87</v>
       </c>
       <c r="W75" s="34" t="n">
-        <v>-112.06</v>
+        <v>-3707.74</v>
       </c>
       <c r="X75" s="18" t="n">
-        <v>-10.45</v>
+        <v>-939.9400000000001</v>
       </c>
       <c r="Y75" s="19" t="n">
-        <v>87.59</v>
+        <v>-952.52</v>
       </c>
       <c r="Z75" s="10" t="n"/>
       <c r="AA75" s="10" t="n"/>
@@ -14642,49 +14611,49 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>투자활동으로인한현금흐름</t>
+          <t>법인세납부(CF)</t>
         </is>
       </c>
       <c r="H76" s="9" t="n"/>
       <c r="L76" s="18" t="n">
-        <v>-12024.34</v>
+        <v>-56.89</v>
       </c>
       <c r="M76" s="9" t="n"/>
       <c r="N76" s="18" t="n">
-        <v>-106453.41</v>
+        <v>-41.59</v>
       </c>
       <c r="O76" s="18" t="n">
-        <v>5413.59</v>
+        <v>383.95</v>
       </c>
       <c r="P76" s="18" t="n">
-        <v>-2679.26</v>
+        <v>-56.61</v>
       </c>
       <c r="Q76" s="18" t="n">
-        <v>-18052.02</v>
+        <v>-21.3</v>
       </c>
       <c r="R76" s="34" t="n">
-        <v>-121771.1</v>
+        <v>264.45</v>
       </c>
       <c r="S76" s="18" t="n">
-        <v>2915.55</v>
+        <v>-28.43</v>
       </c>
       <c r="T76" s="18" t="n">
-        <v>-11999.52</v>
+        <v>92.64</v>
       </c>
       <c r="U76" s="18" t="n">
-        <v>-4089.06</v>
+        <v>-74.31</v>
       </c>
       <c r="V76" s="18" t="n">
-        <v>217.08</v>
+        <v>-101.96</v>
       </c>
       <c r="W76" s="34" t="n">
-        <v>-12955.95</v>
+        <v>-112.06</v>
       </c>
       <c r="X76" s="18" t="n">
-        <v>-12980.04</v>
+        <v>-10.45</v>
       </c>
       <c r="Y76" s="19" t="n">
-        <v>3592.94</v>
+        <v>87.59</v>
       </c>
       <c r="Z76" s="10" t="n"/>
       <c r="AA76" s="10" t="n"/>
@@ -14706,49 +14675,49 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>재무활동으로인한현금흐름</t>
+          <t>투자활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="H77" s="9" t="n"/>
       <c r="L77" s="18" t="n">
-        <v>-53.46</v>
+        <v>-12024.34</v>
       </c>
       <c r="M77" s="9" t="n"/>
       <c r="N77" s="18" t="n">
-        <v>87959.69</v>
+        <v>-106453.41</v>
       </c>
       <c r="O77" s="18" t="n">
-        <v>-40.86</v>
+        <v>5413.59</v>
       </c>
       <c r="P77" s="18" t="n">
-        <v>-33.92</v>
+        <v>-2679.26</v>
       </c>
       <c r="Q77" s="18" t="n">
-        <v>17843.86</v>
+        <v>-18052.02</v>
       </c>
       <c r="R77" s="34" t="n">
-        <v>105728.77</v>
+        <v>-121771.1</v>
       </c>
       <c r="S77" s="18" t="n">
-        <v>1978.09</v>
+        <v>2915.55</v>
       </c>
       <c r="T77" s="18" t="n">
-        <v>-522.9299999999999</v>
+        <v>-11999.52</v>
       </c>
       <c r="U77" s="18" t="n">
-        <v>-277.65</v>
+        <v>-4089.06</v>
       </c>
       <c r="V77" s="18" t="n">
-        <v>16436.37</v>
+        <v>217.08</v>
       </c>
       <c r="W77" s="34" t="n">
-        <v>17613.88</v>
+        <v>-12955.95</v>
       </c>
       <c r="X77" s="18" t="n">
-        <v>3231.89</v>
+        <v>-12980.04</v>
       </c>
       <c r="Y77" s="19" t="n">
-        <v>-793.08</v>
+        <v>3592.94</v>
       </c>
       <c r="Z77" s="10" t="n"/>
       <c r="AA77" s="10" t="n"/>
@@ -14770,41 +14739,49 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>단기차입금의증가</t>
+          <t>재무활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="H78" s="9" t="n"/>
       <c r="L78" s="18" t="n">
-        <v>0</v>
+        <v>-53.46</v>
       </c>
       <c r="M78" s="9" t="n"/>
+      <c r="N78" s="18" t="n">
+        <v>87959.69</v>
+      </c>
+      <c r="O78" s="18" t="n">
+        <v>-40.86</v>
+      </c>
       <c r="P78" s="18" t="n">
-        <v>0</v>
+        <v>-33.92</v>
       </c>
       <c r="Q78" s="18" t="n">
-        <v>5000</v>
-      </c>
-      <c r="R78" s="9" t="n"/>
+        <v>17843.86</v>
+      </c>
+      <c r="R78" s="34" t="n">
+        <v>105728.77</v>
+      </c>
       <c r="S78" s="18" t="n">
-        <v>5000</v>
+        <v>1978.09</v>
       </c>
       <c r="T78" s="18" t="n">
-        <v>0</v>
+        <v>-522.9299999999999</v>
       </c>
       <c r="U78" s="18" t="n">
-        <v>0</v>
+        <v>-277.65</v>
       </c>
       <c r="V78" s="18" t="n">
-        <v>10000</v>
+        <v>16436.37</v>
       </c>
       <c r="W78" s="34" t="n">
-        <v>15000</v>
+        <v>17613.88</v>
       </c>
       <c r="X78" s="18" t="n">
-        <v>0</v>
+        <v>3231.89</v>
       </c>
       <c r="Y78" s="19" t="n">
-        <v>0</v>
+        <v>-793.08</v>
       </c>
       <c r="Z78" s="10" t="n"/>
       <c r="AA78" s="10" t="n"/>
@@ -14826,7 +14803,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>장기차입금의증가</t>
+          <t>단기차입금의증가</t>
         </is>
       </c>
       <c r="H79" s="9" t="n"/>
@@ -14834,23 +14811,15 @@
         <v>0</v>
       </c>
       <c r="M79" s="9" t="n"/>
-      <c r="N79" s="18" t="n">
-        <v>88000</v>
-      </c>
-      <c r="O79" s="18" t="n">
-        <v>0</v>
-      </c>
       <c r="P79" s="18" t="n">
         <v>0</v>
       </c>
       <c r="Q79" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R79" s="34" t="n">
-        <v>88000</v>
-      </c>
+        <v>5000</v>
+      </c>
+      <c r="R79" s="9" t="n"/>
       <c r="S79" s="18" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="T79" s="18" t="n">
         <v>0</v>
@@ -14859,12 +14828,17 @@
         <v>0</v>
       </c>
       <c r="V79" s="18" t="n">
+        <v>10000</v>
+      </c>
+      <c r="W79" s="34" t="n">
+        <v>15000</v>
+      </c>
+      <c r="X79" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W79" s="34" t="n">
+      <c r="Y79" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="Y79" s="5" t="n"/>
       <c r="Z79" s="10" t="n"/>
       <c r="AA79" s="10" t="n"/>
       <c r="AB79" s="11" t="n"/>
@@ -14885,7 +14859,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>단기차입금의감소</t>
+          <t>장기차입금의증가</t>
         </is>
       </c>
       <c r="H80" s="9" t="n"/>
@@ -14893,34 +14867,37 @@
         <v>0</v>
       </c>
       <c r="M80" s="9" t="n"/>
+      <c r="N80" s="18" t="n">
+        <v>88000</v>
+      </c>
+      <c r="O80" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="P80" s="18" t="n">
         <v>0</v>
       </c>
       <c r="Q80" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="R80" s="9" t="n"/>
+      <c r="R80" s="34" t="n">
+        <v>88000</v>
+      </c>
       <c r="S80" s="18" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="T80" s="18" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="U80" s="18" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="V80" s="18" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="W80" s="34" t="n">
-        <v>3000</v>
-      </c>
-      <c r="X80" s="18" t="n">
-        <v>3750</v>
-      </c>
-      <c r="Y80" s="19" t="n">
-        <v>750</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y80" s="5" t="n"/>
       <c r="Z80" s="10" t="n"/>
       <c r="AA80" s="10" t="n"/>
       <c r="AB80" s="11" t="n"/>
@@ -14941,7 +14918,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>장기차입금의감소</t>
+          <t>단기차입금의감소</t>
         </is>
       </c>
       <c r="H81" s="9" t="n"/>
@@ -14949,12 +14926,34 @@
         <v>0</v>
       </c>
       <c r="M81" s="9" t="n"/>
+      <c r="P81" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="Q81" s="18" t="n">
         <v>0</v>
       </c>
       <c r="R81" s="9" t="n"/>
-      <c r="W81" s="9" t="n"/>
-      <c r="Y81" s="5" t="n"/>
+      <c r="S81" s="18" t="n">
+        <v>2000</v>
+      </c>
+      <c r="T81" s="18" t="n">
+        <v>500</v>
+      </c>
+      <c r="U81" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="V81" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="W81" s="34" t="n">
+        <v>3000</v>
+      </c>
+      <c r="X81" s="18" t="n">
+        <v>3750</v>
+      </c>
+      <c r="Y81" s="19" t="n">
+        <v>750</v>
+      </c>
       <c r="Z81" s="10" t="n"/>
       <c r="AA81" s="10" t="n"/>
       <c r="AB81" s="11" t="n"/>
@@ -14975,7 +14974,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>유동성장기부채의감소</t>
+          <t>장기차입금의감소</t>
         </is>
       </c>
       <c r="H82" s="9" t="n"/>
@@ -14983,34 +14982,12 @@
         <v>0</v>
       </c>
       <c r="M82" s="9" t="n"/>
-      <c r="P82" s="18" t="n">
-        <v>0</v>
-      </c>
       <c r="Q82" s="18" t="n">
         <v>0</v>
       </c>
       <c r="R82" s="9" t="n"/>
-      <c r="S82" s="18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="T82" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U82" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V82" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W82" s="34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="X82" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y82" s="19" t="n">
-        <v>0</v>
-      </c>
+      <c r="W82" s="9" t="n"/>
+      <c r="Y82" s="5" t="n"/>
       <c r="Z82" s="10" t="n"/>
       <c r="AA82" s="10" t="n"/>
       <c r="AB82" s="11" t="n"/>
@@ -15031,49 +15008,41 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>리스부채의상환</t>
+          <t>유동성장기부채의감소</t>
         </is>
       </c>
       <c r="H83" s="9" t="n"/>
       <c r="L83" s="18" t="n">
-        <v>7.71</v>
+        <v>0</v>
       </c>
       <c r="M83" s="9" t="n"/>
-      <c r="N83" s="18" t="n">
-        <v>40.31</v>
-      </c>
-      <c r="O83" s="18" t="n">
-        <v>40.86</v>
-      </c>
       <c r="P83" s="18" t="n">
-        <v>33.92</v>
+        <v>0</v>
       </c>
       <c r="Q83" s="18" t="n">
-        <v>23.09</v>
-      </c>
-      <c r="R83" s="34" t="n">
-        <v>138.18</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R83" s="9" t="n"/>
       <c r="S83" s="18" t="n">
-        <v>21.91</v>
+        <v>1000</v>
       </c>
       <c r="T83" s="18" t="n">
-        <v>22.93</v>
+        <v>0</v>
       </c>
       <c r="U83" s="18" t="n">
-        <v>27.65</v>
+        <v>0</v>
       </c>
       <c r="V83" s="18" t="n">
-        <v>47.85</v>
+        <v>0</v>
       </c>
       <c r="W83" s="34" t="n">
-        <v>120.34</v>
+        <v>1000</v>
       </c>
       <c r="X83" s="18" t="n">
-        <v>43.27</v>
+        <v>0</v>
       </c>
       <c r="Y83" s="19" t="n">
-        <v>43.08</v>
+        <v>0</v>
       </c>
       <c r="Z83" s="10" t="n"/>
       <c r="AA83" s="10" t="n"/>
@@ -15095,48 +15064,50 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>현금및현금성자산의증감</t>
+          <t>리스부채의상환</t>
         </is>
       </c>
       <c r="H84" s="9" t="n"/>
       <c r="L84" s="18" t="n">
-        <v>-8904.18</v>
+        <v>7.71</v>
       </c>
       <c r="M84" s="9" t="n"/>
       <c r="N84" s="18" t="n">
-        <v>-23914.98</v>
+        <v>40.31</v>
       </c>
       <c r="O84" s="18" t="n">
-        <v>24111.38</v>
+        <v>40.86</v>
       </c>
       <c r="P84" s="18" t="n">
-        <v>-9736.690000000001</v>
+        <v>33.92</v>
       </c>
       <c r="Q84" s="18" t="n">
-        <v>2404.72</v>
+        <v>23.09</v>
       </c>
       <c r="R84" s="34" t="n">
-        <v>-7135.57</v>
+        <v>138.18</v>
       </c>
       <c r="S84" s="18" t="n">
-        <v>6289.14</v>
+        <v>21.91</v>
       </c>
       <c r="T84" s="18" t="n">
-        <v>-12154.55</v>
+        <v>22.93</v>
       </c>
       <c r="U84" s="18" t="n">
-        <v>-5745.7</v>
+        <v>27.65</v>
       </c>
       <c r="V84" s="18" t="n">
-        <v>37952.16</v>
+        <v>47.85</v>
       </c>
       <c r="W84" s="34" t="n">
-        <v>26341.05</v>
+        <v>120.34</v>
       </c>
       <c r="X84" s="18" t="n">
-        <v>-25074.62</v>
-      </c>
-      <c r="Y84" s="5" t="n"/>
+        <v>43.27</v>
+      </c>
+      <c r="Y84" s="19" t="n">
+        <v>43.08</v>
+      </c>
       <c r="Z84" s="10" t="n"/>
       <c r="AA84" s="10" t="n"/>
       <c r="AB84" s="11" t="n"/>
@@ -15157,7 +15128,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>기말현금및현금성자산</t>
+          <t>현금및현금성자산의증감</t>
         </is>
       </c>
       <c r="H85" s="9" t="n"/>
@@ -15166,41 +15137,39 @@
       </c>
       <c r="M85" s="9" t="n"/>
       <c r="N85" s="18" t="n">
-        <v>2817.92</v>
+        <v>-23914.98</v>
       </c>
       <c r="O85" s="18" t="n">
         <v>24111.38</v>
       </c>
       <c r="P85" s="18" t="n">
-        <v>-9736.68</v>
+        <v>-9736.690000000001</v>
       </c>
       <c r="Q85" s="18" t="n">
-        <v>2404.71</v>
+        <v>2404.72</v>
       </c>
       <c r="R85" s="34" t="n">
-        <v>19597.33</v>
+        <v>-7135.57</v>
       </c>
       <c r="S85" s="18" t="n">
-        <v>25886.48</v>
+        <v>6289.14</v>
       </c>
       <c r="T85" s="18" t="n">
-        <v>-12154.56</v>
+        <v>-12154.55</v>
       </c>
       <c r="U85" s="18" t="n">
         <v>-5745.7</v>
       </c>
       <c r="V85" s="18" t="n">
-        <v>37867.75</v>
+        <v>37952.16</v>
       </c>
       <c r="W85" s="34" t="n">
-        <v>45853.97</v>
+        <v>26341.05</v>
       </c>
       <c r="X85" s="18" t="n">
-        <v>21114.54</v>
-      </c>
-      <c r="Y85" s="19" t="n">
-        <v>-1274.09</v>
-      </c>
+        <v>-25074.62</v>
+      </c>
+      <c r="Y85" s="5" t="n"/>
       <c r="Z85" s="10" t="n"/>
       <c r="AA85" s="10" t="n"/>
       <c r="AB85" s="11" t="n"/>
@@ -15221,20 +15190,50 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>배당금수취(CF)</t>
+          <t>기말현금및현금성자산</t>
         </is>
       </c>
       <c r="H86" s="9" t="n"/>
+      <c r="L86" s="18" t="n">
+        <v>-8904.18</v>
+      </c>
       <c r="M86" s="9" t="n"/>
-      <c r="R86" s="9" t="n"/>
+      <c r="N86" s="18" t="n">
+        <v>2817.92</v>
+      </c>
+      <c r="O86" s="18" t="n">
+        <v>24111.38</v>
+      </c>
+      <c r="P86" s="18" t="n">
+        <v>-9736.68</v>
+      </c>
+      <c r="Q86" s="18" t="n">
+        <v>2404.71</v>
+      </c>
+      <c r="R86" s="34" t="n">
+        <v>19597.33</v>
+      </c>
+      <c r="S86" s="18" t="n">
+        <v>25886.48</v>
+      </c>
+      <c r="T86" s="18" t="n">
+        <v>-12154.56</v>
+      </c>
       <c r="U86" s="18" t="n">
-        <v>0</v>
+        <v>-5745.7</v>
       </c>
       <c r="V86" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W86" s="9" t="n"/>
-      <c r="Y86" s="5" t="n"/>
+        <v>37867.75</v>
+      </c>
+      <c r="W86" s="34" t="n">
+        <v>45853.97</v>
+      </c>
+      <c r="X86" s="18" t="n">
+        <v>21114.54</v>
+      </c>
+      <c r="Y86" s="19" t="n">
+        <v>-1274.09</v>
+      </c>
       <c r="Z86" s="10" t="n"/>
       <c r="AA86" s="10" t="n"/>
       <c r="AB86" s="11" t="n"/>
@@ -15248,6 +15247,40 @@
       <c r="AJ86" s="10" t="n"/>
       <c r="AK86" s="10" t="n"/>
       <c r="AL86" s="11" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>1</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>배당금수취(CF)</t>
+        </is>
+      </c>
+      <c r="H87" s="9" t="n"/>
+      <c r="M87" s="9" t="n"/>
+      <c r="R87" s="9" t="n"/>
+      <c r="U87" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V87" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W87" s="9" t="n"/>
+      <c r="Y87" s="5" t="n"/>
+      <c r="Z87" s="10" t="n"/>
+      <c r="AA87" s="10" t="n"/>
+      <c r="AB87" s="11" t="n"/>
+      <c r="AC87" s="10" t="n"/>
+      <c r="AD87" s="10" t="n"/>
+      <c r="AE87" s="10" t="n"/>
+      <c r="AF87" s="10" t="n"/>
+      <c r="AG87" s="11" t="n"/>
+      <c r="AH87" s="10" t="n"/>
+      <c r="AI87" s="10" t="n"/>
+      <c r="AJ87" s="10" t="n"/>
+      <c r="AK87" s="10" t="n"/>
+      <c r="AL87" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15492,7 +15525,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/382900_model.xlsx
+++ b/argus/kship/models/382900_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AL$1</definedName>
@@ -3934,7 +3934,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-05</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -4755,35 +4755,35 @@
         <v>1418.75</v>
       </c>
       <c r="AA6" s="16" t="n">
-        <v>1354.78</v>
+        <v>1351.18</v>
       </c>
       <c r="AB6" s="17" t="n">
-        <v>1460.21</v>
+        <v>1459.61</v>
       </c>
       <c r="AC6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AE6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG6" s="11" t="n"/>
       <c r="AH6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AK6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL6" s="11" t="n"/>
     </row>
@@ -4865,35 +4865,35 @@
         <v>1355.4</v>
       </c>
       <c r="AA7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AB7" s="17" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AC7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AE7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG7" s="11" t="n"/>
       <c r="AH7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AK7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL7" s="11" t="n"/>
     </row>
@@ -4975,35 +4975,35 @@
         <v>890.41</v>
       </c>
       <c r="AA8" s="16" t="n">
-        <v>858.4</v>
+        <v>855.39</v>
       </c>
       <c r="AB8" s="17" t="n">
-        <v>921.0599999999999</v>
+        <v>920.6900000000001</v>
       </c>
       <c r="AC8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AE8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG8" s="11" t="n"/>
       <c r="AH8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AK8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL8" s="11" t="n"/>
     </row>
@@ -5085,35 +5085,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AA9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AB9" s="17" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AC9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AE9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG9" s="11" t="n"/>
       <c r="AH9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AK9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL9" s="11" t="n"/>
     </row>
@@ -5195,35 +5195,35 @@
         <v>1631.97</v>
       </c>
       <c r="AA10" s="16" t="n">
-        <v>1525.7</v>
+        <v>1519.07</v>
       </c>
       <c r="AB10" s="17" t="n">
-        <v>1694.79</v>
+        <v>1693.81</v>
       </c>
       <c r="AC10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AE10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG10" s="11" t="n"/>
       <c r="AH10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AK10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL10" s="11" t="n"/>
     </row>
@@ -5305,35 +5305,35 @@
         <v>1539.06</v>
       </c>
       <c r="AA11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AB11" s="17" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AC11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AE11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG11" s="11" t="n"/>
       <c r="AH11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AK11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL11" s="11" t="n"/>
     </row>
@@ -5415,35 +5415,35 @@
         <v>210.43</v>
       </c>
       <c r="AA12" s="16" t="n">
-        <v>202.07</v>
+        <v>201.53</v>
       </c>
       <c r="AB12" s="17" t="n">
-        <v>214.1</v>
+        <v>214.03</v>
       </c>
       <c r="AC12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AE12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="11" t="n"/>
       <c r="AH12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AK12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="11" t="n"/>
     </row>
@@ -5525,35 +5525,35 @@
         <v>202.16</v>
       </c>
       <c r="AA13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AB13" s="17" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AC13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="11" t="n"/>
       <c r="AH13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AK13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="11" t="n"/>
     </row>
@@ -5652,7 +5652,7 @@
         <v>25050</v>
       </c>
       <c r="AA15" s="20" t="n">
-        <v>25050</v>
+        <v>25300</v>
       </c>
       <c r="AB15" s="11" t="n"/>
       <c r="AC15" s="10" t="n"/>
@@ -5904,7 +5904,7 @@
         <v>18741.1</v>
       </c>
       <c r="AA18" s="20" t="n">
-        <v>25450</v>
+        <v>25400</v>
       </c>
       <c r="AB18" s="11" t="n"/>
       <c r="AC18" s="10" t="n"/>
@@ -8169,7 +8169,7 @@
         </is>
       </c>
       <c r="D40" s="34" t="n">
-        <v>25050</v>
+        <v>25300</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="D41" s="35" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -8475,7 +8475,7 @@
         </is>
       </c>
       <c r="D48" s="36" t="n">
-        <v>0.09373844061392077</v>
+        <v>0.09373844061392075</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -8551,7 +8551,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.04894776875942602</v>
+        <v>0.04894776875943081</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9005,7 +9005,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -14983,7 +14983,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -27954,7 +27954,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -32523,7 +32523,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34430,7 +34430,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="33">
@@ -34464,7 +34464,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>106.94</v>
+        <v>107.67</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/382900_model.xlsx
+++ b/argus/kship/models/382900_model.xlsx
@@ -3934,7 +3934,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -4755,35 +4755,35 @@
         <v>1418.75</v>
       </c>
       <c r="AA6" s="16" t="n">
-        <v>1351.18</v>
+        <v>1348.08</v>
       </c>
       <c r="AB6" s="17" t="n">
-        <v>1459.61</v>
+        <v>1458.99</v>
       </c>
       <c r="AC6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AE6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG6" s="11" t="n"/>
       <c r="AH6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AK6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL6" s="11" t="n"/>
     </row>
@@ -4865,35 +4865,35 @@
         <v>1355.4</v>
       </c>
       <c r="AA7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AB7" s="17" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AC7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AE7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG7" s="11" t="n"/>
       <c r="AH7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AK7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL7" s="11" t="n"/>
     </row>
@@ -4975,35 +4975,35 @@
         <v>890.41</v>
       </c>
       <c r="AA8" s="16" t="n">
-        <v>855.39</v>
+        <v>853.26</v>
       </c>
       <c r="AB8" s="17" t="n">
-        <v>920.6900000000001</v>
+        <v>920.3099999999999</v>
       </c>
       <c r="AC8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AE8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG8" s="11" t="n"/>
       <c r="AH8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AK8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL8" s="11" t="n"/>
     </row>
@@ -5085,35 +5085,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AA9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AB9" s="17" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AC9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AE9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG9" s="11" t="n"/>
       <c r="AH9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AK9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL9" s="11" t="n"/>
     </row>
@@ -5195,35 +5195,35 @@
         <v>1631.97</v>
       </c>
       <c r="AA10" s="16" t="n">
-        <v>1519.07</v>
+        <v>1516.47</v>
       </c>
       <c r="AB10" s="17" t="n">
-        <v>1693.81</v>
+        <v>1692.86</v>
       </c>
       <c r="AC10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AE10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG10" s="11" t="n"/>
       <c r="AH10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AK10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL10" s="11" t="n"/>
     </row>
@@ -5305,35 +5305,35 @@
         <v>1539.06</v>
       </c>
       <c r="AA11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AB11" s="17" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AC11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AE11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG11" s="11" t="n"/>
       <c r="AH11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AK11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL11" s="11" t="n"/>
     </row>
@@ -5415,35 +5415,35 @@
         <v>210.43</v>
       </c>
       <c r="AA12" s="16" t="n">
-        <v>201.53</v>
+        <v>201.07</v>
       </c>
       <c r="AB12" s="17" t="n">
-        <v>214.03</v>
+        <v>213.96</v>
       </c>
       <c r="AC12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AE12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG12" s="11" t="n"/>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL12" s="11" t="n"/>
     </row>
@@ -5525,35 +5525,35 @@
         <v>202.16</v>
       </c>
       <c r="AA13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AB13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AC13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AE13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG13" s="11" t="n"/>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL13" s="11" t="n"/>
     </row>
@@ -5652,7 +5652,7 @@
         <v>25050</v>
       </c>
       <c r="AA15" s="20" t="n">
-        <v>25300</v>
+        <v>25200</v>
       </c>
       <c r="AB15" s="11" t="n"/>
       <c r="AC15" s="10" t="n"/>
@@ -5736,7 +5736,7 @@
         <v>28200</v>
       </c>
       <c r="AA16" s="20" t="n">
-        <v>25900</v>
+        <v>26450</v>
       </c>
       <c r="AB16" s="11" t="n"/>
       <c r="AC16" s="10" t="n"/>
@@ -5904,7 +5904,7 @@
         <v>18741.1</v>
       </c>
       <c r="AA18" s="20" t="n">
-        <v>25400</v>
+        <v>25437.5</v>
       </c>
       <c r="AB18" s="11" t="n"/>
       <c r="AC18" s="10" t="n"/>
@@ -8169,11 +8169,11 @@
         </is>
       </c>
       <c r="D40" s="34" t="n">
-        <v>25300</v>
+        <v>25200</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 25,450원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 24,950원)</t>
         </is>
       </c>
       <c r="H40" s="9" t="n"/>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="D41" s="35" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -9005,7 +9005,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -14983,7 +14983,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -27954,7 +27954,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -32523,7 +32523,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34464,7 +34464,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>107.67</v>
+        <v>107.38</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/382900_model.xlsx
+++ b/argus/kship/models/382900_model.xlsx
@@ -3934,7 +3934,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
         </is>
       </c>
     </row>
@@ -9005,7 +9005,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -14983,7 +14983,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/382900_model.xlsx
+++ b/argus/kship/models/382900_model.xlsx
@@ -4755,35 +4755,35 @@
         <v>1418.75</v>
       </c>
       <c r="AA6" s="16" t="n">
-        <v>1348.08</v>
+        <v>1346.2</v>
       </c>
       <c r="AB6" s="17" t="n">
-        <v>1458.99</v>
+        <v>1458.38</v>
       </c>
       <c r="AC6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AE6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG6" s="11" t="n"/>
       <c r="AH6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AK6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL6" s="11" t="n"/>
     </row>
@@ -4865,35 +4865,35 @@
         <v>1355.4</v>
       </c>
       <c r="AA7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AB7" s="17" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AC7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AE7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG7" s="11" t="n"/>
       <c r="AH7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AK7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL7" s="11" t="n"/>
     </row>
@@ -4975,35 +4975,35 @@
         <v>890.41</v>
       </c>
       <c r="AA8" s="16" t="n">
-        <v>853.26</v>
+        <v>851.8099999999999</v>
       </c>
       <c r="AB8" s="17" t="n">
-        <v>920.3099999999999</v>
+        <v>919.9299999999999</v>
       </c>
       <c r="AC8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AE8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG8" s="11" t="n"/>
       <c r="AH8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AK8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL8" s="11" t="n"/>
     </row>
@@ -5085,35 +5085,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AA9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AB9" s="17" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AC9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AE9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG9" s="11" t="n"/>
       <c r="AH9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AK9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL9" s="11" t="n"/>
     </row>
@@ -5195,35 +5195,35 @@
         <v>1631.97</v>
       </c>
       <c r="AA10" s="16" t="n">
-        <v>1516.47</v>
+        <v>1512.43</v>
       </c>
       <c r="AB10" s="17" t="n">
-        <v>1692.86</v>
+        <v>1691.86</v>
       </c>
       <c r="AC10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AE10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG10" s="11" t="n"/>
       <c r="AH10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AK10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL10" s="11" t="n"/>
     </row>
@@ -5305,35 +5305,35 @@
         <v>1539.06</v>
       </c>
       <c r="AA11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AB11" s="17" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AC11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AE11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG11" s="11" t="n"/>
       <c r="AH11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AK11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL11" s="11" t="n"/>
     </row>
@@ -5415,35 +5415,35 @@
         <v>210.43</v>
       </c>
       <c r="AA12" s="16" t="n">
-        <v>201.07</v>
+        <v>200.79</v>
       </c>
       <c r="AB12" s="17" t="n">
-        <v>213.96</v>
+        <v>213.89</v>
       </c>
       <c r="AC12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AE12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG12" s="11" t="n"/>
       <c r="AH12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AK12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL12" s="11" t="n"/>
     </row>
@@ -5525,35 +5525,35 @@
         <v>202.16</v>
       </c>
       <c r="AA13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AB13" s="17" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AC13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AE13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG13" s="11" t="n"/>
       <c r="AH13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AK13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL13" s="11" t="n"/>
     </row>
@@ -5652,7 +5652,7 @@
         <v>25050</v>
       </c>
       <c r="AA15" s="20" t="n">
-        <v>25200</v>
+        <v>24250</v>
       </c>
       <c r="AB15" s="11" t="n"/>
       <c r="AC15" s="10" t="n"/>
@@ -5820,7 +5820,7 @@
         <v>11810</v>
       </c>
       <c r="AA17" s="20" t="n">
-        <v>24100</v>
+        <v>24050</v>
       </c>
       <c r="AB17" s="11" t="n"/>
       <c r="AC17" s="10" t="n"/>
@@ -5904,7 +5904,7 @@
         <v>18741.1</v>
       </c>
       <c r="AA18" s="20" t="n">
-        <v>25437.5</v>
+        <v>25120</v>
       </c>
       <c r="AB18" s="11" t="n"/>
       <c r="AC18" s="10" t="n"/>
@@ -8169,11 +8169,11 @@
         </is>
       </c>
       <c r="D40" s="34" t="n">
-        <v>25200</v>
+        <v>24250</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 24,950원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 25,350원)</t>
         </is>
       </c>
       <c r="H40" s="9" t="n"/>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="D41" s="35" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -27954,7 +27954,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -32523,7 +32523,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34430,7 +34430,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="33">
@@ -34464,7 +34464,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>107.38</v>
+        <v>104.62</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/382900_model.xlsx
+++ b/argus/kship/models/382900_model.xlsx
@@ -1,29 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AL$1</definedName>
     <definedName name="환율">변수!$C$6:$AL$13</definedName>
     <definedName name="BS연결H">BS연결!$C$1:$AL$1</definedName>
-    <definedName name="BS연결">BS연결!$C$5:$AL$93</definedName>
+    <definedName name="BS연결">BS연결!$C$5:$AL$95</definedName>
     <definedName name="BS별도H">BS별도!$C$1:$AL$1</definedName>
-    <definedName name="BS별도">BS별도!$C$5:$AL$93</definedName>
+    <definedName name="BS별도">BS별도!$C$5:$AL$95</definedName>
     <definedName name="SUBQH">subQ!$A$1:$AL$1</definedName>
     <definedName name="subQ">subQ!$A$5:$AL$40</definedName>
   </definedNames>
@@ -3934,7 +3934,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
         </is>
       </c>
     </row>
@@ -8475,7 +8475,7 @@
         </is>
       </c>
       <c r="D48" s="36" t="n">
-        <v>0.09373844061392075</v>
+        <v>0.09373844061392077</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -8551,7 +8551,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.04894776875943081</v>
+        <v>0.04894776875942602</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -8773,7 +8773,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL93"/>
+  <dimension ref="A1:AL95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -9005,7 +9005,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -10874,46 +10874,46 @@
       </c>
       <c r="H29" s="9" t="n"/>
       <c r="L29" s="18" t="n">
-        <v>167.76</v>
+        <v>1217.15</v>
       </c>
       <c r="M29" s="37" t="n">
-        <v>167.76</v>
+        <v>1217.15</v>
       </c>
       <c r="N29" s="18" t="n">
-        <v>153.64</v>
+        <v>1186.97</v>
       </c>
       <c r="O29" s="18" t="n">
-        <v>134.37</v>
+        <v>1136.75</v>
       </c>
       <c r="P29" s="18" t="n">
-        <v>120.25</v>
+        <v>1103.64</v>
       </c>
       <c r="Q29" s="18" t="n">
-        <v>120.62</v>
+        <v>1080.55</v>
       </c>
       <c r="R29" s="37" t="n">
-        <v>120.62</v>
+        <v>1080.55</v>
       </c>
       <c r="S29" s="18" t="n">
-        <v>119.08</v>
+        <v>1010.5</v>
       </c>
       <c r="T29" s="18" t="n">
-        <v>116.23</v>
+        <v>987.5599999999999</v>
       </c>
       <c r="U29" s="18" t="n">
-        <v>168.46</v>
+        <v>1448.35</v>
       </c>
       <c r="V29" s="18" t="n">
-        <v>163.92</v>
+        <v>1140.94</v>
       </c>
       <c r="W29" s="37" t="n">
-        <v>163.92</v>
+        <v>1140.94</v>
       </c>
       <c r="X29" s="18" t="n">
-        <v>154.52</v>
+        <v>1108.1</v>
       </c>
       <c r="Y29" s="19" t="n">
-        <v>146.75</v>
+        <v>1076.37</v>
       </c>
       <c r="Z29" s="10" t="n"/>
       <c r="AA29" s="10" t="n"/>
@@ -11298,51 +11298,51 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>확정급여부채</t>
+          <t>비유동리스부채</t>
         </is>
       </c>
       <c r="H36" s="9" t="n"/>
       <c r="L36" s="18" t="n">
-        <v>338.53</v>
+        <v>1049.39</v>
       </c>
       <c r="M36" s="37" t="n">
-        <v>338.53</v>
+        <v>1049.39</v>
       </c>
       <c r="N36" s="18" t="n">
-        <v>488.6</v>
+        <v>1033.33</v>
       </c>
       <c r="O36" s="18" t="n">
-        <v>625.52</v>
+        <v>1002.38</v>
       </c>
       <c r="P36" s="18" t="n">
-        <v>759.51</v>
+        <v>983.39</v>
       </c>
       <c r="Q36" s="18" t="n">
-        <v>913.67</v>
+        <v>959.9299999999999</v>
       </c>
       <c r="R36" s="37" t="n">
-        <v>913.67</v>
+        <v>959.9299999999999</v>
       </c>
       <c r="S36" s="18" t="n">
-        <v>1093.17</v>
+        <v>891.42</v>
       </c>
       <c r="T36" s="18" t="n">
-        <v>1277.01</v>
+        <v>871.33</v>
       </c>
       <c r="U36" s="18" t="n">
-        <v>1451.31</v>
+        <v>1279.89</v>
       </c>
       <c r="V36" s="18" t="n">
-        <v>760</v>
+        <v>977.02</v>
       </c>
       <c r="W36" s="37" t="n">
-        <v>760</v>
+        <v>977.02</v>
       </c>
       <c r="X36" s="18" t="n">
-        <v>957.75</v>
+        <v>953.58</v>
       </c>
       <c r="Y36" s="19" t="n">
-        <v>990.04</v>
+        <v>929.62</v>
       </c>
       <c r="Z36" s="10" t="n"/>
       <c r="AA36" s="10" t="n"/>
@@ -11364,51 +11364,51 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>기타비유동부채</t>
+          <t>장기금융부채</t>
         </is>
       </c>
       <c r="H37" s="9" t="n"/>
       <c r="L37" s="18" t="n">
-        <v>30.43</v>
+        <v>1049.39</v>
       </c>
       <c r="M37" s="37" t="n">
-        <v>30.43</v>
+        <v>1049.39</v>
       </c>
       <c r="N37" s="18" t="n">
-        <v>31.98</v>
+        <v>1033.33</v>
       </c>
       <c r="O37" s="18" t="n">
-        <v>33.54</v>
+        <v>1002.38</v>
       </c>
       <c r="P37" s="18" t="n">
-        <v>35.1</v>
+        <v>983.39</v>
       </c>
       <c r="Q37" s="18" t="n">
-        <v>34.93</v>
+        <v>959.9299999999999</v>
       </c>
       <c r="R37" s="37" t="n">
-        <v>34.93</v>
+        <v>959.9299999999999</v>
       </c>
       <c r="S37" s="18" t="n">
-        <v>36.59</v>
+        <v>891.42</v>
       </c>
       <c r="T37" s="18" t="n">
-        <v>38.39</v>
+        <v>871.33</v>
       </c>
       <c r="U37" s="18" t="n">
-        <v>40.12</v>
+        <v>1279.89</v>
       </c>
       <c r="V37" s="18" t="n">
-        <v>43.77</v>
+        <v>977.02</v>
       </c>
       <c r="W37" s="37" t="n">
-        <v>43.77</v>
+        <v>977.02</v>
       </c>
       <c r="X37" s="18" t="n">
-        <v>45.65</v>
+        <v>953.58</v>
       </c>
       <c r="Y37" s="19" t="n">
-        <v>47.54</v>
+        <v>929.62</v>
       </c>
       <c r="Z37" s="10" t="n"/>
       <c r="AA37" s="10" t="n"/>
@@ -11430,51 +11430,51 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>부채총계</t>
+          <t>확정급여부채</t>
         </is>
       </c>
       <c r="H38" s="9" t="n"/>
       <c r="L38" s="18" t="n">
-        <v>17739.06</v>
+        <v>338.53</v>
       </c>
       <c r="M38" s="37" t="n">
-        <v>17739.06</v>
+        <v>338.53</v>
       </c>
       <c r="N38" s="18" t="n">
-        <v>126083.3</v>
+        <v>488.6</v>
       </c>
       <c r="O38" s="18" t="n">
-        <v>121979.57</v>
+        <v>625.52</v>
       </c>
       <c r="P38" s="18" t="n">
-        <v>116200.41</v>
+        <v>759.51</v>
       </c>
       <c r="Q38" s="18" t="n">
-        <v>146566.52</v>
+        <v>913.67</v>
       </c>
       <c r="R38" s="37" t="n">
-        <v>146566.52</v>
+        <v>913.67</v>
       </c>
       <c r="S38" s="18" t="n">
-        <v>148071.87</v>
+        <v>1093.17</v>
       </c>
       <c r="T38" s="18" t="n">
-        <v>144648.48</v>
+        <v>1277.01</v>
       </c>
       <c r="U38" s="18" t="n">
-        <v>143815.82</v>
+        <v>1451.31</v>
       </c>
       <c r="V38" s="18" t="n">
-        <v>189667.51</v>
+        <v>760</v>
       </c>
       <c r="W38" s="37" t="n">
-        <v>189667.51</v>
+        <v>760</v>
       </c>
       <c r="X38" s="18" t="n">
-        <v>190006.4</v>
+        <v>957.75</v>
       </c>
       <c r="Y38" s="19" t="n">
-        <v>179509.57</v>
+        <v>990.04</v>
       </c>
       <c r="Z38" s="10" t="n"/>
       <c r="AA38" s="10" t="n"/>
@@ -11496,51 +11496,51 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>지배주주지분</t>
+          <t>기타비유동부채</t>
         </is>
       </c>
       <c r="H39" s="9" t="n"/>
       <c r="L39" s="18" t="n">
-        <v>103901.83</v>
+        <v>30.43</v>
       </c>
       <c r="M39" s="37" t="n">
-        <v>103901.83</v>
+        <v>30.43</v>
       </c>
       <c r="N39" s="18" t="n">
-        <v>103319.43</v>
+        <v>31.98</v>
       </c>
       <c r="O39" s="18" t="n">
-        <v>104241.26</v>
+        <v>33.54</v>
       </c>
       <c r="P39" s="18" t="n">
-        <v>105016.48</v>
+        <v>35.1</v>
       </c>
       <c r="Q39" s="18" t="n">
-        <v>164067.07</v>
+        <v>34.93</v>
       </c>
       <c r="R39" s="37" t="n">
-        <v>164067.07</v>
+        <v>34.93</v>
       </c>
       <c r="S39" s="18" t="n">
-        <v>164071.91</v>
+        <v>36.59</v>
       </c>
       <c r="T39" s="18" t="n">
-        <v>163694.17</v>
+        <v>38.39</v>
       </c>
       <c r="U39" s="18" t="n">
-        <v>164030.72</v>
+        <v>40.12</v>
       </c>
       <c r="V39" s="18" t="n">
-        <v>161305.57</v>
+        <v>43.77</v>
       </c>
       <c r="W39" s="37" t="n">
-        <v>161305.57</v>
+        <v>43.77</v>
       </c>
       <c r="X39" s="18" t="n">
-        <v>159659.58</v>
+        <v>45.65</v>
       </c>
       <c r="Y39" s="19" t="n">
-        <v>155873</v>
+        <v>47.54</v>
       </c>
       <c r="Z39" s="10" t="n"/>
       <c r="AA39" s="10" t="n"/>
@@ -11562,51 +11562,51 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>자본금</t>
+          <t>부채총계</t>
         </is>
       </c>
       <c r="H40" s="9" t="n"/>
       <c r="L40" s="18" t="n">
-        <v>4380.5</v>
+        <v>17739.06</v>
       </c>
       <c r="M40" s="37" t="n">
-        <v>4380.5</v>
+        <v>17739.06</v>
       </c>
       <c r="N40" s="18" t="n">
-        <v>4380.5</v>
+        <v>126083.3</v>
       </c>
       <c r="O40" s="18" t="n">
-        <v>4380.5</v>
+        <v>121979.57</v>
       </c>
       <c r="P40" s="18" t="n">
-        <v>4380.5</v>
+        <v>116200.41</v>
       </c>
       <c r="Q40" s="18" t="n">
-        <v>4380.5</v>
+        <v>146566.52</v>
       </c>
       <c r="R40" s="37" t="n">
-        <v>4380.5</v>
+        <v>146566.52</v>
       </c>
       <c r="S40" s="18" t="n">
-        <v>4380.5</v>
+        <v>148071.87</v>
       </c>
       <c r="T40" s="18" t="n">
-        <v>4380.5</v>
+        <v>144648.48</v>
       </c>
       <c r="U40" s="18" t="n">
-        <v>4380.5</v>
+        <v>143815.82</v>
       </c>
       <c r="V40" s="18" t="n">
-        <v>4380.5</v>
+        <v>189667.51</v>
       </c>
       <c r="W40" s="37" t="n">
-        <v>4380.5</v>
+        <v>189667.51</v>
       </c>
       <c r="X40" s="18" t="n">
-        <v>4380.5</v>
+        <v>190006.4</v>
       </c>
       <c r="Y40" s="19" t="n">
-        <v>4380.5</v>
+        <v>179509.57</v>
       </c>
       <c r="Z40" s="10" t="n"/>
       <c r="AA40" s="10" t="n"/>
@@ -11628,51 +11628,51 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>자본잉여금</t>
+          <t>지배주주지분</t>
         </is>
       </c>
       <c r="H41" s="9" t="n"/>
       <c r="L41" s="18" t="n">
-        <v>92513.42</v>
+        <v>103901.83</v>
       </c>
       <c r="M41" s="37" t="n">
-        <v>92513.42</v>
+        <v>103901.83</v>
       </c>
       <c r="N41" s="18" t="n">
-        <v>92527.78999999999</v>
+        <v>103319.43</v>
       </c>
       <c r="O41" s="18" t="n">
-        <v>92538.2</v>
+        <v>104241.26</v>
       </c>
       <c r="P41" s="18" t="n">
-        <v>92538.2</v>
+        <v>105016.48</v>
       </c>
       <c r="Q41" s="18" t="n">
-        <v>92538.2</v>
+        <v>164067.07</v>
       </c>
       <c r="R41" s="37" t="n">
-        <v>92538.2</v>
+        <v>164067.07</v>
       </c>
       <c r="S41" s="18" t="n">
-        <v>92538.2</v>
+        <v>164071.91</v>
       </c>
       <c r="T41" s="18" t="n">
-        <v>92538.2</v>
+        <v>163694.17</v>
       </c>
       <c r="U41" s="18" t="n">
-        <v>92538.2</v>
+        <v>164030.72</v>
       </c>
       <c r="V41" s="18" t="n">
-        <v>92538.2</v>
+        <v>161305.57</v>
       </c>
       <c r="W41" s="37" t="n">
-        <v>92538.2</v>
+        <v>161305.57</v>
       </c>
       <c r="X41" s="18" t="n">
-        <v>92538.2</v>
+        <v>159659.58</v>
       </c>
       <c r="Y41" s="19" t="n">
-        <v>92538.2</v>
+        <v>155873</v>
       </c>
       <c r="Z41" s="10" t="n"/>
       <c r="AA41" s="10" t="n"/>
@@ -11694,51 +11694,51 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>이익잉여금</t>
+          <t>자본금</t>
         </is>
       </c>
       <c r="H42" s="9" t="n"/>
       <c r="L42" s="18" t="n">
-        <v>7007.91</v>
+        <v>4380.5</v>
       </c>
       <c r="M42" s="37" t="n">
-        <v>7007.91</v>
+        <v>4380.5</v>
       </c>
       <c r="N42" s="18" t="n">
-        <v>6411.14</v>
+        <v>4380.5</v>
       </c>
       <c r="O42" s="18" t="n">
-        <v>7322.57</v>
+        <v>4380.5</v>
       </c>
       <c r="P42" s="18" t="n">
-        <v>8097.78</v>
+        <v>4380.5</v>
       </c>
       <c r="Q42" s="18" t="n">
-        <v>7452.06</v>
+        <v>4380.5</v>
       </c>
       <c r="R42" s="37" t="n">
-        <v>7452.06</v>
+        <v>4380.5</v>
       </c>
       <c r="S42" s="18" t="n">
-        <v>7456.9</v>
+        <v>4380.5</v>
       </c>
       <c r="T42" s="18" t="n">
-        <v>7079.16</v>
+        <v>4380.5</v>
       </c>
       <c r="U42" s="18" t="n">
-        <v>7415.71</v>
+        <v>4380.5</v>
       </c>
       <c r="V42" s="18" t="n">
-        <v>8935.43</v>
+        <v>4380.5</v>
       </c>
       <c r="W42" s="37" t="n">
-        <v>8935.43</v>
+        <v>4380.5</v>
       </c>
       <c r="X42" s="18" t="n">
-        <v>7289.44</v>
+        <v>4380.5</v>
       </c>
       <c r="Y42" s="19" t="n">
-        <v>3502.86</v>
+        <v>4380.5</v>
       </c>
       <c r="Z42" s="10" t="n"/>
       <c r="AA42" s="10" t="n"/>
@@ -11760,51 +11760,51 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>비지배주주지분</t>
+          <t>자본잉여금</t>
         </is>
       </c>
       <c r="H43" s="9" t="n"/>
       <c r="L43" s="18" t="n">
-        <v>1994.79</v>
+        <v>92513.42</v>
       </c>
       <c r="M43" s="37" t="n">
-        <v>1994.79</v>
+        <v>92513.42</v>
       </c>
       <c r="N43" s="18" t="n">
-        <v>1954.41</v>
+        <v>92527.78999999999</v>
       </c>
       <c r="O43" s="18" t="n">
-        <v>1939.18</v>
+        <v>92538.2</v>
       </c>
       <c r="P43" s="18" t="n">
-        <v>1868.8</v>
+        <v>92538.2</v>
       </c>
       <c r="Q43" s="18" t="n">
-        <v>1785.34</v>
+        <v>92538.2</v>
       </c>
       <c r="R43" s="37" t="n">
-        <v>1785.34</v>
+        <v>92538.2</v>
       </c>
       <c r="S43" s="18" t="n">
-        <v>1707.76</v>
+        <v>92538.2</v>
       </c>
       <c r="T43" s="18" t="n">
-        <v>1618.68</v>
+        <v>92538.2</v>
       </c>
       <c r="U43" s="18" t="n">
-        <v>1511.49</v>
+        <v>92538.2</v>
       </c>
       <c r="V43" s="18" t="n">
-        <v>1387.69</v>
+        <v>92538.2</v>
       </c>
       <c r="W43" s="37" t="n">
-        <v>1387.69</v>
+        <v>92538.2</v>
       </c>
       <c r="X43" s="18" t="n">
-        <v>1376.62</v>
+        <v>92538.2</v>
       </c>
       <c r="Y43" s="19" t="n">
-        <v>1187.19</v>
+        <v>92538.2</v>
       </c>
       <c r="Z43" s="10" t="n"/>
       <c r="AA43" s="10" t="n"/>
@@ -11826,51 +11826,51 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>자본총계</t>
+          <t>이익잉여금</t>
         </is>
       </c>
       <c r="H44" s="9" t="n"/>
       <c r="L44" s="18" t="n">
-        <v>105896.62</v>
+        <v>7007.91</v>
       </c>
       <c r="M44" s="37" t="n">
-        <v>105896.62</v>
+        <v>7007.91</v>
       </c>
       <c r="N44" s="18" t="n">
-        <v>105273.84</v>
+        <v>6411.14</v>
       </c>
       <c r="O44" s="18" t="n">
-        <v>106180.45</v>
+        <v>7322.57</v>
       </c>
       <c r="P44" s="18" t="n">
-        <v>106885.28</v>
+        <v>8097.78</v>
       </c>
       <c r="Q44" s="18" t="n">
-        <v>165852.41</v>
+        <v>7452.06</v>
       </c>
       <c r="R44" s="37" t="n">
-        <v>165852.41</v>
+        <v>7452.06</v>
       </c>
       <c r="S44" s="18" t="n">
-        <v>165779.67</v>
+        <v>7456.9</v>
       </c>
       <c r="T44" s="18" t="n">
-        <v>165312.85</v>
+        <v>7079.16</v>
       </c>
       <c r="U44" s="18" t="n">
-        <v>165542.22</v>
+        <v>7415.71</v>
       </c>
       <c r="V44" s="18" t="n">
-        <v>162693.26</v>
+        <v>8935.43</v>
       </c>
       <c r="W44" s="37" t="n">
-        <v>162693.26</v>
+        <v>8935.43</v>
       </c>
       <c r="X44" s="18" t="n">
-        <v>161036.2</v>
+        <v>7289.44</v>
       </c>
       <c r="Y44" s="19" t="n">
-        <v>157060.19</v>
+        <v>3502.86</v>
       </c>
       <c r="Z44" s="10" t="n"/>
       <c r="AA44" s="10" t="n"/>
@@ -11892,51 +11892,51 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>부채와자본총계</t>
+          <t>비지배주주지분</t>
         </is>
       </c>
       <c r="H45" s="9" t="n"/>
       <c r="L45" s="18" t="n">
-        <v>123635.67</v>
+        <v>1994.79</v>
       </c>
       <c r="M45" s="37" t="n">
-        <v>123635.67</v>
+        <v>1994.79</v>
       </c>
       <c r="N45" s="18" t="n">
-        <v>231357.15</v>
+        <v>1954.41</v>
       </c>
       <c r="O45" s="18" t="n">
-        <v>228160.02</v>
+        <v>1939.18</v>
       </c>
       <c r="P45" s="18" t="n">
-        <v>223085.69</v>
+        <v>1868.8</v>
       </c>
       <c r="Q45" s="18" t="n">
-        <v>312418.93</v>
+        <v>1785.34</v>
       </c>
       <c r="R45" s="37" t="n">
-        <v>312418.93</v>
+        <v>1785.34</v>
       </c>
       <c r="S45" s="18" t="n">
-        <v>313851.54</v>
+        <v>1707.76</v>
       </c>
       <c r="T45" s="18" t="n">
-        <v>309961.34</v>
+        <v>1618.68</v>
       </c>
       <c r="U45" s="18" t="n">
-        <v>309358.04</v>
+        <v>1511.49</v>
       </c>
       <c r="V45" s="18" t="n">
-        <v>352360.77</v>
+        <v>1387.69</v>
       </c>
       <c r="W45" s="37" t="n">
-        <v>352360.77</v>
+        <v>1387.69</v>
       </c>
       <c r="X45" s="18" t="n">
-        <v>351042.61</v>
+        <v>1376.62</v>
       </c>
       <c r="Y45" s="19" t="n">
-        <v>336569.76</v>
+        <v>1187.19</v>
       </c>
       <c r="Z45" s="10" t="n"/>
       <c r="AA45" s="10" t="n"/>
@@ -11958,51 +11958,51 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>총차입금</t>
+          <t>자본총계</t>
         </is>
       </c>
       <c r="H46" s="9" t="n"/>
       <c r="L46" s="18" t="n">
-        <v>8090</v>
+        <v>105896.62</v>
       </c>
       <c r="M46" s="37" t="n">
-        <v>8090</v>
+        <v>105896.62</v>
       </c>
       <c r="N46" s="18" t="n">
-        <v>96090</v>
+        <v>105273.84</v>
       </c>
       <c r="O46" s="18" t="n">
-        <v>96090</v>
+        <v>106180.45</v>
       </c>
       <c r="P46" s="18" t="n">
-        <v>96090</v>
+        <v>106885.28</v>
       </c>
       <c r="Q46" s="18" t="n">
-        <v>124660.02</v>
+        <v>165852.41</v>
       </c>
       <c r="R46" s="37" t="n">
-        <v>124660.02</v>
+        <v>165852.41</v>
       </c>
       <c r="S46" s="18" t="n">
-        <v>127107.84</v>
+        <v>165779.67</v>
       </c>
       <c r="T46" s="18" t="n">
-        <v>127064.16</v>
+        <v>165312.85</v>
       </c>
       <c r="U46" s="18" t="n">
-        <v>127279.14</v>
+        <v>165542.22</v>
       </c>
       <c r="V46" s="18" t="n">
-        <v>134731.4</v>
+        <v>162693.26</v>
       </c>
       <c r="W46" s="37" t="n">
-        <v>134731.4</v>
+        <v>162693.26</v>
       </c>
       <c r="X46" s="18" t="n">
-        <v>127363.51</v>
+        <v>161036.2</v>
       </c>
       <c r="Y46" s="19" t="n">
-        <v>123207.83</v>
+        <v>157060.19</v>
       </c>
       <c r="Z46" s="10" t="n"/>
       <c r="AA46" s="10" t="n"/>
@@ -12024,51 +12024,51 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>순차입금</t>
+          <t>부채와자본총계</t>
         </is>
       </c>
       <c r="H47" s="9" t="n"/>
       <c r="L47" s="18" t="n">
-        <v>-34182.9</v>
+        <v>123635.67</v>
       </c>
       <c r="M47" s="37" t="n">
-        <v>-34182.9</v>
+        <v>123635.67</v>
       </c>
       <c r="N47" s="18" t="n">
-        <v>87642.08</v>
+        <v>231357.15</v>
       </c>
       <c r="O47" s="18" t="n">
-        <v>63800.7</v>
+        <v>228160.02</v>
       </c>
       <c r="P47" s="18" t="n">
-        <v>74447.38</v>
+        <v>223085.69</v>
       </c>
       <c r="Q47" s="18" t="n">
-        <v>101522.69</v>
+        <v>312418.93</v>
       </c>
       <c r="R47" s="37" t="n">
-        <v>101522.69</v>
+        <v>312418.93</v>
       </c>
       <c r="S47" s="18" t="n">
-        <v>100621.36</v>
+        <v>313851.54</v>
       </c>
       <c r="T47" s="18" t="n">
-        <v>110680.88</v>
+        <v>309961.34</v>
       </c>
       <c r="U47" s="18" t="n">
-        <v>116641.56</v>
+        <v>309358.04</v>
       </c>
       <c r="V47" s="18" t="n">
-        <v>86226.07000000001</v>
+        <v>352360.77</v>
       </c>
       <c r="W47" s="37" t="n">
-        <v>86226.07000000001</v>
+        <v>352360.77</v>
       </c>
       <c r="X47" s="18" t="n">
-        <v>98597.61</v>
+        <v>351042.61</v>
       </c>
       <c r="Y47" s="19" t="n">
-        <v>101016.38</v>
+        <v>336569.76</v>
       </c>
       <c r="Z47" s="10" t="n"/>
       <c r="AA47" s="10" t="n"/>
@@ -12090,51 +12090,51 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>이자발생자산</t>
+          <t>총차입금</t>
         </is>
       </c>
       <c r="H48" s="9" t="n"/>
       <c r="L48" s="18" t="n">
-        <v>50379.58</v>
+        <v>8090</v>
       </c>
       <c r="M48" s="37" t="n">
-        <v>50379.58</v>
+        <v>8090</v>
       </c>
       <c r="N48" s="18" t="n">
-        <v>16579.04</v>
+        <v>96090</v>
       </c>
       <c r="O48" s="18" t="n">
-        <v>40420.42</v>
+        <v>96090</v>
       </c>
       <c r="P48" s="18" t="n">
-        <v>29773.74</v>
+        <v>96090</v>
       </c>
       <c r="Q48" s="18" t="n">
-        <v>27768.45</v>
+        <v>124660.02</v>
       </c>
       <c r="R48" s="37" t="n">
-        <v>27768.45</v>
+        <v>124660.02</v>
       </c>
       <c r="S48" s="18" t="n">
-        <v>31436.09</v>
+        <v>127107.84</v>
       </c>
       <c r="T48" s="18" t="n">
-        <v>21332.89</v>
+        <v>127064.16</v>
       </c>
       <c r="U48" s="18" t="n">
-        <v>19597.19</v>
+        <v>127279.14</v>
       </c>
       <c r="V48" s="18" t="n">
-        <v>55589.94</v>
+        <v>134731.4</v>
       </c>
       <c r="W48" s="37" t="n">
-        <v>55589.94</v>
+        <v>134731.4</v>
       </c>
       <c r="X48" s="18" t="n">
-        <v>36305.23</v>
+        <v>127363.51</v>
       </c>
       <c r="Y48" s="19" t="n">
-        <v>29730.78</v>
+        <v>123207.83</v>
       </c>
       <c r="Z48" s="10" t="n"/>
       <c r="AA48" s="10" t="n"/>
@@ -12156,20 +12156,52 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>투자부동산</t>
+          <t>순차입금</t>
         </is>
       </c>
       <c r="H49" s="9" t="n"/>
-      <c r="M49" s="9" t="n"/>
+      <c r="L49" s="18" t="n">
+        <v>-34182.9</v>
+      </c>
+      <c r="M49" s="37" t="n">
+        <v>-34182.9</v>
+      </c>
+      <c r="N49" s="18" t="n">
+        <v>87642.08</v>
+      </c>
       <c r="O49" s="18" t="n">
-        <v>116302.65</v>
+        <v>63800.7</v>
       </c>
       <c r="P49" s="18" t="n">
-        <v>116194.1</v>
-      </c>
-      <c r="R49" s="9" t="n"/>
-      <c r="W49" s="9" t="n"/>
-      <c r="Y49" s="5" t="n"/>
+        <v>74447.38</v>
+      </c>
+      <c r="Q49" s="18" t="n">
+        <v>101522.69</v>
+      </c>
+      <c r="R49" s="37" t="n">
+        <v>101522.69</v>
+      </c>
+      <c r="S49" s="18" t="n">
+        <v>100621.36</v>
+      </c>
+      <c r="T49" s="18" t="n">
+        <v>110680.88</v>
+      </c>
+      <c r="U49" s="18" t="n">
+        <v>116641.56</v>
+      </c>
+      <c r="V49" s="18" t="n">
+        <v>86226.07000000001</v>
+      </c>
+      <c r="W49" s="37" t="n">
+        <v>86226.07000000001</v>
+      </c>
+      <c r="X49" s="18" t="n">
+        <v>98597.61</v>
+      </c>
+      <c r="Y49" s="19" t="n">
+        <v>101016.38</v>
+      </c>
       <c r="Z49" s="10" t="n"/>
       <c r="AA49" s="10" t="n"/>
       <c r="AB49" s="11" t="n"/>
@@ -12190,37 +12222,51 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>기타유동금융부채</t>
+          <t>이자발생자산</t>
         </is>
       </c>
       <c r="H50" s="9" t="n"/>
-      <c r="M50" s="9" t="n"/>
+      <c r="L50" s="18" t="n">
+        <v>50379.58</v>
+      </c>
+      <c r="M50" s="37" t="n">
+        <v>50379.58</v>
+      </c>
+      <c r="N50" s="18" t="n">
+        <v>16579.04</v>
+      </c>
+      <c r="O50" s="18" t="n">
+        <v>40420.42</v>
+      </c>
+      <c r="P50" s="18" t="n">
+        <v>29773.74</v>
+      </c>
       <c r="Q50" s="18" t="n">
-        <v>4081.04</v>
+        <v>27768.45</v>
       </c>
       <c r="R50" s="37" t="n">
-        <v>4081.04</v>
+        <v>27768.45</v>
       </c>
       <c r="S50" s="18" t="n">
-        <v>4081.04</v>
+        <v>31436.09</v>
       </c>
       <c r="T50" s="18" t="n">
-        <v>4081.04</v>
+        <v>21332.89</v>
       </c>
       <c r="U50" s="18" t="n">
-        <v>4081.04</v>
+        <v>19597.19</v>
       </c>
       <c r="V50" s="18" t="n">
-        <v>9554.57</v>
+        <v>55589.94</v>
       </c>
       <c r="W50" s="37" t="n">
-        <v>9554.57</v>
+        <v>55589.94</v>
       </c>
       <c r="X50" s="18" t="n">
-        <v>9554.57</v>
+        <v>36305.23</v>
       </c>
       <c r="Y50" s="19" t="n">
-        <v>13373.8</v>
+        <v>29730.78</v>
       </c>
       <c r="Z50" s="10" t="n"/>
       <c r="AA50" s="10" t="n"/>
@@ -12242,38 +12288,20 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>이연법인세부채</t>
+          <t>투자부동산</t>
         </is>
       </c>
       <c r="H51" s="9" t="n"/>
       <c r="M51" s="9" t="n"/>
-      <c r="Q51" s="18" t="n">
-        <v>11480.74</v>
-      </c>
-      <c r="R51" s="37" t="n">
-        <v>11480.74</v>
-      </c>
-      <c r="S51" s="18" t="n">
-        <v>11480.74</v>
-      </c>
-      <c r="T51" s="18" t="n">
-        <v>11555.1</v>
-      </c>
-      <c r="U51" s="18" t="n">
-        <v>11555.1</v>
-      </c>
-      <c r="V51" s="18" t="n">
-        <v>14160.66</v>
-      </c>
-      <c r="W51" s="37" t="n">
-        <v>14160.66</v>
-      </c>
-      <c r="X51" s="18" t="n">
-        <v>14160.66</v>
-      </c>
-      <c r="Y51" s="19" t="n">
-        <v>12939.38</v>
-      </c>
+      <c r="O51" s="18" t="n">
+        <v>116302.65</v>
+      </c>
+      <c r="P51" s="18" t="n">
+        <v>116194.1</v>
+      </c>
+      <c r="R51" s="9" t="n"/>
+      <c r="W51" s="9" t="n"/>
+      <c r="Y51" s="5" t="n"/>
       <c r="Z51" s="10" t="n"/>
       <c r="AA51" s="10" t="n"/>
       <c r="AB51" s="11" t="n"/>
@@ -12294,37 +12322,37 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>기타포괄이익누계액</t>
+          <t>기타유동금융부채</t>
         </is>
       </c>
       <c r="H52" s="9" t="n"/>
       <c r="M52" s="9" t="n"/>
       <c r="Q52" s="18" t="n">
-        <v>59696.31</v>
+        <v>4081.04</v>
       </c>
       <c r="R52" s="37" t="n">
-        <v>59696.31</v>
+        <v>4081.04</v>
       </c>
       <c r="S52" s="18" t="n">
-        <v>59696.31</v>
+        <v>4081.04</v>
       </c>
       <c r="T52" s="18" t="n">
-        <v>59696.31</v>
+        <v>4081.04</v>
       </c>
       <c r="U52" s="18" t="n">
-        <v>59696.31</v>
+        <v>4081.04</v>
       </c>
       <c r="V52" s="18" t="n">
-        <v>55451.44</v>
+        <v>9554.57</v>
       </c>
       <c r="W52" s="37" t="n">
-        <v>55451.44</v>
+        <v>9554.57</v>
       </c>
       <c r="X52" s="18" t="n">
-        <v>55451.44</v>
+        <v>9554.57</v>
       </c>
       <c r="Y52" s="19" t="n">
-        <v>55451.44</v>
+        <v>13373.8</v>
       </c>
       <c r="Z52" s="10" t="n"/>
       <c r="AA52" s="10" t="n"/>
@@ -12346,33 +12374,38 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>사채</t>
+          <t>이연법인세부채</t>
         </is>
       </c>
       <c r="H53" s="9" t="n"/>
       <c r="M53" s="9" t="n"/>
       <c r="Q53" s="18" t="n">
-        <v>11785.01</v>
+        <v>11480.74</v>
       </c>
       <c r="R53" s="37" t="n">
-        <v>11785.01</v>
+        <v>11480.74</v>
       </c>
       <c r="S53" s="18" t="n">
-        <v>12008.92</v>
+        <v>11480.74</v>
       </c>
       <c r="T53" s="18" t="n">
-        <v>12237.08</v>
+        <v>11555.1</v>
       </c>
       <c r="U53" s="18" t="n">
-        <v>12469.57</v>
+        <v>11555.1</v>
       </c>
       <c r="V53" s="18" t="n">
-        <v>11320.7</v>
+        <v>14160.66</v>
       </c>
       <c r="W53" s="37" t="n">
-        <v>11320.7</v>
-      </c>
-      <c r="Y53" s="5" t="n"/>
+        <v>14160.66</v>
+      </c>
+      <c r="X53" s="18" t="n">
+        <v>14160.66</v>
+      </c>
+      <c r="Y53" s="19" t="n">
+        <v>12939.38</v>
+      </c>
       <c r="Z53" s="10" t="n"/>
       <c r="AA53" s="10" t="n"/>
       <c r="AB53" s="11" t="n"/>
@@ -12393,15 +12426,37 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>단기금융부채(face)</t>
+          <t>기타포괄이익누계액</t>
         </is>
       </c>
       <c r="H54" s="9" t="n"/>
       <c r="M54" s="9" t="n"/>
-      <c r="R54" s="9" t="n"/>
-      <c r="W54" s="9" t="n"/>
+      <c r="Q54" s="18" t="n">
+        <v>59696.31</v>
+      </c>
+      <c r="R54" s="37" t="n">
+        <v>59696.31</v>
+      </c>
+      <c r="S54" s="18" t="n">
+        <v>59696.31</v>
+      </c>
+      <c r="T54" s="18" t="n">
+        <v>59696.31</v>
+      </c>
+      <c r="U54" s="18" t="n">
+        <v>59696.31</v>
+      </c>
+      <c r="V54" s="18" t="n">
+        <v>55451.44</v>
+      </c>
+      <c r="W54" s="37" t="n">
+        <v>55451.44</v>
+      </c>
+      <c r="X54" s="18" t="n">
+        <v>55451.44</v>
+      </c>
       <c r="Y54" s="19" t="n">
-        <v>123207.83</v>
+        <v>55451.44</v>
       </c>
       <c r="Z54" s="10" t="n"/>
       <c r="AA54" s="10" t="n"/>
@@ -12423,16 +12478,33 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>장기금융부채(face)</t>
+          <t>사채</t>
         </is>
       </c>
       <c r="H55" s="9" t="n"/>
       <c r="M55" s="9" t="n"/>
-      <c r="R55" s="9" t="n"/>
-      <c r="W55" s="9" t="n"/>
-      <c r="Y55" s="19" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q55" s="18" t="n">
+        <v>11785.01</v>
+      </c>
+      <c r="R55" s="37" t="n">
+        <v>11785.01</v>
+      </c>
+      <c r="S55" s="18" t="n">
+        <v>12008.92</v>
+      </c>
+      <c r="T55" s="18" t="n">
+        <v>12237.08</v>
+      </c>
+      <c r="U55" s="18" t="n">
+        <v>12469.57</v>
+      </c>
+      <c r="V55" s="18" t="n">
+        <v>11320.7</v>
+      </c>
+      <c r="W55" s="37" t="n">
+        <v>11320.7</v>
+      </c>
+      <c r="Y55" s="5" t="n"/>
       <c r="Z55" s="10" t="n"/>
       <c r="AA55" s="10" t="n"/>
       <c r="AB55" s="11" t="n"/>
@@ -12453,49 +12525,15 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>매출액(수익)</t>
+          <t>단기금융부채(face)</t>
         </is>
       </c>
       <c r="H56" s="9" t="n"/>
-      <c r="L56" s="18" t="n">
-        <v>7450.42</v>
-      </c>
       <c r="M56" s="9" t="n"/>
-      <c r="N56" s="18" t="n">
-        <v>6719.84</v>
-      </c>
-      <c r="O56" s="18" t="n">
-        <v>9194.01</v>
-      </c>
-      <c r="P56" s="18" t="n">
-        <v>11000.03</v>
-      </c>
-      <c r="Q56" s="18" t="n">
-        <v>9280.799999999999</v>
-      </c>
-      <c r="R56" s="37" t="n">
-        <v>36194.68</v>
-      </c>
-      <c r="S56" s="18" t="n">
-        <v>10446.45</v>
-      </c>
-      <c r="T56" s="18" t="n">
-        <v>7061.17</v>
-      </c>
-      <c r="U56" s="18" t="n">
-        <v>10398.92</v>
-      </c>
-      <c r="V56" s="18" t="n">
-        <v>15454.55</v>
-      </c>
-      <c r="W56" s="37" t="n">
-        <v>43361.09</v>
-      </c>
-      <c r="X56" s="18" t="n">
-        <v>5053.88</v>
-      </c>
+      <c r="R56" s="9" t="n"/>
+      <c r="W56" s="9" t="n"/>
       <c r="Y56" s="19" t="n">
-        <v>17824.99</v>
+        <v>123207.83</v>
       </c>
       <c r="Z56" s="10" t="n"/>
       <c r="AA56" s="10" t="n"/>
@@ -12517,49 +12555,15 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>매출원가</t>
+          <t>장기금융부채(face)</t>
         </is>
       </c>
       <c r="H57" s="9" t="n"/>
-      <c r="L57" s="18" t="n">
-        <v>8731.35</v>
-      </c>
       <c r="M57" s="9" t="n"/>
-      <c r="N57" s="18" t="n">
-        <v>6447.46</v>
-      </c>
-      <c r="O57" s="18" t="n">
-        <v>6693.01</v>
-      </c>
-      <c r="P57" s="18" t="n">
-        <v>8828.98</v>
-      </c>
-      <c r="Q57" s="18" t="n">
-        <v>7973.61</v>
-      </c>
-      <c r="R57" s="37" t="n">
-        <v>29943.06</v>
-      </c>
-      <c r="S57" s="18" t="n">
-        <v>8736.040000000001</v>
-      </c>
-      <c r="T57" s="18" t="n">
-        <v>5738.35</v>
-      </c>
-      <c r="U57" s="18" t="n">
-        <v>8500.41</v>
-      </c>
-      <c r="V57" s="18" t="n">
-        <v>14952.79</v>
-      </c>
-      <c r="W57" s="37" t="n">
-        <v>37927.59</v>
-      </c>
-      <c r="X57" s="18" t="n">
-        <v>6362.33</v>
-      </c>
+      <c r="R57" s="9" t="n"/>
+      <c r="W57" s="9" t="n"/>
       <c r="Y57" s="19" t="n">
-        <v>19527.47</v>
+        <v>0</v>
       </c>
       <c r="Z57" s="10" t="n"/>
       <c r="AA57" s="10" t="n"/>
@@ -12581,49 +12585,49 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>매출총이익</t>
+          <t>매출액(수익)</t>
         </is>
       </c>
       <c r="H58" s="9" t="n"/>
       <c r="L58" s="18" t="n">
-        <v>-1280.93</v>
+        <v>7450.42</v>
       </c>
       <c r="M58" s="9" t="n"/>
       <c r="N58" s="18" t="n">
-        <v>272.38</v>
+        <v>6719.84</v>
       </c>
       <c r="O58" s="18" t="n">
-        <v>2500.99</v>
+        <v>9194.01</v>
       </c>
       <c r="P58" s="18" t="n">
-        <v>2171.05</v>
+        <v>11000.03</v>
       </c>
       <c r="Q58" s="18" t="n">
-        <v>1307.2</v>
+        <v>9280.799999999999</v>
       </c>
       <c r="R58" s="37" t="n">
-        <v>6251.62</v>
+        <v>36194.68</v>
       </c>
       <c r="S58" s="18" t="n">
-        <v>1710.41</v>
+        <v>10446.45</v>
       </c>
       <c r="T58" s="18" t="n">
-        <v>1322.81</v>
+        <v>7061.17</v>
       </c>
       <c r="U58" s="18" t="n">
-        <v>1898.51</v>
+        <v>10398.92</v>
       </c>
       <c r="V58" s="18" t="n">
-        <v>501.76</v>
+        <v>15454.55</v>
       </c>
       <c r="W58" s="37" t="n">
-        <v>5433.49</v>
+        <v>43361.09</v>
       </c>
       <c r="X58" s="18" t="n">
-        <v>-1308.45</v>
+        <v>5053.88</v>
       </c>
       <c r="Y58" s="19" t="n">
-        <v>-1702.47</v>
+        <v>17824.99</v>
       </c>
       <c r="Z58" s="10" t="n"/>
       <c r="AA58" s="10" t="n"/>
@@ -12645,49 +12649,49 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>판관비</t>
+          <t>매출원가</t>
         </is>
       </c>
       <c r="H59" s="9" t="n"/>
       <c r="L59" s="18" t="n">
-        <v>765.54</v>
+        <v>8731.35</v>
       </c>
       <c r="M59" s="9" t="n"/>
       <c r="N59" s="18" t="n">
-        <v>907.8099999999999</v>
+        <v>6447.46</v>
       </c>
       <c r="O59" s="18" t="n">
-        <v>850.8099999999999</v>
+        <v>6693.01</v>
       </c>
       <c r="P59" s="18" t="n">
-        <v>832.6900000000001</v>
+        <v>8828.98</v>
       </c>
       <c r="Q59" s="18" t="n">
-        <v>1249.17</v>
+        <v>7973.61</v>
       </c>
       <c r="R59" s="37" t="n">
-        <v>3840.48</v>
+        <v>29943.06</v>
       </c>
       <c r="S59" s="18" t="n">
-        <v>1030.14</v>
+        <v>8736.040000000001</v>
       </c>
       <c r="T59" s="18" t="n">
-        <v>1166.39</v>
+        <v>5738.35</v>
       </c>
       <c r="U59" s="18" t="n">
-        <v>1056.59</v>
+        <v>8500.41</v>
       </c>
       <c r="V59" s="18" t="n">
-        <v>1322.54</v>
+        <v>14952.79</v>
       </c>
       <c r="W59" s="37" t="n">
-        <v>4575.66</v>
+        <v>37927.59</v>
       </c>
       <c r="X59" s="18" t="n">
-        <v>836.67</v>
+        <v>6362.33</v>
       </c>
       <c r="Y59" s="19" t="n">
-        <v>1530.79</v>
+        <v>19527.47</v>
       </c>
       <c r="Z59" s="10" t="n"/>
       <c r="AA59" s="10" t="n"/>
@@ -12709,49 +12713,49 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>영업이익</t>
+          <t>매출총이익</t>
         </is>
       </c>
       <c r="H60" s="9" t="n"/>
       <c r="L60" s="18" t="n">
-        <v>-2046.47</v>
+        <v>-1280.93</v>
       </c>
       <c r="M60" s="9" t="n"/>
       <c r="N60" s="18" t="n">
-        <v>-635.4299999999999</v>
+        <v>272.38</v>
       </c>
       <c r="O60" s="18" t="n">
-        <v>1650.18</v>
+        <v>2500.99</v>
       </c>
       <c r="P60" s="18" t="n">
-        <v>1338.36</v>
+        <v>2171.05</v>
       </c>
       <c r="Q60" s="18" t="n">
-        <v>58.03</v>
+        <v>1307.2</v>
       </c>
       <c r="R60" s="37" t="n">
-        <v>2411.14</v>
+        <v>6251.62</v>
       </c>
       <c r="S60" s="18" t="n">
-        <v>680.28</v>
+        <v>1710.41</v>
       </c>
       <c r="T60" s="18" t="n">
-        <v>156.43</v>
+        <v>1322.81</v>
       </c>
       <c r="U60" s="18" t="n">
-        <v>841.9299999999999</v>
+        <v>1898.51</v>
       </c>
       <c r="V60" s="18" t="n">
-        <v>-820.78</v>
+        <v>501.76</v>
       </c>
       <c r="W60" s="37" t="n">
-        <v>857.86</v>
+        <v>5433.49</v>
       </c>
       <c r="X60" s="18" t="n">
-        <v>-2145.12</v>
+        <v>-1308.45</v>
       </c>
       <c r="Y60" s="19" t="n">
-        <v>-3233.27</v>
+        <v>-1702.47</v>
       </c>
       <c r="Z60" s="10" t="n"/>
       <c r="AA60" s="10" t="n"/>
@@ -12773,49 +12777,49 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>금융수익</t>
+          <t>판관비</t>
         </is>
       </c>
       <c r="H61" s="9" t="n"/>
       <c r="L61" s="18" t="n">
-        <v>513.77</v>
+        <v>765.54</v>
       </c>
       <c r="M61" s="9" t="n"/>
       <c r="N61" s="18" t="n">
-        <v>387.04</v>
+        <v>907.8099999999999</v>
       </c>
       <c r="O61" s="18" t="n">
-        <v>333.56</v>
+        <v>850.8099999999999</v>
       </c>
       <c r="P61" s="18" t="n">
-        <v>353.3</v>
+        <v>832.6900000000001</v>
       </c>
       <c r="Q61" s="18" t="n">
-        <v>762.24</v>
+        <v>1249.17</v>
       </c>
       <c r="R61" s="37" t="n">
-        <v>1836.14</v>
+        <v>3840.48</v>
       </c>
       <c r="S61" s="18" t="n">
-        <v>540.38</v>
+        <v>1030.14</v>
       </c>
       <c r="T61" s="18" t="n">
-        <v>566.9</v>
+        <v>1166.39</v>
       </c>
       <c r="U61" s="18" t="n">
-        <v>517.03</v>
+        <v>1056.59</v>
       </c>
       <c r="V61" s="18" t="n">
-        <v>6312.34</v>
+        <v>1322.54</v>
       </c>
       <c r="W61" s="37" t="n">
-        <v>7936.65</v>
+        <v>4575.66</v>
       </c>
       <c r="X61" s="18" t="n">
-        <v>562.11</v>
+        <v>836.67</v>
       </c>
       <c r="Y61" s="19" t="n">
-        <v>1106.75</v>
+        <v>1530.79</v>
       </c>
       <c r="Z61" s="10" t="n"/>
       <c r="AA61" s="10" t="n"/>
@@ -12837,49 +12841,49 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>금융비용</t>
+          <t>영업이익</t>
         </is>
       </c>
       <c r="H62" s="9" t="n"/>
       <c r="L62" s="18" t="n">
-        <v>100.24</v>
+        <v>-2046.47</v>
       </c>
       <c r="M62" s="9" t="n"/>
       <c r="N62" s="18" t="n">
-        <v>405.09</v>
+        <v>-635.4299999999999</v>
       </c>
       <c r="O62" s="18" t="n">
-        <v>968.38</v>
+        <v>1650.18</v>
       </c>
       <c r="P62" s="18" t="n">
-        <v>983.92</v>
+        <v>1338.36</v>
       </c>
       <c r="Q62" s="18" t="n">
-        <v>1709.99</v>
+        <v>58.03</v>
       </c>
       <c r="R62" s="37" t="n">
-        <v>4067.38</v>
+        <v>2411.14</v>
       </c>
       <c r="S62" s="18" t="n">
-        <v>1238.07</v>
+        <v>680.28</v>
       </c>
       <c r="T62" s="18" t="n">
-        <v>1156.32</v>
+        <v>156.43</v>
       </c>
       <c r="U62" s="18" t="n">
-        <v>1101.3</v>
+        <v>841.9299999999999</v>
       </c>
       <c r="V62" s="18" t="n">
-        <v>4036.32</v>
+        <v>-820.78</v>
       </c>
       <c r="W62" s="37" t="n">
-        <v>7532.01</v>
+        <v>857.86</v>
       </c>
       <c r="X62" s="18" t="n">
-        <v>1608.56</v>
+        <v>-2145.12</v>
       </c>
       <c r="Y62" s="19" t="n">
-        <v>1885.98</v>
+        <v>-3233.27</v>
       </c>
       <c r="Z62" s="10" t="n"/>
       <c r="AA62" s="10" t="n"/>
@@ -12901,49 +12905,49 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>기타영업외수익</t>
+          <t>금융수익</t>
         </is>
       </c>
       <c r="H63" s="9" t="n"/>
       <c r="L63" s="18" t="n">
-        <v>29.37</v>
+        <v>513.77</v>
       </c>
       <c r="M63" s="9" t="n"/>
       <c r="N63" s="18" t="n">
-        <v>33.33</v>
+        <v>387.04</v>
       </c>
       <c r="O63" s="18" t="n">
-        <v>73.16</v>
+        <v>333.56</v>
       </c>
       <c r="P63" s="18" t="n">
-        <v>15.09</v>
+        <v>353.3</v>
       </c>
       <c r="Q63" s="18" t="n">
-        <v>87.13</v>
+        <v>762.24</v>
       </c>
       <c r="R63" s="37" t="n">
-        <v>208.71</v>
+        <v>1836.14</v>
       </c>
       <c r="S63" s="18" t="n">
-        <v>6.5</v>
+        <v>540.38</v>
       </c>
       <c r="T63" s="18" t="n">
-        <v>64.59</v>
+        <v>566.9</v>
       </c>
       <c r="U63" s="18" t="n">
-        <v>17.48</v>
+        <v>517.03</v>
       </c>
       <c r="V63" s="18" t="n">
-        <v>22.46</v>
+        <v>6312.34</v>
       </c>
       <c r="W63" s="37" t="n">
-        <v>111.03</v>
+        <v>7936.65</v>
       </c>
       <c r="X63" s="18" t="n">
-        <v>1611.05</v>
+        <v>562.11</v>
       </c>
       <c r="Y63" s="19" t="n">
-        <v>-1144.06</v>
+        <v>1106.75</v>
       </c>
       <c r="Z63" s="10" t="n"/>
       <c r="AA63" s="10" t="n"/>
@@ -12965,49 +12969,49 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>기타영업외비용</t>
+          <t>금융비용</t>
         </is>
       </c>
       <c r="H64" s="9" t="n"/>
       <c r="L64" s="18" t="n">
-        <v>84.97</v>
+        <v>100.24</v>
       </c>
       <c r="M64" s="9" t="n"/>
       <c r="N64" s="18" t="n">
-        <v>16.99</v>
+        <v>405.09</v>
       </c>
       <c r="O64" s="18" t="n">
-        <v>59.28</v>
+        <v>968.38</v>
       </c>
       <c r="P64" s="18" t="n">
-        <v>18</v>
+        <v>983.92</v>
       </c>
       <c r="Q64" s="18" t="n">
-        <v>15.11</v>
+        <v>1709.99</v>
       </c>
       <c r="R64" s="37" t="n">
-        <v>109.38</v>
+        <v>4067.38</v>
       </c>
       <c r="S64" s="18" t="n">
-        <v>61.82</v>
+        <v>1238.07</v>
       </c>
       <c r="T64" s="18" t="n">
-        <v>24.04</v>
+        <v>1156.32</v>
       </c>
       <c r="U64" s="18" t="n">
-        <v>45.79</v>
+        <v>1101.3</v>
       </c>
       <c r="V64" s="18" t="n">
-        <v>94.84999999999999</v>
+        <v>4036.32</v>
       </c>
       <c r="W64" s="37" t="n">
-        <v>226.5</v>
+        <v>7532.01</v>
       </c>
       <c r="X64" s="18" t="n">
-        <v>88.63</v>
+        <v>1608.56</v>
       </c>
       <c r="Y64" s="19" t="n">
-        <v>30.2</v>
+        <v>1885.98</v>
       </c>
       <c r="Z64" s="10" t="n"/>
       <c r="AA64" s="10" t="n"/>
@@ -13029,49 +13033,49 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>법인세비용차감전계속사업이익</t>
+          <t>기타영업외수익</t>
         </is>
       </c>
       <c r="H65" s="9" t="n"/>
       <c r="L65" s="18" t="n">
-        <v>-1688.54</v>
+        <v>29.37</v>
       </c>
       <c r="M65" s="9" t="n"/>
       <c r="N65" s="18" t="n">
-        <v>-637.14</v>
+        <v>33.33</v>
       </c>
       <c r="O65" s="18" t="n">
-        <v>1029.24</v>
+        <v>73.16</v>
       </c>
       <c r="P65" s="18" t="n">
-        <v>704.83</v>
+        <v>15.09</v>
       </c>
       <c r="Q65" s="18" t="n">
-        <v>-817.7</v>
+        <v>87.13</v>
       </c>
       <c r="R65" s="37" t="n">
-        <v>279.23</v>
+        <v>208.71</v>
       </c>
       <c r="S65" s="18" t="n">
-        <v>-72.73</v>
+        <v>6.5</v>
       </c>
       <c r="T65" s="18" t="n">
-        <v>-392.45</v>
+        <v>64.59</v>
       </c>
       <c r="U65" s="18" t="n">
-        <v>229.36</v>
+        <v>17.48</v>
       </c>
       <c r="V65" s="18" t="n">
-        <v>1382.85</v>
+        <v>22.46</v>
       </c>
       <c r="W65" s="37" t="n">
-        <v>1147.03</v>
+        <v>111.03</v>
       </c>
       <c r="X65" s="18" t="n">
-        <v>-1669.15</v>
+        <v>1611.05</v>
       </c>
       <c r="Y65" s="19" t="n">
-        <v>-5186.75</v>
+        <v>-1144.06</v>
       </c>
       <c r="Z65" s="10" t="n"/>
       <c r="AA65" s="10" t="n"/>
@@ -13093,49 +13097,49 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>법인세비용</t>
+          <t>기타영업외비용</t>
         </is>
       </c>
       <c r="H66" s="9" t="n"/>
       <c r="L66" s="18" t="n">
-        <v>-542.73</v>
+        <v>84.97</v>
       </c>
       <c r="M66" s="9" t="n"/>
       <c r="N66" s="18" t="n">
-        <v>0</v>
+        <v>16.99</v>
       </c>
       <c r="O66" s="18" t="n">
-        <v>133.04</v>
+        <v>59.28</v>
       </c>
       <c r="P66" s="18" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Q66" s="18" t="n">
-        <v>-478.9</v>
+        <v>15.11</v>
       </c>
       <c r="R66" s="37" t="n">
-        <v>-345.86</v>
+        <v>109.38</v>
       </c>
       <c r="S66" s="18" t="n">
-        <v>0</v>
+        <v>61.82</v>
       </c>
       <c r="T66" s="18" t="n">
-        <v>74.37</v>
+        <v>24.04</v>
       </c>
       <c r="U66" s="18" t="n">
-        <v>0</v>
+        <v>45.79</v>
       </c>
       <c r="V66" s="18" t="n">
-        <v>-109.42</v>
+        <v>94.84999999999999</v>
       </c>
       <c r="W66" s="37" t="n">
-        <v>-35.05</v>
+        <v>226.5</v>
       </c>
       <c r="X66" s="18" t="n">
-        <v>0</v>
+        <v>88.63</v>
       </c>
       <c r="Y66" s="19" t="n">
-        <v>-1198.64</v>
+        <v>30.2</v>
       </c>
       <c r="Z66" s="10" t="n"/>
       <c r="AA66" s="10" t="n"/>
@@ -13157,49 +13161,49 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>당기순이익</t>
+          <t>법인세비용차감전계속사업이익</t>
         </is>
       </c>
       <c r="H67" s="9" t="n"/>
       <c r="L67" s="18" t="n">
-        <v>-1145.81</v>
+        <v>-1688.54</v>
       </c>
       <c r="M67" s="9" t="n"/>
       <c r="N67" s="18" t="n">
         <v>-637.14</v>
       </c>
       <c r="O67" s="18" t="n">
-        <v>896.2</v>
+        <v>1029.24</v>
       </c>
       <c r="P67" s="18" t="n">
         <v>704.83</v>
       </c>
       <c r="Q67" s="18" t="n">
-        <v>-338.8</v>
+        <v>-817.7</v>
       </c>
       <c r="R67" s="37" t="n">
-        <v>625.09</v>
+        <v>279.23</v>
       </c>
       <c r="S67" s="18" t="n">
         <v>-72.73</v>
       </c>
       <c r="T67" s="18" t="n">
-        <v>-466.82</v>
+        <v>-392.45</v>
       </c>
       <c r="U67" s="18" t="n">
         <v>229.36</v>
       </c>
       <c r="V67" s="18" t="n">
-        <v>1492.27</v>
+        <v>1382.85</v>
       </c>
       <c r="W67" s="37" t="n">
-        <v>1182.08</v>
+        <v>1147.03</v>
       </c>
       <c r="X67" s="18" t="n">
         <v>-1669.15</v>
       </c>
       <c r="Y67" s="19" t="n">
-        <v>-3988.11</v>
+        <v>-5186.75</v>
       </c>
       <c r="Z67" s="10" t="n"/>
       <c r="AA67" s="10" t="n"/>
@@ -13221,49 +13225,49 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>총포괄손익</t>
+          <t>법인세비용</t>
         </is>
       </c>
       <c r="H68" s="9" t="n"/>
       <c r="L68" s="18" t="n">
-        <v>-1188.63</v>
+        <v>-542.73</v>
       </c>
       <c r="M68" s="9" t="n"/>
       <c r="N68" s="18" t="n">
-        <v>-637.14</v>
+        <v>0</v>
       </c>
       <c r="O68" s="18" t="n">
-        <v>896.2</v>
+        <v>133.04</v>
       </c>
       <c r="P68" s="18" t="n">
-        <v>704.83</v>
+        <v>0</v>
       </c>
       <c r="Q68" s="18" t="n">
-        <v>58967.13</v>
+        <v>-478.9</v>
       </c>
       <c r="R68" s="37" t="n">
-        <v>59931.02</v>
+        <v>-345.86</v>
       </c>
       <c r="S68" s="18" t="n">
-        <v>-72.73</v>
+        <v>0</v>
       </c>
       <c r="T68" s="18" t="n">
-        <v>-466.82</v>
+        <v>74.37</v>
       </c>
       <c r="U68" s="18" t="n">
-        <v>229.36</v>
+        <v>0</v>
       </c>
       <c r="V68" s="18" t="n">
-        <v>-2864.07</v>
+        <v>-109.42</v>
       </c>
       <c r="W68" s="37" t="n">
-        <v>-3174.26</v>
+        <v>-35.05</v>
       </c>
       <c r="X68" s="18" t="n">
-        <v>-1669.15</v>
+        <v>0</v>
       </c>
       <c r="Y68" s="19" t="n">
-        <v>-3988.11</v>
+        <v>-1198.64</v>
       </c>
       <c r="Z68" s="10" t="n"/>
       <c r="AA68" s="10" t="n"/>
@@ -13285,49 +13289,49 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>(지배주주지분)당기순이익</t>
+          <t>당기순이익</t>
         </is>
       </c>
       <c r="H69" s="9" t="n"/>
       <c r="L69" s="18" t="n">
-        <v>-1090.6</v>
+        <v>-1145.81</v>
       </c>
       <c r="M69" s="9" t="n"/>
       <c r="N69" s="18" t="n">
-        <v>-596.77</v>
+        <v>-637.14</v>
       </c>
       <c r="O69" s="18" t="n">
-        <v>911.4299999999999</v>
+        <v>896.2</v>
       </c>
       <c r="P69" s="18" t="n">
-        <v>775.21</v>
+        <v>704.83</v>
       </c>
       <c r="Q69" s="18" t="n">
-        <v>-255.33</v>
+        <v>-338.8</v>
       </c>
       <c r="R69" s="37" t="n">
-        <v>834.54</v>
+        <v>625.09</v>
       </c>
       <c r="S69" s="18" t="n">
-        <v>4.84</v>
+        <v>-72.73</v>
       </c>
       <c r="T69" s="18" t="n">
-        <v>-377.74</v>
+        <v>-466.82</v>
       </c>
       <c r="U69" s="18" t="n">
-        <v>336.55</v>
+        <v>229.36</v>
       </c>
       <c r="V69" s="18" t="n">
-        <v>1626.51</v>
+        <v>1492.27</v>
       </c>
       <c r="W69" s="37" t="n">
-        <v>1590.16</v>
+        <v>1182.08</v>
       </c>
       <c r="X69" s="18" t="n">
-        <v>-1645.99</v>
+        <v>-1669.15</v>
       </c>
       <c r="Y69" s="19" t="n">
-        <v>-3786.59</v>
+        <v>-3988.11</v>
       </c>
       <c r="Z69" s="10" t="n"/>
       <c r="AA69" s="10" t="n"/>
@@ -13349,49 +13353,49 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>(비지배주주지분)당기순이익</t>
+          <t>총포괄손익</t>
         </is>
       </c>
       <c r="H70" s="9" t="n"/>
       <c r="L70" s="18" t="n">
-        <v>-55.21</v>
+        <v>-1188.63</v>
       </c>
       <c r="M70" s="9" t="n"/>
       <c r="N70" s="18" t="n">
-        <v>-40.38</v>
+        <v>-637.14</v>
       </c>
       <c r="O70" s="18" t="n">
-        <v>-15.23</v>
+        <v>896.2</v>
       </c>
       <c r="P70" s="18" t="n">
-        <v>-70.38</v>
+        <v>704.83</v>
       </c>
       <c r="Q70" s="18" t="n">
-        <v>-83.47</v>
+        <v>58967.13</v>
       </c>
       <c r="R70" s="37" t="n">
-        <v>-209.46</v>
+        <v>59931.02</v>
       </c>
       <c r="S70" s="18" t="n">
-        <v>-77.56999999999999</v>
+        <v>-72.73</v>
       </c>
       <c r="T70" s="18" t="n">
-        <v>-89.08</v>
+        <v>-466.82</v>
       </c>
       <c r="U70" s="18" t="n">
-        <v>-107.19</v>
+        <v>229.36</v>
       </c>
       <c r="V70" s="18" t="n">
-        <v>-134.24</v>
+        <v>-2864.07</v>
       </c>
       <c r="W70" s="37" t="n">
-        <v>-408.08</v>
+        <v>-3174.26</v>
       </c>
       <c r="X70" s="18" t="n">
-        <v>-23.16</v>
+        <v>-1669.15</v>
       </c>
       <c r="Y70" s="19" t="n">
-        <v>-201.52</v>
+        <v>-3988.11</v>
       </c>
       <c r="Z70" s="10" t="n"/>
       <c r="AA70" s="10" t="n"/>
@@ -13413,49 +13417,49 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>금융손익</t>
+          <t>(지배주주지분)당기순이익</t>
         </is>
       </c>
       <c r="H71" s="9" t="n"/>
       <c r="L71" s="18" t="n">
-        <v>413.53</v>
+        <v>-1090.6</v>
       </c>
       <c r="M71" s="9" t="n"/>
       <c r="N71" s="18" t="n">
-        <v>-18.05</v>
+        <v>-596.77</v>
       </c>
       <c r="O71" s="18" t="n">
-        <v>-634.8200000000001</v>
+        <v>911.4299999999999</v>
       </c>
       <c r="P71" s="18" t="n">
-        <v>-630.62</v>
+        <v>775.21</v>
       </c>
       <c r="Q71" s="18" t="n">
-        <v>-947.75</v>
+        <v>-255.33</v>
       </c>
       <c r="R71" s="37" t="n">
-        <v>-2231.24</v>
+        <v>834.54</v>
       </c>
       <c r="S71" s="18" t="n">
-        <v>-697.6900000000001</v>
+        <v>4.84</v>
       </c>
       <c r="T71" s="18" t="n">
-        <v>-589.42</v>
+        <v>-377.74</v>
       </c>
       <c r="U71" s="18" t="n">
-        <v>-584.27</v>
+        <v>336.55</v>
       </c>
       <c r="V71" s="18" t="n">
-        <v>2276.02</v>
+        <v>1626.51</v>
       </c>
       <c r="W71" s="37" t="n">
-        <v>404.64</v>
+        <v>1590.16</v>
       </c>
       <c r="X71" s="18" t="n">
-        <v>-1046.45</v>
+        <v>-1645.99</v>
       </c>
       <c r="Y71" s="19" t="n">
-        <v>-779.23</v>
+        <v>-3786.59</v>
       </c>
       <c r="Z71" s="10" t="n"/>
       <c r="AA71" s="10" t="n"/>
@@ -13477,49 +13481,49 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>기타영업외손익</t>
+          <t>(비지배주주지분)당기순이익</t>
         </is>
       </c>
       <c r="H72" s="9" t="n"/>
       <c r="L72" s="18" t="n">
-        <v>-55.6</v>
+        <v>-55.21</v>
       </c>
       <c r="M72" s="9" t="n"/>
       <c r="N72" s="18" t="n">
-        <v>16.34</v>
+        <v>-40.38</v>
       </c>
       <c r="O72" s="18" t="n">
-        <v>13.88</v>
+        <v>-15.23</v>
       </c>
       <c r="P72" s="18" t="n">
-        <v>-2.91</v>
+        <v>-70.38</v>
       </c>
       <c r="Q72" s="18" t="n">
-        <v>72.02</v>
+        <v>-83.47</v>
       </c>
       <c r="R72" s="37" t="n">
-        <v>99.33</v>
+        <v>-209.46</v>
       </c>
       <c r="S72" s="18" t="n">
-        <v>-55.32</v>
+        <v>-77.56999999999999</v>
       </c>
       <c r="T72" s="18" t="n">
-        <v>40.55</v>
+        <v>-89.08</v>
       </c>
       <c r="U72" s="18" t="n">
-        <v>-28.31</v>
+        <v>-107.19</v>
       </c>
       <c r="V72" s="18" t="n">
-        <v>-72.39</v>
+        <v>-134.24</v>
       </c>
       <c r="W72" s="37" t="n">
-        <v>-115.47</v>
+        <v>-408.08</v>
       </c>
       <c r="X72" s="18" t="n">
-        <v>1522.42</v>
+        <v>-23.16</v>
       </c>
       <c r="Y72" s="19" t="n">
-        <v>-1174.26</v>
+        <v>-201.52</v>
       </c>
       <c r="Z72" s="10" t="n"/>
       <c r="AA72" s="10" t="n"/>
@@ -13541,49 +13545,49 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>계속사업이익</t>
+          <t>금융손익</t>
         </is>
       </c>
       <c r="H73" s="9" t="n"/>
       <c r="L73" s="18" t="n">
-        <v>-1145.81</v>
+        <v>413.53</v>
       </c>
       <c r="M73" s="9" t="n"/>
       <c r="N73" s="18" t="n">
-        <v>-637.14</v>
+        <v>-18.05</v>
       </c>
       <c r="O73" s="18" t="n">
-        <v>896.2</v>
+        <v>-634.8200000000001</v>
       </c>
       <c r="P73" s="18" t="n">
-        <v>704.83</v>
+        <v>-630.62</v>
       </c>
       <c r="Q73" s="18" t="n">
-        <v>-338.8</v>
+        <v>-947.75</v>
       </c>
       <c r="R73" s="37" t="n">
-        <v>625.09</v>
+        <v>-2231.24</v>
       </c>
       <c r="S73" s="18" t="n">
-        <v>-72.73</v>
+        <v>-697.6900000000001</v>
       </c>
       <c r="T73" s="18" t="n">
-        <v>-466.82</v>
+        <v>-589.42</v>
       </c>
       <c r="U73" s="18" t="n">
-        <v>229.36</v>
+        <v>-584.27</v>
       </c>
       <c r="V73" s="18" t="n">
-        <v>1492.27</v>
+        <v>2276.02</v>
       </c>
       <c r="W73" s="37" t="n">
-        <v>1182.08</v>
+        <v>404.64</v>
       </c>
       <c r="X73" s="18" t="n">
-        <v>-1669.15</v>
+        <v>-1046.45</v>
       </c>
       <c r="Y73" s="19" t="n">
-        <v>-3988.11</v>
+        <v>-779.23</v>
       </c>
       <c r="Z73" s="10" t="n"/>
       <c r="AA73" s="10" t="n"/>
@@ -13605,34 +13609,50 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>이자수익</t>
+          <t>기타영업외손익</t>
         </is>
       </c>
       <c r="H74" s="9" t="n"/>
       <c r="L74" s="18" t="n">
-        <v>513.77</v>
+        <v>-55.6</v>
       </c>
       <c r="M74" s="9" t="n"/>
       <c r="N74" s="18" t="n">
-        <v>362.6</v>
+        <v>16.34</v>
       </c>
       <c r="O74" s="18" t="n">
-        <v>333.56</v>
+        <v>13.88</v>
       </c>
       <c r="P74" s="18" t="n">
-        <v>353.3</v>
+        <v>-2.91</v>
       </c>
       <c r="Q74" s="18" t="n">
-        <v>389.74</v>
+        <v>72.02</v>
       </c>
       <c r="R74" s="37" t="n">
-        <v>1439.2</v>
+        <v>99.33</v>
       </c>
       <c r="S74" s="18" t="n">
-        <v>517.98</v>
-      </c>
-      <c r="W74" s="9" t="n"/>
-      <c r="Y74" s="5" t="n"/>
+        <v>-55.32</v>
+      </c>
+      <c r="T74" s="18" t="n">
+        <v>40.55</v>
+      </c>
+      <c r="U74" s="18" t="n">
+        <v>-28.31</v>
+      </c>
+      <c r="V74" s="18" t="n">
+        <v>-72.39</v>
+      </c>
+      <c r="W74" s="37" t="n">
+        <v>-115.47</v>
+      </c>
+      <c r="X74" s="18" t="n">
+        <v>1522.42</v>
+      </c>
+      <c r="Y74" s="19" t="n">
+        <v>-1174.26</v>
+      </c>
       <c r="Z74" s="10" t="n"/>
       <c r="AA74" s="10" t="n"/>
       <c r="AB74" s="11" t="n"/>
@@ -13653,34 +13673,50 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>이자비용</t>
+          <t>계속사업이익</t>
         </is>
       </c>
       <c r="H75" s="9" t="n"/>
       <c r="L75" s="18" t="n">
-        <v>100.24</v>
+        <v>-1145.81</v>
       </c>
       <c r="M75" s="9" t="n"/>
       <c r="N75" s="18" t="n">
-        <v>405.09</v>
+        <v>-637.14</v>
       </c>
       <c r="O75" s="18" t="n">
-        <v>968.38</v>
+        <v>896.2</v>
       </c>
       <c r="P75" s="18" t="n">
-        <v>983.92</v>
+        <v>704.83</v>
       </c>
       <c r="Q75" s="18" t="n">
-        <v>1176.78</v>
+        <v>-338.8</v>
       </c>
       <c r="R75" s="37" t="n">
-        <v>3534.17</v>
+        <v>625.09</v>
       </c>
       <c r="S75" s="18" t="n">
-        <v>1238.07</v>
-      </c>
-      <c r="W75" s="9" t="n"/>
-      <c r="Y75" s="5" t="n"/>
+        <v>-72.73</v>
+      </c>
+      <c r="T75" s="18" t="n">
+        <v>-466.82</v>
+      </c>
+      <c r="U75" s="18" t="n">
+        <v>229.36</v>
+      </c>
+      <c r="V75" s="18" t="n">
+        <v>1492.27</v>
+      </c>
+      <c r="W75" s="37" t="n">
+        <v>1182.08</v>
+      </c>
+      <c r="X75" s="18" t="n">
+        <v>-1669.15</v>
+      </c>
+      <c r="Y75" s="19" t="n">
+        <v>-3988.11</v>
+      </c>
       <c r="Z75" s="10" t="n"/>
       <c r="AA75" s="10" t="n"/>
       <c r="AB75" s="11" t="n"/>
@@ -13701,31 +13737,31 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>이자손익</t>
+          <t>이자수익</t>
         </is>
       </c>
       <c r="H76" s="9" t="n"/>
       <c r="L76" s="18" t="n">
-        <v>413.53</v>
+        <v>513.77</v>
       </c>
       <c r="M76" s="9" t="n"/>
       <c r="N76" s="18" t="n">
-        <v>-42.49</v>
+        <v>362.6</v>
       </c>
       <c r="O76" s="18" t="n">
-        <v>-634.8200000000001</v>
+        <v>333.56</v>
       </c>
       <c r="P76" s="18" t="n">
-        <v>-630.62</v>
+        <v>353.3</v>
       </c>
       <c r="Q76" s="18" t="n">
-        <v>-787.04</v>
+        <v>389.74</v>
       </c>
       <c r="R76" s="37" t="n">
-        <v>-2094.97</v>
+        <v>1439.2</v>
       </c>
       <c r="S76" s="18" t="n">
-        <v>-720.09</v>
+        <v>517.98</v>
       </c>
       <c r="W76" s="9" t="n"/>
       <c r="Y76" s="5" t="n"/>
@@ -13749,50 +13785,34 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>영업활동으로인한현금흐름</t>
+          <t>이자비용</t>
         </is>
       </c>
       <c r="H77" s="9" t="n"/>
       <c r="L77" s="18" t="n">
-        <v>3190.35</v>
+        <v>100.24</v>
       </c>
       <c r="M77" s="9" t="n"/>
       <c r="N77" s="18" t="n">
-        <v>-5439.91</v>
+        <v>405.09</v>
       </c>
       <c r="O77" s="18" t="n">
-        <v>18754.8</v>
+        <v>968.38</v>
       </c>
       <c r="P77" s="18" t="n">
-        <v>-7021.01</v>
+        <v>983.92</v>
       </c>
       <c r="Q77" s="18" t="n">
-        <v>2612.06</v>
+        <v>1176.78</v>
       </c>
       <c r="R77" s="37" t="n">
-        <v>8905.940000000001</v>
+        <v>3534.17</v>
       </c>
       <c r="S77" s="18" t="n">
-        <v>1393.17</v>
-      </c>
-      <c r="T77" s="18" t="n">
-        <v>367.76</v>
-      </c>
-      <c r="U77" s="18" t="n">
-        <v>-1381.07</v>
-      </c>
-      <c r="V77" s="18" t="n">
-        <v>21303.26</v>
-      </c>
-      <c r="W77" s="37" t="n">
-        <v>21683.12</v>
-      </c>
-      <c r="X77" s="18" t="n">
-        <v>-15326.48</v>
-      </c>
-      <c r="Y77" s="19" t="n">
-        <v>-4061.11</v>
-      </c>
+        <v>1238.07</v>
+      </c>
+      <c r="W77" s="9" t="n"/>
+      <c r="Y77" s="5" t="n"/>
       <c r="Z77" s="10" t="n"/>
       <c r="AA77" s="10" t="n"/>
       <c r="AB77" s="11" t="n"/>
@@ -13813,50 +13833,34 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>감가상각비</t>
+          <t>이자손익</t>
         </is>
       </c>
       <c r="H78" s="9" t="n"/>
       <c r="L78" s="18" t="n">
-        <v>340.45</v>
+        <v>413.53</v>
       </c>
       <c r="M78" s="9" t="n"/>
       <c r="N78" s="18" t="n">
-        <v>405.32</v>
+        <v>-42.49</v>
       </c>
       <c r="O78" s="18" t="n">
-        <v>446.48</v>
+        <v>-634.8200000000001</v>
       </c>
       <c r="P78" s="18" t="n">
-        <v>444.16</v>
+        <v>-630.62</v>
       </c>
       <c r="Q78" s="18" t="n">
-        <v>437.22</v>
+        <v>-787.04</v>
       </c>
       <c r="R78" s="37" t="n">
-        <v>1733.18</v>
+        <v>-2094.97</v>
       </c>
       <c r="S78" s="18" t="n">
-        <v>441.4</v>
-      </c>
-      <c r="T78" s="18" t="n">
-        <v>460.01</v>
-      </c>
-      <c r="U78" s="18" t="n">
-        <v>481.48</v>
-      </c>
-      <c r="V78" s="18" t="n">
-        <v>515.9400000000001</v>
-      </c>
-      <c r="W78" s="37" t="n">
-        <v>1898.83</v>
-      </c>
-      <c r="X78" s="18" t="n">
-        <v>515.92</v>
-      </c>
-      <c r="Y78" s="19" t="n">
-        <v>537.61</v>
-      </c>
+        <v>-720.09</v>
+      </c>
+      <c r="W78" s="9" t="n"/>
+      <c r="Y78" s="5" t="n"/>
       <c r="Z78" s="10" t="n"/>
       <c r="AA78" s="10" t="n"/>
       <c r="AB78" s="11" t="n"/>
@@ -13877,49 +13881,49 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>무형자산상각비</t>
+          <t>영업활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="H79" s="9" t="n"/>
       <c r="L79" s="18" t="n">
-        <v>66.12</v>
+        <v>3190.35</v>
       </c>
       <c r="M79" s="9" t="n"/>
       <c r="N79" s="18" t="n">
-        <v>66.39</v>
+        <v>-5439.91</v>
       </c>
       <c r="O79" s="18" t="n">
-        <v>68.03</v>
+        <v>18754.8</v>
       </c>
       <c r="P79" s="18" t="n">
-        <v>111.05</v>
+        <v>-7021.01</v>
       </c>
       <c r="Q79" s="18" t="n">
-        <v>225.38</v>
+        <v>2612.06</v>
       </c>
       <c r="R79" s="37" t="n">
-        <v>470.85</v>
+        <v>8905.940000000001</v>
       </c>
       <c r="S79" s="18" t="n">
-        <v>189.29</v>
+        <v>1393.17</v>
       </c>
       <c r="T79" s="18" t="n">
-        <v>179.99</v>
+        <v>367.76</v>
       </c>
       <c r="U79" s="18" t="n">
-        <v>170.78</v>
+        <v>-1381.07</v>
       </c>
       <c r="V79" s="18" t="n">
-        <v>170.03</v>
+        <v>21303.26</v>
       </c>
       <c r="W79" s="37" t="n">
-        <v>710.09</v>
+        <v>21683.12</v>
       </c>
       <c r="X79" s="18" t="n">
-        <v>170.03</v>
+        <v>-15326.48</v>
       </c>
       <c r="Y79" s="19" t="n">
-        <v>169.37</v>
+        <v>-4061.11</v>
       </c>
       <c r="Z79" s="10" t="n"/>
       <c r="AA79" s="10" t="n"/>
@@ -13941,49 +13945,49 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>이자수취(CF)</t>
+          <t>감가상각비</t>
         </is>
       </c>
       <c r="H80" s="9" t="n"/>
       <c r="L80" s="18" t="n">
-        <v>299.44</v>
+        <v>340.45</v>
       </c>
       <c r="M80" s="9" t="n"/>
       <c r="N80" s="18" t="n">
-        <v>271</v>
+        <v>405.32</v>
       </c>
       <c r="O80" s="18" t="n">
-        <v>396</v>
+        <v>446.48</v>
       </c>
       <c r="P80" s="18" t="n">
-        <v>362.39</v>
+        <v>444.16</v>
       </c>
       <c r="Q80" s="18" t="n">
-        <v>172.35</v>
+        <v>437.22</v>
       </c>
       <c r="R80" s="37" t="n">
-        <v>1201.74</v>
+        <v>1733.18</v>
       </c>
       <c r="S80" s="18" t="n">
-        <v>165.34</v>
+        <v>441.4</v>
       </c>
       <c r="T80" s="18" t="n">
-        <v>508.18</v>
+        <v>460.01</v>
       </c>
       <c r="U80" s="18" t="n">
-        <v>279.27</v>
+        <v>481.48</v>
       </c>
       <c r="V80" s="18" t="n">
-        <v>879.38</v>
+        <v>515.9400000000001</v>
       </c>
       <c r="W80" s="37" t="n">
-        <v>1832.17</v>
+        <v>1898.83</v>
       </c>
       <c r="X80" s="18" t="n">
-        <v>69.93000000000001</v>
+        <v>515.92</v>
       </c>
       <c r="Y80" s="19" t="n">
-        <v>778.64</v>
+        <v>537.61</v>
       </c>
       <c r="Z80" s="10" t="n"/>
       <c r="AA80" s="10" t="n"/>
@@ -14005,49 +14009,49 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>이자지급(CF)</t>
+          <t>무형자산상각비</t>
         </is>
       </c>
       <c r="H81" s="9" t="n"/>
       <c r="L81" s="18" t="n">
-        <v>-131.95</v>
+        <v>66.12</v>
       </c>
       <c r="M81" s="9" t="n"/>
       <c r="N81" s="18" t="n">
-        <v>-374.72</v>
+        <v>66.39</v>
       </c>
       <c r="O81" s="18" t="n">
-        <v>-980.23</v>
+        <v>68.03</v>
       </c>
       <c r="P81" s="18" t="n">
-        <v>-991.25</v>
+        <v>111.05</v>
       </c>
       <c r="Q81" s="18" t="n">
-        <v>-1004.01</v>
+        <v>225.38</v>
       </c>
       <c r="R81" s="37" t="n">
-        <v>-3350.21</v>
+        <v>470.85</v>
       </c>
       <c r="S81" s="18" t="n">
-        <v>-1013.81</v>
+        <v>189.29</v>
       </c>
       <c r="T81" s="18" t="n">
-        <v>-945.74</v>
+        <v>179.99</v>
       </c>
       <c r="U81" s="18" t="n">
-        <v>-870.3200000000001</v>
+        <v>170.78</v>
       </c>
       <c r="V81" s="18" t="n">
-        <v>-877.87</v>
+        <v>170.03</v>
       </c>
       <c r="W81" s="37" t="n">
-        <v>-3707.74</v>
+        <v>710.09</v>
       </c>
       <c r="X81" s="18" t="n">
-        <v>-939.9400000000001</v>
+        <v>170.03</v>
       </c>
       <c r="Y81" s="19" t="n">
-        <v>-952.52</v>
+        <v>169.37</v>
       </c>
       <c r="Z81" s="10" t="n"/>
       <c r="AA81" s="10" t="n"/>
@@ -14069,49 +14073,49 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>법인세납부(CF)</t>
+          <t>이자수취(CF)</t>
         </is>
       </c>
       <c r="H82" s="9" t="n"/>
       <c r="L82" s="18" t="n">
-        <v>-56.89</v>
+        <v>299.44</v>
       </c>
       <c r="M82" s="9" t="n"/>
       <c r="N82" s="18" t="n">
-        <v>-41.59</v>
+        <v>271</v>
       </c>
       <c r="O82" s="18" t="n">
-        <v>383.95</v>
+        <v>396</v>
       </c>
       <c r="P82" s="18" t="n">
-        <v>-56.61</v>
+        <v>362.39</v>
       </c>
       <c r="Q82" s="18" t="n">
-        <v>-21.3</v>
+        <v>172.35</v>
       </c>
       <c r="R82" s="37" t="n">
-        <v>264.45</v>
+        <v>1201.74</v>
       </c>
       <c r="S82" s="18" t="n">
-        <v>-28.43</v>
+        <v>165.34</v>
       </c>
       <c r="T82" s="18" t="n">
-        <v>92.64</v>
+        <v>508.18</v>
       </c>
       <c r="U82" s="18" t="n">
-        <v>-74.31</v>
+        <v>279.27</v>
       </c>
       <c r="V82" s="18" t="n">
-        <v>-101.96</v>
+        <v>879.38</v>
       </c>
       <c r="W82" s="37" t="n">
-        <v>-112.06</v>
+        <v>1832.17</v>
       </c>
       <c r="X82" s="18" t="n">
-        <v>-10.45</v>
+        <v>69.93000000000001</v>
       </c>
       <c r="Y82" s="19" t="n">
-        <v>87.59</v>
+        <v>778.64</v>
       </c>
       <c r="Z82" s="10" t="n"/>
       <c r="AA82" s="10" t="n"/>
@@ -14133,49 +14137,49 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>투자활동으로인한현금흐름</t>
+          <t>이자지급(CF)</t>
         </is>
       </c>
       <c r="H83" s="9" t="n"/>
       <c r="L83" s="18" t="n">
-        <v>-12024.34</v>
+        <v>-131.95</v>
       </c>
       <c r="M83" s="9" t="n"/>
       <c r="N83" s="18" t="n">
-        <v>-106453.41</v>
+        <v>-374.72</v>
       </c>
       <c r="O83" s="18" t="n">
-        <v>5413.59</v>
+        <v>-980.23</v>
       </c>
       <c r="P83" s="18" t="n">
-        <v>-2679.26</v>
+        <v>-991.25</v>
       </c>
       <c r="Q83" s="18" t="n">
-        <v>-18052.02</v>
+        <v>-1004.01</v>
       </c>
       <c r="R83" s="37" t="n">
-        <v>-121771.1</v>
+        <v>-3350.21</v>
       </c>
       <c r="S83" s="18" t="n">
-        <v>2915.55</v>
+        <v>-1013.81</v>
       </c>
       <c r="T83" s="18" t="n">
-        <v>-11999.52</v>
+        <v>-945.74</v>
       </c>
       <c r="U83" s="18" t="n">
-        <v>-4089.06</v>
+        <v>-870.3200000000001</v>
       </c>
       <c r="V83" s="18" t="n">
-        <v>217.08</v>
+        <v>-877.87</v>
       </c>
       <c r="W83" s="37" t="n">
-        <v>-12955.95</v>
+        <v>-3707.74</v>
       </c>
       <c r="X83" s="18" t="n">
-        <v>-12980.04</v>
+        <v>-939.9400000000001</v>
       </c>
       <c r="Y83" s="19" t="n">
-        <v>3592.94</v>
+        <v>-952.52</v>
       </c>
       <c r="Z83" s="10" t="n"/>
       <c r="AA83" s="10" t="n"/>
@@ -14197,49 +14201,49 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>재무활동으로인한현금흐름</t>
+          <t>법인세납부(CF)</t>
         </is>
       </c>
       <c r="H84" s="9" t="n"/>
       <c r="L84" s="18" t="n">
-        <v>-53.46</v>
+        <v>-56.89</v>
       </c>
       <c r="M84" s="9" t="n"/>
       <c r="N84" s="18" t="n">
-        <v>87959.69</v>
+        <v>-41.59</v>
       </c>
       <c r="O84" s="18" t="n">
-        <v>-40.86</v>
+        <v>383.95</v>
       </c>
       <c r="P84" s="18" t="n">
-        <v>-33.92</v>
+        <v>-56.61</v>
       </c>
       <c r="Q84" s="18" t="n">
-        <v>17843.86</v>
+        <v>-21.3</v>
       </c>
       <c r="R84" s="37" t="n">
-        <v>105728.77</v>
+        <v>264.45</v>
       </c>
       <c r="S84" s="18" t="n">
-        <v>1978.09</v>
+        <v>-28.43</v>
       </c>
       <c r="T84" s="18" t="n">
-        <v>-522.9299999999999</v>
+        <v>92.64</v>
       </c>
       <c r="U84" s="18" t="n">
-        <v>-277.65</v>
+        <v>-74.31</v>
       </c>
       <c r="V84" s="18" t="n">
-        <v>16436.37</v>
+        <v>-101.96</v>
       </c>
       <c r="W84" s="37" t="n">
-        <v>17613.88</v>
+        <v>-112.06</v>
       </c>
       <c r="X84" s="18" t="n">
-        <v>3231.89</v>
+        <v>-10.45</v>
       </c>
       <c r="Y84" s="19" t="n">
-        <v>-793.08</v>
+        <v>87.59</v>
       </c>
       <c r="Z84" s="10" t="n"/>
       <c r="AA84" s="10" t="n"/>
@@ -14261,41 +14265,49 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>단기차입금의증가</t>
+          <t>투자활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="H85" s="9" t="n"/>
       <c r="L85" s="18" t="n">
-        <v>0</v>
+        <v>-12024.34</v>
       </c>
       <c r="M85" s="9" t="n"/>
+      <c r="N85" s="18" t="n">
+        <v>-106453.41</v>
+      </c>
+      <c r="O85" s="18" t="n">
+        <v>5413.59</v>
+      </c>
       <c r="P85" s="18" t="n">
-        <v>0</v>
+        <v>-2679.26</v>
       </c>
       <c r="Q85" s="18" t="n">
-        <v>5000</v>
-      </c>
-      <c r="R85" s="9" t="n"/>
+        <v>-18052.02</v>
+      </c>
+      <c r="R85" s="37" t="n">
+        <v>-121771.1</v>
+      </c>
       <c r="S85" s="18" t="n">
-        <v>5000</v>
+        <v>2915.55</v>
       </c>
       <c r="T85" s="18" t="n">
-        <v>0</v>
+        <v>-11999.52</v>
       </c>
       <c r="U85" s="18" t="n">
-        <v>0</v>
+        <v>-4089.06</v>
       </c>
       <c r="V85" s="18" t="n">
-        <v>10000</v>
+        <v>217.08</v>
       </c>
       <c r="W85" s="37" t="n">
-        <v>15000</v>
+        <v>-12955.95</v>
       </c>
       <c r="X85" s="18" t="n">
-        <v>0</v>
+        <v>-12980.04</v>
       </c>
       <c r="Y85" s="19" t="n">
-        <v>0</v>
+        <v>3592.94</v>
       </c>
       <c r="Z85" s="10" t="n"/>
       <c r="AA85" s="10" t="n"/>
@@ -14317,45 +14329,50 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>장기차입금의증가</t>
+          <t>재무활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="H86" s="9" t="n"/>
       <c r="L86" s="18" t="n">
-        <v>0</v>
+        <v>-53.46</v>
       </c>
       <c r="M86" s="9" t="n"/>
       <c r="N86" s="18" t="n">
-        <v>88000</v>
+        <v>87959.69</v>
       </c>
       <c r="O86" s="18" t="n">
-        <v>0</v>
+        <v>-40.86</v>
       </c>
       <c r="P86" s="18" t="n">
-        <v>0</v>
+        <v>-33.92</v>
       </c>
       <c r="Q86" s="18" t="n">
-        <v>0</v>
+        <v>17843.86</v>
       </c>
       <c r="R86" s="37" t="n">
-        <v>88000</v>
+        <v>105728.77</v>
       </c>
       <c r="S86" s="18" t="n">
-        <v>0</v>
+        <v>1978.09</v>
       </c>
       <c r="T86" s="18" t="n">
-        <v>0</v>
+        <v>-522.9299999999999</v>
       </c>
       <c r="U86" s="18" t="n">
-        <v>0</v>
+        <v>-277.65</v>
       </c>
       <c r="V86" s="18" t="n">
-        <v>0</v>
+        <v>16436.37</v>
       </c>
       <c r="W86" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y86" s="5" t="n"/>
+        <v>17613.88</v>
+      </c>
+      <c r="X86" s="18" t="n">
+        <v>3231.89</v>
+      </c>
+      <c r="Y86" s="19" t="n">
+        <v>-793.08</v>
+      </c>
       <c r="Z86" s="10" t="n"/>
       <c r="AA86" s="10" t="n"/>
       <c r="AB86" s="11" t="n"/>
@@ -14376,7 +14393,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>단기차입금의감소</t>
+          <t>단기차입금의증가</t>
         </is>
       </c>
       <c r="H87" s="9" t="n"/>
@@ -14388,29 +14405,29 @@
         <v>0</v>
       </c>
       <c r="Q87" s="18" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="R87" s="9" t="n"/>
       <c r="S87" s="18" t="n">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="T87" s="18" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="U87" s="18" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="V87" s="18" t="n">
-        <v>250</v>
+        <v>10000</v>
       </c>
       <c r="W87" s="37" t="n">
-        <v>3000</v>
+        <v>15000</v>
       </c>
       <c r="X87" s="18" t="n">
-        <v>3750</v>
+        <v>0</v>
       </c>
       <c r="Y87" s="19" t="n">
-        <v>750</v>
+        <v>0</v>
       </c>
       <c r="Z87" s="10" t="n"/>
       <c r="AA87" s="10" t="n"/>
@@ -14432,7 +14449,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>장기차입금의감소</t>
+          <t>장기차입금의증가</t>
         </is>
       </c>
       <c r="H88" s="9" t="n"/>
@@ -14440,11 +14457,36 @@
         <v>0</v>
       </c>
       <c r="M88" s="9" t="n"/>
+      <c r="N88" s="18" t="n">
+        <v>88000</v>
+      </c>
+      <c r="O88" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P88" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="Q88" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="R88" s="9" t="n"/>
-      <c r="W88" s="9" t="n"/>
+      <c r="R88" s="37" t="n">
+        <v>88000</v>
+      </c>
+      <c r="S88" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T88" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U88" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V88" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W88" s="37" t="n">
+        <v>0</v>
+      </c>
       <c r="Y88" s="5" t="n"/>
       <c r="Z88" s="10" t="n"/>
       <c r="AA88" s="10" t="n"/>
@@ -14466,7 +14508,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>유동성장기부채의감소</t>
+          <t>단기차입금의감소</t>
         </is>
       </c>
       <c r="H89" s="9" t="n"/>
@@ -14482,25 +14524,25 @@
       </c>
       <c r="R89" s="9" t="n"/>
       <c r="S89" s="18" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="T89" s="18" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="U89" s="18" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="V89" s="18" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="W89" s="37" t="n">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="X89" s="18" t="n">
-        <v>0</v>
+        <v>3750</v>
       </c>
       <c r="Y89" s="19" t="n">
-        <v>0</v>
+        <v>750</v>
       </c>
       <c r="Z89" s="10" t="n"/>
       <c r="AA89" s="10" t="n"/>
@@ -14522,50 +14564,20 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>리스부채의상환</t>
+          <t>장기차입금의감소</t>
         </is>
       </c>
       <c r="H90" s="9" t="n"/>
       <c r="L90" s="18" t="n">
-        <v>7.71</v>
+        <v>0</v>
       </c>
       <c r="M90" s="9" t="n"/>
-      <c r="N90" s="18" t="n">
-        <v>40.31</v>
-      </c>
-      <c r="O90" s="18" t="n">
-        <v>40.86</v>
-      </c>
-      <c r="P90" s="18" t="n">
-        <v>33.92</v>
-      </c>
       <c r="Q90" s="18" t="n">
-        <v>23.09</v>
-      </c>
-      <c r="R90" s="37" t="n">
-        <v>138.18</v>
-      </c>
-      <c r="S90" s="18" t="n">
-        <v>21.91</v>
-      </c>
-      <c r="T90" s="18" t="n">
-        <v>22.93</v>
-      </c>
-      <c r="U90" s="18" t="n">
-        <v>27.65</v>
-      </c>
-      <c r="V90" s="18" t="n">
-        <v>47.85</v>
-      </c>
-      <c r="W90" s="37" t="n">
-        <v>120.34</v>
-      </c>
-      <c r="X90" s="18" t="n">
-        <v>43.27</v>
-      </c>
-      <c r="Y90" s="19" t="n">
-        <v>43.08</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R90" s="9" t="n"/>
+      <c r="W90" s="9" t="n"/>
+      <c r="Y90" s="5" t="n"/>
       <c r="Z90" s="10" t="n"/>
       <c r="AA90" s="10" t="n"/>
       <c r="AB90" s="11" t="n"/>
@@ -14586,48 +14598,42 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>현금및현금성자산의증감</t>
+          <t>유동성장기부채의감소</t>
         </is>
       </c>
       <c r="H91" s="9" t="n"/>
       <c r="L91" s="18" t="n">
-        <v>-8904.18</v>
+        <v>0</v>
       </c>
       <c r="M91" s="9" t="n"/>
-      <c r="N91" s="18" t="n">
-        <v>-23914.98</v>
-      </c>
-      <c r="O91" s="18" t="n">
-        <v>24111.38</v>
-      </c>
       <c r="P91" s="18" t="n">
-        <v>-9736.690000000001</v>
+        <v>0</v>
       </c>
       <c r="Q91" s="18" t="n">
-        <v>2404.72</v>
-      </c>
-      <c r="R91" s="37" t="n">
-        <v>-7135.57</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R91" s="9" t="n"/>
       <c r="S91" s="18" t="n">
-        <v>6289.14</v>
+        <v>1000</v>
       </c>
       <c r="T91" s="18" t="n">
-        <v>-12154.55</v>
+        <v>0</v>
       </c>
       <c r="U91" s="18" t="n">
-        <v>-5745.7</v>
+        <v>0</v>
       </c>
       <c r="V91" s="18" t="n">
-        <v>37952.16</v>
+        <v>0</v>
       </c>
       <c r="W91" s="37" t="n">
-        <v>26341.05</v>
+        <v>1000</v>
       </c>
       <c r="X91" s="18" t="n">
-        <v>-25074.62</v>
-      </c>
-      <c r="Y91" s="5" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="Y91" s="19" t="n">
+        <v>0</v>
+      </c>
       <c r="Z91" s="10" t="n"/>
       <c r="AA91" s="10" t="n"/>
       <c r="AB91" s="11" t="n"/>
@@ -14648,49 +14654,49 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>기말현금및현금성자산</t>
+          <t>리스부채의상환</t>
         </is>
       </c>
       <c r="H92" s="9" t="n"/>
       <c r="L92" s="18" t="n">
-        <v>-8904.18</v>
+        <v>7.71</v>
       </c>
       <c r="M92" s="9" t="n"/>
       <c r="N92" s="18" t="n">
-        <v>2817.92</v>
+        <v>40.31</v>
       </c>
       <c r="O92" s="18" t="n">
-        <v>24111.38</v>
+        <v>40.86</v>
       </c>
       <c r="P92" s="18" t="n">
-        <v>-9736.68</v>
+        <v>33.92</v>
       </c>
       <c r="Q92" s="18" t="n">
-        <v>2404.71</v>
+        <v>23.09</v>
       </c>
       <c r="R92" s="37" t="n">
-        <v>19597.33</v>
+        <v>138.18</v>
       </c>
       <c r="S92" s="18" t="n">
-        <v>25886.48</v>
+        <v>21.91</v>
       </c>
       <c r="T92" s="18" t="n">
-        <v>-12154.56</v>
+        <v>22.93</v>
       </c>
       <c r="U92" s="18" t="n">
-        <v>-5745.7</v>
+        <v>27.65</v>
       </c>
       <c r="V92" s="18" t="n">
-        <v>37867.75</v>
+        <v>47.85</v>
       </c>
       <c r="W92" s="37" t="n">
-        <v>45853.97</v>
+        <v>120.34</v>
       </c>
       <c r="X92" s="18" t="n">
-        <v>21114.54</v>
+        <v>43.27</v>
       </c>
       <c r="Y92" s="19" t="n">
-        <v>-1274.09</v>
+        <v>43.08</v>
       </c>
       <c r="Z92" s="10" t="n"/>
       <c r="AA92" s="10" t="n"/>
@@ -14712,19 +14718,47 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>배당금수취(CF)</t>
+          <t>현금및현금성자산의증감</t>
         </is>
       </c>
       <c r="H93" s="9" t="n"/>
+      <c r="L93" s="18" t="n">
+        <v>-8904.18</v>
+      </c>
       <c r="M93" s="9" t="n"/>
-      <c r="R93" s="9" t="n"/>
+      <c r="N93" s="18" t="n">
+        <v>-23914.98</v>
+      </c>
+      <c r="O93" s="18" t="n">
+        <v>24111.38</v>
+      </c>
+      <c r="P93" s="18" t="n">
+        <v>-9736.690000000001</v>
+      </c>
+      <c r="Q93" s="18" t="n">
+        <v>2404.72</v>
+      </c>
+      <c r="R93" s="37" t="n">
+        <v>-7135.57</v>
+      </c>
+      <c r="S93" s="18" t="n">
+        <v>6289.14</v>
+      </c>
+      <c r="T93" s="18" t="n">
+        <v>-12154.55</v>
+      </c>
       <c r="U93" s="18" t="n">
-        <v>0</v>
+        <v>-5745.7</v>
       </c>
       <c r="V93" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W93" s="9" t="n"/>
+        <v>37952.16</v>
+      </c>
+      <c r="W93" s="37" t="n">
+        <v>26341.05</v>
+      </c>
+      <c r="X93" s="18" t="n">
+        <v>-25074.62</v>
+      </c>
       <c r="Y93" s="5" t="n"/>
       <c r="Z93" s="10" t="n"/>
       <c r="AA93" s="10" t="n"/>
@@ -14740,6 +14774,104 @@
       <c r="AK93" s="10" t="n"/>
       <c r="AL93" s="11" t="n"/>
     </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>1</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>기말현금및현금성자산</t>
+        </is>
+      </c>
+      <c r="H94" s="9" t="n"/>
+      <c r="L94" s="18" t="n">
+        <v>-8904.18</v>
+      </c>
+      <c r="M94" s="9" t="n"/>
+      <c r="N94" s="18" t="n">
+        <v>2817.92</v>
+      </c>
+      <c r="O94" s="18" t="n">
+        <v>24111.38</v>
+      </c>
+      <c r="P94" s="18" t="n">
+        <v>-9736.68</v>
+      </c>
+      <c r="Q94" s="18" t="n">
+        <v>2404.71</v>
+      </c>
+      <c r="R94" s="37" t="n">
+        <v>19597.33</v>
+      </c>
+      <c r="S94" s="18" t="n">
+        <v>25886.48</v>
+      </c>
+      <c r="T94" s="18" t="n">
+        <v>-12154.56</v>
+      </c>
+      <c r="U94" s="18" t="n">
+        <v>-5745.7</v>
+      </c>
+      <c r="V94" s="18" t="n">
+        <v>37867.75</v>
+      </c>
+      <c r="W94" s="37" t="n">
+        <v>45853.97</v>
+      </c>
+      <c r="X94" s="18" t="n">
+        <v>21114.54</v>
+      </c>
+      <c r="Y94" s="19" t="n">
+        <v>-1274.09</v>
+      </c>
+      <c r="Z94" s="10" t="n"/>
+      <c r="AA94" s="10" t="n"/>
+      <c r="AB94" s="11" t="n"/>
+      <c r="AC94" s="10" t="n"/>
+      <c r="AD94" s="10" t="n"/>
+      <c r="AE94" s="10" t="n"/>
+      <c r="AF94" s="10" t="n"/>
+      <c r="AG94" s="11" t="n"/>
+      <c r="AH94" s="10" t="n"/>
+      <c r="AI94" s="10" t="n"/>
+      <c r="AJ94" s="10" t="n"/>
+      <c r="AK94" s="10" t="n"/>
+      <c r="AL94" s="11" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>1</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>배당금수취(CF)</t>
+        </is>
+      </c>
+      <c r="H95" s="9" t="n"/>
+      <c r="M95" s="9" t="n"/>
+      <c r="R95" s="9" t="n"/>
+      <c r="U95" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V95" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W95" s="9" t="n"/>
+      <c r="Y95" s="5" t="n"/>
+      <c r="Z95" s="10" t="n"/>
+      <c r="AA95" s="10" t="n"/>
+      <c r="AB95" s="11" t="n"/>
+      <c r="AC95" s="10" t="n"/>
+      <c r="AD95" s="10" t="n"/>
+      <c r="AE95" s="10" t="n"/>
+      <c r="AF95" s="10" t="n"/>
+      <c r="AG95" s="11" t="n"/>
+      <c r="AH95" s="10" t="n"/>
+      <c r="AI95" s="10" t="n"/>
+      <c r="AJ95" s="10" t="n"/>
+      <c r="AK95" s="10" t="n"/>
+      <c r="AL95" s="11" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14751,7 +14883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL93"/>
+  <dimension ref="A1:AL95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -14983,7 +15115,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -17159,67 +17291,67 @@
         </is>
       </c>
       <c r="E27" s="18" t="n">
-        <v>113.54</v>
+        <v>846.67</v>
       </c>
       <c r="F27" s="18" t="n">
-        <v>102.03</v>
+        <v>813.0599999999999</v>
       </c>
       <c r="G27" s="18" t="n">
-        <v>128.34</v>
+        <v>904.86</v>
       </c>
       <c r="H27" s="37" t="n">
-        <v>128.34</v>
+        <v>904.86</v>
       </c>
       <c r="I27" s="18" t="n">
-        <v>162.31</v>
+        <v>1058.99</v>
       </c>
       <c r="J27" s="18" t="n">
-        <v>149.71</v>
+        <v>1019.37</v>
       </c>
       <c r="K27" s="18" t="n">
-        <v>147.05</v>
+        <v>992.45</v>
       </c>
       <c r="L27" s="18" t="n">
-        <v>131.65</v>
+        <v>957.1799999999999</v>
       </c>
       <c r="M27" s="37" t="n">
-        <v>131.65</v>
+        <v>957.1799999999999</v>
       </c>
       <c r="N27" s="18" t="n">
-        <v>117.53</v>
+        <v>929.15</v>
       </c>
       <c r="O27" s="18" t="n">
-        <v>98.25</v>
+        <v>881.14</v>
       </c>
       <c r="P27" s="18" t="n">
-        <v>84.13</v>
+        <v>850.3099999999999</v>
       </c>
       <c r="Q27" s="18" t="n">
-        <v>84.51000000000001</v>
+        <v>829.5700000000001</v>
       </c>
       <c r="R27" s="37" t="n">
-        <v>84.51000000000001</v>
+        <v>829.5700000000001</v>
       </c>
       <c r="S27" s="18" t="n">
-        <v>82.09</v>
+        <v>761.9400000000001</v>
       </c>
       <c r="T27" s="18" t="n">
-        <v>78.78</v>
+        <v>741.49</v>
       </c>
       <c r="U27" s="18" t="n">
-        <v>75.02</v>
+        <v>720.8200000000001</v>
       </c>
       <c r="V27" s="18" t="n">
-        <v>69.84999999999999</v>
+        <v>699.9299999999999</v>
       </c>
       <c r="W27" s="37" t="n">
-        <v>69.84999999999999</v>
+        <v>699.9299999999999</v>
       </c>
       <c r="X27" s="18" t="n">
-        <v>60.33</v>
+        <v>690.53</v>
       </c>
       <c r="Y27" s="19" t="n">
-        <v>52.45</v>
+        <v>682.26</v>
       </c>
       <c r="Z27" s="10" t="n"/>
       <c r="AA27" s="10" t="n"/>
@@ -17715,71 +17847,71 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>확정급여부채</t>
+          <t>비유동리스부채</t>
         </is>
       </c>
       <c r="E34" s="18" t="n">
-        <v>1424.81</v>
+        <v>733.13</v>
       </c>
       <c r="F34" s="18" t="n">
-        <v>1562.5</v>
+        <v>711.03</v>
       </c>
       <c r="G34" s="18" t="n">
-        <v>1183.55</v>
+        <v>776.52</v>
       </c>
       <c r="H34" s="37" t="n">
-        <v>1183.55</v>
+        <v>776.52</v>
       </c>
       <c r="I34" s="18" t="n">
-        <v>398.48</v>
+        <v>896.6799999999999</v>
       </c>
       <c r="J34" s="18" t="n">
-        <v>530.91</v>
+        <v>869.66</v>
       </c>
       <c r="K34" s="18" t="n">
-        <v>560.34</v>
+        <v>845.4</v>
       </c>
       <c r="L34" s="18" t="n">
-        <v>338.53</v>
+        <v>825.53</v>
       </c>
       <c r="M34" s="37" t="n">
-        <v>338.53</v>
+        <v>825.53</v>
       </c>
       <c r="N34" s="18" t="n">
-        <v>488.6</v>
+        <v>811.62</v>
       </c>
       <c r="O34" s="18" t="n">
-        <v>625.52</v>
+        <v>782.89</v>
       </c>
       <c r="P34" s="18" t="n">
-        <v>759.51</v>
+        <v>766.1799999999999</v>
       </c>
       <c r="Q34" s="18" t="n">
-        <v>880.67</v>
+        <v>745.0599999999999</v>
       </c>
       <c r="R34" s="37" t="n">
-        <v>880.67</v>
+        <v>745.0599999999999</v>
       </c>
       <c r="S34" s="18" t="n">
-        <v>1053.55</v>
+        <v>679.85</v>
       </c>
       <c r="T34" s="18" t="n">
-        <v>1226.43</v>
+        <v>662.71</v>
       </c>
       <c r="U34" s="18" t="n">
-        <v>1399.32</v>
+        <v>645.8</v>
       </c>
       <c r="V34" s="18" t="n">
-        <v>683.26</v>
+        <v>630.08</v>
       </c>
       <c r="W34" s="37" t="n">
-        <v>683.26</v>
+        <v>630.08</v>
       </c>
       <c r="X34" s="18" t="n">
-        <v>876.25</v>
+        <v>630.2</v>
       </c>
       <c r="Y34" s="19" t="n">
-        <v>901.5</v>
+        <v>629.8099999999999</v>
       </c>
       <c r="Z34" s="10" t="n"/>
       <c r="AA34" s="10" t="n"/>
@@ -17801,71 +17933,71 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>기타비유동부채</t>
+          <t>장기금융부채</t>
         </is>
       </c>
       <c r="E35" s="18" t="n">
-        <v>28.46</v>
+        <v>733.13</v>
       </c>
       <c r="F35" s="18" t="n">
-        <v>29.76</v>
+        <v>711.03</v>
       </c>
       <c r="G35" s="18" t="n">
-        <v>28.17</v>
+        <v>776.52</v>
       </c>
       <c r="H35" s="37" t="n">
-        <v>28.17</v>
+        <v>776.52</v>
       </c>
       <c r="I35" s="18" t="n">
-        <v>29.51</v>
+        <v>896.6799999999999</v>
       </c>
       <c r="J35" s="18" t="n">
-        <v>30.84</v>
+        <v>869.66</v>
       </c>
       <c r="K35" s="18" t="n">
-        <v>32.18</v>
+        <v>845.4</v>
       </c>
       <c r="L35" s="18" t="n">
-        <v>30.43</v>
+        <v>825.53</v>
       </c>
       <c r="M35" s="37" t="n">
-        <v>30.43</v>
+        <v>825.53</v>
       </c>
       <c r="N35" s="18" t="n">
-        <v>31.98</v>
+        <v>811.62</v>
       </c>
       <c r="O35" s="18" t="n">
-        <v>33.54</v>
+        <v>782.89</v>
       </c>
       <c r="P35" s="18" t="n">
-        <v>35.1</v>
+        <v>766.1799999999999</v>
       </c>
       <c r="Q35" s="18" t="n">
-        <v>34.75</v>
+        <v>745.0599999999999</v>
       </c>
       <c r="R35" s="37" t="n">
-        <v>34.75</v>
+        <v>745.0599999999999</v>
       </c>
       <c r="S35" s="18" t="n">
-        <v>36.41</v>
+        <v>679.85</v>
       </c>
       <c r="T35" s="18" t="n">
-        <v>38.08</v>
+        <v>662.71</v>
       </c>
       <c r="U35" s="18" t="n">
-        <v>39.74</v>
+        <v>645.8</v>
       </c>
       <c r="V35" s="18" t="n">
-        <v>43.32</v>
+        <v>630.08</v>
       </c>
       <c r="W35" s="37" t="n">
-        <v>43.32</v>
+        <v>630.08</v>
       </c>
       <c r="X35" s="18" t="n">
-        <v>45.12</v>
+        <v>630.2</v>
       </c>
       <c r="Y35" s="19" t="n">
-        <v>46.92</v>
+        <v>629.8099999999999</v>
       </c>
       <c r="Z35" s="10" t="n"/>
       <c r="AA35" s="10" t="n"/>
@@ -17887,71 +18019,71 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>부채총계</t>
+          <t>확정급여부채</t>
         </is>
       </c>
       <c r="E36" s="18" t="n">
-        <v>26928.39</v>
+        <v>1424.81</v>
       </c>
       <c r="F36" s="18" t="n">
-        <v>28191.75</v>
+        <v>1562.5</v>
       </c>
       <c r="G36" s="18" t="n">
-        <v>23293.14</v>
+        <v>1183.55</v>
       </c>
       <c r="H36" s="37" t="n">
-        <v>23293.14</v>
+        <v>1183.55</v>
       </c>
       <c r="I36" s="18" t="n">
-        <v>17266.04</v>
+        <v>398.48</v>
       </c>
       <c r="J36" s="18" t="n">
-        <v>22808.26</v>
+        <v>530.91</v>
       </c>
       <c r="K36" s="18" t="n">
-        <v>17861.93</v>
+        <v>560.34</v>
       </c>
       <c r="L36" s="18" t="n">
-        <v>17197.67</v>
+        <v>338.53</v>
       </c>
       <c r="M36" s="37" t="n">
-        <v>17197.67</v>
+        <v>338.53</v>
       </c>
       <c r="N36" s="18" t="n">
-        <v>125766.88</v>
+        <v>488.6</v>
       </c>
       <c r="O36" s="18" t="n">
-        <v>121645.59</v>
+        <v>625.52</v>
       </c>
       <c r="P36" s="18" t="n">
-        <v>115775.57</v>
+        <v>759.51</v>
       </c>
       <c r="Q36" s="18" t="n">
-        <v>145973.11</v>
+        <v>880.67</v>
       </c>
       <c r="R36" s="37" t="n">
-        <v>145973.11</v>
+        <v>880.67</v>
       </c>
       <c r="S36" s="18" t="n">
-        <v>147430.19</v>
+        <v>1053.55</v>
       </c>
       <c r="T36" s="18" t="n">
-        <v>144047.44</v>
+        <v>1226.43</v>
       </c>
       <c r="U36" s="18" t="n">
-        <v>142938.04</v>
+        <v>1399.32</v>
       </c>
       <c r="V36" s="18" t="n">
-        <v>188886.35</v>
+        <v>683.26</v>
       </c>
       <c r="W36" s="37" t="n">
-        <v>188886.35</v>
+        <v>683.26</v>
       </c>
       <c r="X36" s="18" t="n">
-        <v>188919.21</v>
+        <v>876.25</v>
       </c>
       <c r="Y36" s="19" t="n">
-        <v>178815.67</v>
+        <v>901.5</v>
       </c>
       <c r="Z36" s="10" t="n"/>
       <c r="AA36" s="10" t="n"/>
@@ -17973,71 +18105,71 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>자본금</t>
+          <t>기타비유동부채</t>
         </is>
       </c>
       <c r="E37" s="18" t="n">
-        <v>4380.5</v>
+        <v>28.46</v>
       </c>
       <c r="F37" s="18" t="n">
-        <v>4380.5</v>
+        <v>29.76</v>
       </c>
       <c r="G37" s="18" t="n">
-        <v>4380.5</v>
+        <v>28.17</v>
       </c>
       <c r="H37" s="37" t="n">
-        <v>4380.5</v>
+        <v>28.17</v>
       </c>
       <c r="I37" s="18" t="n">
-        <v>4380.5</v>
+        <v>29.51</v>
       </c>
       <c r="J37" s="18" t="n">
-        <v>4380.5</v>
+        <v>30.84</v>
       </c>
       <c r="K37" s="18" t="n">
-        <v>4380.5</v>
+        <v>32.18</v>
       </c>
       <c r="L37" s="18" t="n">
-        <v>4380.5</v>
+        <v>30.43</v>
       </c>
       <c r="M37" s="37" t="n">
-        <v>4380.5</v>
+        <v>30.43</v>
       </c>
       <c r="N37" s="18" t="n">
-        <v>4380.5</v>
+        <v>31.98</v>
       </c>
       <c r="O37" s="18" t="n">
-        <v>4380.5</v>
+        <v>33.54</v>
       </c>
       <c r="P37" s="18" t="n">
-        <v>4380.5</v>
+        <v>35.1</v>
       </c>
       <c r="Q37" s="18" t="n">
-        <v>4380.5</v>
+        <v>34.75</v>
       </c>
       <c r="R37" s="37" t="n">
-        <v>4380.5</v>
+        <v>34.75</v>
       </c>
       <c r="S37" s="18" t="n">
-        <v>4380.5</v>
+        <v>36.41</v>
       </c>
       <c r="T37" s="18" t="n">
-        <v>4380.5</v>
+        <v>38.08</v>
       </c>
       <c r="U37" s="18" t="n">
-        <v>4380.5</v>
+        <v>39.74</v>
       </c>
       <c r="V37" s="18" t="n">
-        <v>4380.5</v>
+        <v>43.32</v>
       </c>
       <c r="W37" s="37" t="n">
-        <v>4380.5</v>
+        <v>43.32</v>
       </c>
       <c r="X37" s="18" t="n">
-        <v>4380.5</v>
+        <v>45.12</v>
       </c>
       <c r="Y37" s="19" t="n">
-        <v>4380.5</v>
+        <v>46.92</v>
       </c>
       <c r="Z37" s="10" t="n"/>
       <c r="AA37" s="10" t="n"/>
@@ -18059,71 +18191,71 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>자본잉여금</t>
+          <t>부채총계</t>
         </is>
       </c>
       <c r="E38" s="18" t="n">
-        <v>98129.17</v>
+        <v>26928.39</v>
       </c>
       <c r="F38" s="18" t="n">
-        <v>95077.91</v>
+        <v>28191.75</v>
       </c>
       <c r="G38" s="18" t="n">
-        <v>92602.21000000001</v>
+        <v>23293.14</v>
       </c>
       <c r="H38" s="37" t="n">
-        <v>92602.21000000001</v>
+        <v>23293.14</v>
       </c>
       <c r="I38" s="18" t="n">
-        <v>92577.66</v>
+        <v>17266.04</v>
       </c>
       <c r="J38" s="18" t="n">
-        <v>92581.5</v>
+        <v>22808.26</v>
       </c>
       <c r="K38" s="18" t="n">
-        <v>92585.34</v>
+        <v>17861.93</v>
       </c>
       <c r="L38" s="18" t="n">
-        <v>92513.42</v>
+        <v>17197.67</v>
       </c>
       <c r="M38" s="37" t="n">
-        <v>92513.42</v>
+        <v>17197.67</v>
       </c>
       <c r="N38" s="18" t="n">
-        <v>92527.78999999999</v>
+        <v>125766.88</v>
       </c>
       <c r="O38" s="18" t="n">
-        <v>92538.2</v>
+        <v>121645.59</v>
       </c>
       <c r="P38" s="18" t="n">
-        <v>92538.2</v>
+        <v>115775.57</v>
       </c>
       <c r="Q38" s="18" t="n">
-        <v>92538.2</v>
+        <v>145973.11</v>
       </c>
       <c r="R38" s="37" t="n">
-        <v>92538.2</v>
+        <v>145973.11</v>
       </c>
       <c r="S38" s="18" t="n">
-        <v>92538.2</v>
+        <v>147430.19</v>
       </c>
       <c r="T38" s="18" t="n">
-        <v>92538.2</v>
+        <v>144047.44</v>
       </c>
       <c r="U38" s="18" t="n">
-        <v>92538.2</v>
+        <v>142938.04</v>
       </c>
       <c r="V38" s="18" t="n">
-        <v>92538.2</v>
+        <v>188886.35</v>
       </c>
       <c r="W38" s="37" t="n">
-        <v>92538.2</v>
+        <v>188886.35</v>
       </c>
       <c r="X38" s="18" t="n">
-        <v>92538.2</v>
+        <v>188919.21</v>
       </c>
       <c r="Y38" s="19" t="n">
-        <v>92538.2</v>
+        <v>178815.67</v>
       </c>
       <c r="Z38" s="10" t="n"/>
       <c r="AA38" s="10" t="n"/>
@@ -18145,71 +18277,71 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>이익잉여금</t>
+          <t>자본금</t>
         </is>
       </c>
       <c r="E39" s="18" t="n">
-        <v>8479.34</v>
+        <v>4380.5</v>
       </c>
       <c r="F39" s="18" t="n">
-        <v>9883.450000000001</v>
+        <v>4380.5</v>
       </c>
       <c r="G39" s="18" t="n">
-        <v>9426.200000000001</v>
+        <v>4380.5</v>
       </c>
       <c r="H39" s="37" t="n">
-        <v>9426.200000000001</v>
+        <v>4380.5</v>
       </c>
       <c r="I39" s="18" t="n">
-        <v>10015.34</v>
+        <v>4380.5</v>
       </c>
       <c r="J39" s="18" t="n">
-        <v>9615.65</v>
+        <v>4380.5</v>
       </c>
       <c r="K39" s="18" t="n">
-        <v>8141.32</v>
+        <v>4380.5</v>
       </c>
       <c r="L39" s="18" t="n">
-        <v>7142.22</v>
+        <v>4380.5</v>
       </c>
       <c r="M39" s="37" t="n">
-        <v>7142.22</v>
+        <v>4380.5</v>
       </c>
       <c r="N39" s="18" t="n">
-        <v>6642.93</v>
+        <v>4380.5</v>
       </c>
       <c r="O39" s="18" t="n">
-        <v>7591.12</v>
+        <v>4380.5</v>
       </c>
       <c r="P39" s="18" t="n">
-        <v>8536.24</v>
+        <v>4380.5</v>
       </c>
       <c r="Q39" s="18" t="n">
-        <v>8092.02</v>
+        <v>4380.5</v>
       </c>
       <c r="R39" s="37" t="n">
-        <v>8092.02</v>
+        <v>4380.5</v>
       </c>
       <c r="S39" s="18" t="n">
-        <v>8284.129999999999</v>
+        <v>4380.5</v>
       </c>
       <c r="T39" s="18" t="n">
-        <v>8121.44</v>
+        <v>4380.5</v>
       </c>
       <c r="U39" s="18" t="n">
-        <v>8716.77</v>
+        <v>4380.5</v>
       </c>
       <c r="V39" s="18" t="n">
-        <v>10571.84</v>
+        <v>4380.5</v>
       </c>
       <c r="W39" s="37" t="n">
-        <v>10571.84</v>
+        <v>4380.5</v>
       </c>
       <c r="X39" s="18" t="n">
-        <v>8982.27</v>
+        <v>4380.5</v>
       </c>
       <c r="Y39" s="19" t="n">
-        <v>5682.2</v>
+        <v>4380.5</v>
       </c>
       <c r="Z39" s="10" t="n"/>
       <c r="AA39" s="10" t="n"/>
@@ -18231,71 +18363,71 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>자본총계</t>
+          <t>자본잉여금</t>
         </is>
       </c>
       <c r="E40" s="18" t="n">
-        <v>110989.01</v>
+        <v>98129.17</v>
       </c>
       <c r="F40" s="18" t="n">
-        <v>109341.87</v>
+        <v>95077.91</v>
       </c>
       <c r="G40" s="18" t="n">
-        <v>106408.91</v>
+        <v>92602.21000000001</v>
       </c>
       <c r="H40" s="37" t="n">
-        <v>106408.91</v>
+        <v>92602.21000000001</v>
       </c>
       <c r="I40" s="18" t="n">
-        <v>106973.49</v>
+        <v>92577.66</v>
       </c>
       <c r="J40" s="18" t="n">
-        <v>106577.65</v>
+        <v>92581.5</v>
       </c>
       <c r="K40" s="18" t="n">
-        <v>105107.17</v>
+        <v>92585.34</v>
       </c>
       <c r="L40" s="18" t="n">
-        <v>104036.14</v>
+        <v>92513.42</v>
       </c>
       <c r="M40" s="37" t="n">
-        <v>104036.14</v>
+        <v>92513.42</v>
       </c>
       <c r="N40" s="18" t="n">
-        <v>103551.22</v>
+        <v>92527.78999999999</v>
       </c>
       <c r="O40" s="18" t="n">
-        <v>104509.82</v>
+        <v>92538.2</v>
       </c>
       <c r="P40" s="18" t="n">
-        <v>105454.94</v>
+        <v>92538.2</v>
       </c>
       <c r="Q40" s="18" t="n">
-        <v>164707.03</v>
+        <v>92538.2</v>
       </c>
       <c r="R40" s="37" t="n">
-        <v>164707.03</v>
+        <v>92538.2</v>
       </c>
       <c r="S40" s="18" t="n">
-        <v>164899.14</v>
+        <v>92538.2</v>
       </c>
       <c r="T40" s="18" t="n">
-        <v>164736.45</v>
+        <v>92538.2</v>
       </c>
       <c r="U40" s="18" t="n">
-        <v>165331.78</v>
+        <v>92538.2</v>
       </c>
       <c r="V40" s="18" t="n">
-        <v>162941.98</v>
+        <v>92538.2</v>
       </c>
       <c r="W40" s="37" t="n">
-        <v>162941.98</v>
+        <v>92538.2</v>
       </c>
       <c r="X40" s="18" t="n">
-        <v>161352.42</v>
+        <v>92538.2</v>
       </c>
       <c r="Y40" s="19" t="n">
-        <v>158052.34</v>
+        <v>92538.2</v>
       </c>
       <c r="Z40" s="10" t="n"/>
       <c r="AA40" s="10" t="n"/>
@@ -18317,71 +18449,71 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>부채와자본총계</t>
+          <t>이익잉여금</t>
         </is>
       </c>
       <c r="E41" s="18" t="n">
-        <v>137917.4</v>
+        <v>8479.34</v>
       </c>
       <c r="F41" s="18" t="n">
-        <v>137533.61</v>
+        <v>9883.450000000001</v>
       </c>
       <c r="G41" s="18" t="n">
-        <v>129702.05</v>
+        <v>9426.200000000001</v>
       </c>
       <c r="H41" s="37" t="n">
-        <v>129702.05</v>
+        <v>9426.200000000001</v>
       </c>
       <c r="I41" s="18" t="n">
-        <v>124239.54</v>
+        <v>10015.34</v>
       </c>
       <c r="J41" s="18" t="n">
-        <v>129385.9</v>
+        <v>9615.65</v>
       </c>
       <c r="K41" s="18" t="n">
-        <v>122969.1</v>
+        <v>8141.32</v>
       </c>
       <c r="L41" s="18" t="n">
-        <v>121233.81</v>
+        <v>7142.22</v>
       </c>
       <c r="M41" s="37" t="n">
-        <v>121233.81</v>
+        <v>7142.22</v>
       </c>
       <c r="N41" s="18" t="n">
-        <v>229318.1</v>
+        <v>6642.93</v>
       </c>
       <c r="O41" s="18" t="n">
-        <v>226155.41</v>
+        <v>7591.12</v>
       </c>
       <c r="P41" s="18" t="n">
-        <v>221230.51</v>
+        <v>8536.24</v>
       </c>
       <c r="Q41" s="18" t="n">
-        <v>310680.14</v>
+        <v>8092.02</v>
       </c>
       <c r="R41" s="37" t="n">
-        <v>310680.14</v>
+        <v>8092.02</v>
       </c>
       <c r="S41" s="18" t="n">
-        <v>312329.33</v>
+        <v>8284.129999999999</v>
       </c>
       <c r="T41" s="18" t="n">
-        <v>308783.88</v>
+        <v>8121.44</v>
       </c>
       <c r="U41" s="18" t="n">
-        <v>308269.82</v>
+        <v>8716.77</v>
       </c>
       <c r="V41" s="18" t="n">
-        <v>351828.33</v>
+        <v>10571.84</v>
       </c>
       <c r="W41" s="37" t="n">
-        <v>351828.33</v>
+        <v>10571.84</v>
       </c>
       <c r="X41" s="18" t="n">
-        <v>350271.63</v>
+        <v>8982.27</v>
       </c>
       <c r="Y41" s="19" t="n">
-        <v>336868</v>
+        <v>5682.2</v>
       </c>
       <c r="Z41" s="10" t="n"/>
       <c r="AA41" s="10" t="n"/>
@@ -18403,7 +18535,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>지배주주지분</t>
+          <t>자본총계</t>
         </is>
       </c>
       <c r="E42" s="18" t="n">
@@ -18489,71 +18621,71 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>총차입금</t>
+          <t>부채와자본총계</t>
         </is>
       </c>
       <c r="E43" s="18" t="n">
-        <v>5200</v>
+        <v>137917.4</v>
       </c>
       <c r="F43" s="18" t="n">
-        <v>5200</v>
+        <v>137533.61</v>
       </c>
       <c r="G43" s="18" t="n">
-        <v>5200</v>
+        <v>129702.05</v>
       </c>
       <c r="H43" s="37" t="n">
-        <v>5200</v>
+        <v>129702.05</v>
       </c>
       <c r="I43" s="18" t="n">
-        <v>5200</v>
+        <v>124239.54</v>
       </c>
       <c r="J43" s="18" t="n">
-        <v>8090</v>
+        <v>129385.9</v>
       </c>
       <c r="K43" s="18" t="n">
-        <v>8090</v>
+        <v>122969.1</v>
       </c>
       <c r="L43" s="18" t="n">
-        <v>8090</v>
+        <v>121233.81</v>
       </c>
       <c r="M43" s="37" t="n">
-        <v>8090</v>
+        <v>121233.81</v>
       </c>
       <c r="N43" s="18" t="n">
-        <v>96090</v>
+        <v>229318.1</v>
       </c>
       <c r="O43" s="18" t="n">
-        <v>96090</v>
+        <v>226155.41</v>
       </c>
       <c r="P43" s="18" t="n">
-        <v>96090</v>
+        <v>221230.51</v>
       </c>
       <c r="Q43" s="18" t="n">
-        <v>112875.01</v>
+        <v>310680.14</v>
       </c>
       <c r="R43" s="37" t="n">
-        <v>112875.01</v>
+        <v>310680.14</v>
       </c>
       <c r="S43" s="18" t="n">
-        <v>115098.92</v>
+        <v>312329.33</v>
       </c>
       <c r="T43" s="18" t="n">
-        <v>114827.08</v>
+        <v>308783.88</v>
       </c>
       <c r="U43" s="18" t="n">
-        <v>114809.57</v>
+        <v>308269.82</v>
       </c>
       <c r="V43" s="18" t="n">
-        <v>123410.7</v>
+        <v>351828.33</v>
       </c>
       <c r="W43" s="37" t="n">
-        <v>123410.7</v>
+        <v>351828.33</v>
       </c>
       <c r="X43" s="18" t="n">
-        <v>127363.51</v>
+        <v>350271.63</v>
       </c>
       <c r="Y43" s="19" t="n">
-        <v>123207.83</v>
+        <v>336868</v>
       </c>
       <c r="Z43" s="10" t="n"/>
       <c r="AA43" s="10" t="n"/>
@@ -18575,71 +18707,71 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>순차입금</t>
+          <t>지배주주지분</t>
         </is>
       </c>
       <c r="E44" s="18" t="n">
-        <v>-87308.89999999999</v>
+        <v>110989.01</v>
       </c>
       <c r="F44" s="18" t="n">
-        <v>-84589.67</v>
+        <v>109341.87</v>
       </c>
       <c r="G44" s="18" t="n">
-        <v>-71358.12</v>
+        <v>106408.91</v>
       </c>
       <c r="H44" s="37" t="n">
-        <v>-71358.12</v>
+        <v>106408.91</v>
       </c>
       <c r="I44" s="18" t="n">
-        <v>-58521.84</v>
+        <v>106973.49</v>
       </c>
       <c r="J44" s="18" t="n">
-        <v>-54361.89</v>
+        <v>106577.65</v>
       </c>
       <c r="K44" s="18" t="n">
-        <v>-46547.22</v>
+        <v>105107.17</v>
       </c>
       <c r="L44" s="18" t="n">
-        <v>-34079.85</v>
+        <v>104036.14</v>
       </c>
       <c r="M44" s="37" t="n">
-        <v>-34079.85</v>
+        <v>104036.14</v>
       </c>
       <c r="N44" s="18" t="n">
-        <v>87709.06</v>
+        <v>103551.22</v>
       </c>
       <c r="O44" s="18" t="n">
-        <v>63954.82</v>
+        <v>104509.82</v>
       </c>
       <c r="P44" s="18" t="n">
-        <v>74838.3</v>
+        <v>105454.94</v>
       </c>
       <c r="Q44" s="18" t="n">
-        <v>90325.53999999999</v>
+        <v>164707.03</v>
       </c>
       <c r="R44" s="37" t="n">
-        <v>90325.53999999999</v>
+        <v>164707.03</v>
       </c>
       <c r="S44" s="18" t="n">
-        <v>89082.45</v>
+        <v>164899.14</v>
       </c>
       <c r="T44" s="18" t="n">
-        <v>98854.07000000001</v>
+        <v>164736.45</v>
       </c>
       <c r="U44" s="18" t="n">
-        <v>104695.84</v>
+        <v>165331.78</v>
       </c>
       <c r="V44" s="18" t="n">
-        <v>75158.10000000001</v>
+        <v>162941.98</v>
       </c>
       <c r="W44" s="37" t="n">
-        <v>75158.10000000001</v>
+        <v>162941.98</v>
       </c>
       <c r="X44" s="18" t="n">
-        <v>101015.28</v>
+        <v>161352.42</v>
       </c>
       <c r="Y44" s="19" t="n">
-        <v>101529.8</v>
+        <v>158052.34</v>
       </c>
       <c r="Z44" s="10" t="n"/>
       <c r="AA44" s="10" t="n"/>
@@ -18661,71 +18793,71 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>이자발생자산</t>
+          <t>총차입금</t>
         </is>
       </c>
       <c r="E45" s="18" t="n">
-        <v>100144.7</v>
+        <v>5200</v>
       </c>
       <c r="F45" s="18" t="n">
-        <v>97425.47</v>
+        <v>5200</v>
       </c>
       <c r="G45" s="18" t="n">
-        <v>84145.27</v>
+        <v>5200</v>
       </c>
       <c r="H45" s="37" t="n">
-        <v>84145.27</v>
+        <v>5200</v>
       </c>
       <c r="I45" s="18" t="n">
-        <v>71328.52</v>
+        <v>5200</v>
       </c>
       <c r="J45" s="18" t="n">
-        <v>70058.57000000001</v>
+        <v>8090</v>
       </c>
       <c r="K45" s="18" t="n">
-        <v>62243.9</v>
+        <v>8090</v>
       </c>
       <c r="L45" s="18" t="n">
-        <v>50276.53</v>
+        <v>8090</v>
       </c>
       <c r="M45" s="37" t="n">
-        <v>50276.53</v>
+        <v>8090</v>
       </c>
       <c r="N45" s="18" t="n">
-        <v>16512.06</v>
+        <v>96090</v>
       </c>
       <c r="O45" s="18" t="n">
-        <v>40266.3</v>
+        <v>96090</v>
       </c>
       <c r="P45" s="18" t="n">
-        <v>29382.82</v>
+        <v>96090</v>
       </c>
       <c r="Q45" s="18" t="n">
-        <v>27180.59</v>
+        <v>112875.01</v>
       </c>
       <c r="R45" s="37" t="n">
-        <v>27180.59</v>
+        <v>112875.01</v>
       </c>
       <c r="S45" s="18" t="n">
-        <v>30966.08</v>
+        <v>115098.92</v>
       </c>
       <c r="T45" s="18" t="n">
-        <v>20922.62</v>
+        <v>114827.08</v>
       </c>
       <c r="U45" s="18" t="n">
-        <v>19073.34</v>
+        <v>114809.57</v>
       </c>
       <c r="V45" s="18" t="n">
-        <v>55337.21</v>
+        <v>123410.7</v>
       </c>
       <c r="W45" s="37" t="n">
-        <v>55337.21</v>
+        <v>123410.7</v>
       </c>
       <c r="X45" s="18" t="n">
-        <v>33887.56</v>
+        <v>127363.51</v>
       </c>
       <c r="Y45" s="19" t="n">
-        <v>29217.36</v>
+        <v>123207.83</v>
       </c>
       <c r="Z45" s="10" t="n"/>
       <c r="AA45" s="10" t="n"/>
@@ -18747,65 +18879,71 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>당기법인세자산(선급법인세)</t>
-        </is>
+          <t>순차입금</t>
+        </is>
+      </c>
+      <c r="E46" s="18" t="n">
+        <v>-87308.89999999999</v>
+      </c>
+      <c r="F46" s="18" t="n">
+        <v>-84589.67</v>
       </c>
       <c r="G46" s="18" t="n">
-        <v>423.35</v>
+        <v>-71358.12</v>
       </c>
       <c r="H46" s="37" t="n">
-        <v>423.35</v>
+        <v>-71358.12</v>
       </c>
       <c r="I46" s="18" t="n">
-        <v>370.83</v>
+        <v>-58521.84</v>
       </c>
       <c r="J46" s="18" t="n">
-        <v>121.59</v>
+        <v>-54361.89</v>
       </c>
       <c r="K46" s="18" t="n">
-        <v>405.09</v>
+        <v>-46547.22</v>
       </c>
       <c r="L46" s="18" t="n">
-        <v>466.45</v>
+        <v>-34079.85</v>
       </c>
       <c r="M46" s="37" t="n">
-        <v>466.45</v>
+        <v>-34079.85</v>
       </c>
       <c r="N46" s="18" t="n">
-        <v>507.73</v>
+        <v>87709.06</v>
       </c>
       <c r="O46" s="18" t="n">
-        <v>124.7</v>
+        <v>63954.82</v>
       </c>
       <c r="P46" s="18" t="n">
-        <v>170.39</v>
+        <v>74838.3</v>
       </c>
       <c r="Q46" s="18" t="n">
-        <v>183.55</v>
+        <v>90325.53999999999</v>
       </c>
       <c r="R46" s="37" t="n">
-        <v>183.55</v>
+        <v>90325.53999999999</v>
       </c>
       <c r="S46" s="18" t="n">
-        <v>204.32</v>
+        <v>89082.45</v>
       </c>
       <c r="T46" s="18" t="n">
-        <v>119.44</v>
+        <v>98854.07000000001</v>
       </c>
       <c r="U46" s="18" t="n">
-        <v>191.69</v>
+        <v>104695.84</v>
       </c>
       <c r="V46" s="18" t="n">
-        <v>289.9</v>
+        <v>75158.10000000001</v>
       </c>
       <c r="W46" s="37" t="n">
-        <v>289.9</v>
+        <v>75158.10000000001</v>
       </c>
       <c r="X46" s="18" t="n">
-        <v>300.2</v>
+        <v>101015.28</v>
       </c>
       <c r="Y46" s="19" t="n">
-        <v>212.04</v>
+        <v>101529.8</v>
       </c>
       <c r="Z46" s="10" t="n"/>
       <c r="AA46" s="10" t="n"/>
@@ -18827,42 +18965,71 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>기타유동금융부채</t>
-        </is>
+          <t>이자발생자산</t>
+        </is>
+      </c>
+      <c r="E47" s="18" t="n">
+        <v>100144.7</v>
+      </c>
+      <c r="F47" s="18" t="n">
+        <v>97425.47</v>
       </c>
       <c r="G47" s="18" t="n">
-        <v>0</v>
+        <v>84145.27</v>
       </c>
       <c r="H47" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M47" s="9" t="n"/>
+        <v>84145.27</v>
+      </c>
+      <c r="I47" s="18" t="n">
+        <v>71328.52</v>
+      </c>
+      <c r="J47" s="18" t="n">
+        <v>70058.57000000001</v>
+      </c>
+      <c r="K47" s="18" t="n">
+        <v>62243.9</v>
+      </c>
+      <c r="L47" s="18" t="n">
+        <v>50276.53</v>
+      </c>
+      <c r="M47" s="37" t="n">
+        <v>50276.53</v>
+      </c>
+      <c r="N47" s="18" t="n">
+        <v>16512.06</v>
+      </c>
+      <c r="O47" s="18" t="n">
+        <v>40266.3</v>
+      </c>
+      <c r="P47" s="18" t="n">
+        <v>29382.82</v>
+      </c>
       <c r="Q47" s="18" t="n">
-        <v>4081.04</v>
+        <v>27180.59</v>
       </c>
       <c r="R47" s="37" t="n">
-        <v>4081.04</v>
+        <v>27180.59</v>
       </c>
       <c r="S47" s="18" t="n">
-        <v>4081.04</v>
+        <v>30966.08</v>
       </c>
       <c r="T47" s="18" t="n">
-        <v>4081.04</v>
+        <v>20922.62</v>
       </c>
       <c r="U47" s="18" t="n">
-        <v>4081.04</v>
+        <v>19073.34</v>
       </c>
       <c r="V47" s="18" t="n">
-        <v>9554.57</v>
+        <v>55337.21</v>
       </c>
       <c r="W47" s="37" t="n">
-        <v>9554.57</v>
+        <v>55337.21</v>
       </c>
       <c r="X47" s="18" t="n">
-        <v>9554.57</v>
+        <v>33887.56</v>
       </c>
       <c r="Y47" s="19" t="n">
-        <v>13373.8</v>
+        <v>29217.36</v>
       </c>
       <c r="Z47" s="10" t="n"/>
       <c r="AA47" s="10" t="n"/>
@@ -18884,51 +19051,65 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>종속기업및관계기업투자</t>
-        </is>
-      </c>
-      <c r="H48" s="9" t="n"/>
+          <t>당기법인세자산(선급법인세)</t>
+        </is>
+      </c>
+      <c r="G48" s="18" t="n">
+        <v>423.35</v>
+      </c>
+      <c r="H48" s="37" t="n">
+        <v>423.35</v>
+      </c>
+      <c r="I48" s="18" t="n">
+        <v>370.83</v>
+      </c>
+      <c r="J48" s="18" t="n">
+        <v>121.59</v>
+      </c>
+      <c r="K48" s="18" t="n">
+        <v>405.09</v>
+      </c>
       <c r="L48" s="18" t="n">
-        <v>4950</v>
+        <v>466.45</v>
       </c>
       <c r="M48" s="37" t="n">
-        <v>4950</v>
+        <v>466.45</v>
       </c>
       <c r="N48" s="18" t="n">
-        <v>4950</v>
+        <v>507.73</v>
       </c>
       <c r="O48" s="18" t="n">
-        <v>4950</v>
+        <v>124.7</v>
       </c>
       <c r="P48" s="18" t="n">
-        <v>4950</v>
+        <v>170.39</v>
       </c>
       <c r="Q48" s="18" t="n">
-        <v>4950</v>
+        <v>183.55</v>
       </c>
       <c r="R48" s="37" t="n">
-        <v>4950</v>
+        <v>183.55</v>
       </c>
       <c r="S48" s="18" t="n">
-        <v>4950</v>
+        <v>204.32</v>
       </c>
       <c r="T48" s="18" t="n">
-        <v>4950</v>
+        <v>119.44</v>
       </c>
       <c r="U48" s="18" t="n">
-        <v>4950</v>
+        <v>191.69</v>
       </c>
       <c r="V48" s="18" t="n">
-        <v>4950</v>
+        <v>289.9</v>
       </c>
       <c r="W48" s="37" t="n">
-        <v>4950</v>
+        <v>289.9</v>
       </c>
       <c r="X48" s="18" t="n">
-        <v>4950</v>
+        <v>300.2</v>
       </c>
       <c r="Y48" s="19" t="n">
-        <v>4950</v>
+        <v>212.04</v>
       </c>
       <c r="Z48" s="10" t="n"/>
       <c r="AA48" s="10" t="n"/>
@@ -18950,20 +19131,43 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>투자부동산</t>
-        </is>
-      </c>
-      <c r="H49" s="9" t="n"/>
+          <t>기타유동금융부채</t>
+        </is>
+      </c>
+      <c r="G49" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="37" t="n">
+        <v>0</v>
+      </c>
       <c r="M49" s="9" t="n"/>
-      <c r="O49" s="18" t="n">
-        <v>116302.65</v>
-      </c>
-      <c r="P49" s="18" t="n">
-        <v>116194.1</v>
-      </c>
-      <c r="R49" s="9" t="n"/>
-      <c r="W49" s="9" t="n"/>
-      <c r="Y49" s="5" t="n"/>
+      <c r="Q49" s="18" t="n">
+        <v>4081.04</v>
+      </c>
+      <c r="R49" s="37" t="n">
+        <v>4081.04</v>
+      </c>
+      <c r="S49" s="18" t="n">
+        <v>4081.04</v>
+      </c>
+      <c r="T49" s="18" t="n">
+        <v>4081.04</v>
+      </c>
+      <c r="U49" s="18" t="n">
+        <v>4081.04</v>
+      </c>
+      <c r="V49" s="18" t="n">
+        <v>9554.57</v>
+      </c>
+      <c r="W49" s="37" t="n">
+        <v>9554.57</v>
+      </c>
+      <c r="X49" s="18" t="n">
+        <v>9554.57</v>
+      </c>
+      <c r="Y49" s="19" t="n">
+        <v>13373.8</v>
+      </c>
       <c r="Z49" s="10" t="n"/>
       <c r="AA49" s="10" t="n"/>
       <c r="AB49" s="11" t="n"/>
@@ -18984,37 +19188,51 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>단기투자자산(공정가치)</t>
+          <t>종속기업및관계기업투자</t>
         </is>
       </c>
       <c r="H50" s="9" t="n"/>
-      <c r="M50" s="9" t="n"/>
+      <c r="L50" s="18" t="n">
+        <v>4950</v>
+      </c>
+      <c r="M50" s="37" t="n">
+        <v>4950</v>
+      </c>
+      <c r="N50" s="18" t="n">
+        <v>4950</v>
+      </c>
+      <c r="O50" s="18" t="n">
+        <v>4950</v>
+      </c>
+      <c r="P50" s="18" t="n">
+        <v>4950</v>
+      </c>
       <c r="Q50" s="18" t="n">
-        <v>2687.53</v>
+        <v>4950</v>
       </c>
       <c r="R50" s="37" t="n">
-        <v>2687.53</v>
+        <v>4950</v>
       </c>
       <c r="S50" s="18" t="n">
-        <v>2687.53</v>
+        <v>4950</v>
       </c>
       <c r="T50" s="18" t="n">
-        <v>2687.53</v>
+        <v>4950</v>
       </c>
       <c r="U50" s="18" t="n">
-        <v>2687.53</v>
+        <v>4950</v>
       </c>
       <c r="V50" s="18" t="n">
-        <v>2887.42</v>
+        <v>4950</v>
       </c>
       <c r="W50" s="37" t="n">
-        <v>2887.42</v>
+        <v>4950</v>
       </c>
       <c r="X50" s="18" t="n">
-        <v>2887.42</v>
+        <v>4950</v>
       </c>
       <c r="Y50" s="19" t="n">
-        <v>2887.42</v>
+        <v>4950</v>
       </c>
       <c r="Z50" s="10" t="n"/>
       <c r="AA50" s="10" t="n"/>
@@ -19036,38 +19254,20 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>이연법인세부채</t>
+          <t>투자부동산</t>
         </is>
       </c>
       <c r="H51" s="9" t="n"/>
       <c r="M51" s="9" t="n"/>
-      <c r="Q51" s="18" t="n">
-        <v>11480.74</v>
-      </c>
-      <c r="R51" s="37" t="n">
-        <v>11480.74</v>
-      </c>
-      <c r="S51" s="18" t="n">
-        <v>11480.74</v>
-      </c>
-      <c r="T51" s="18" t="n">
-        <v>11555.1</v>
-      </c>
-      <c r="U51" s="18" t="n">
-        <v>11555.1</v>
-      </c>
-      <c r="V51" s="18" t="n">
-        <v>14160.66</v>
-      </c>
-      <c r="W51" s="37" t="n">
-        <v>14160.66</v>
-      </c>
-      <c r="X51" s="18" t="n">
-        <v>14160.66</v>
-      </c>
-      <c r="Y51" s="19" t="n">
-        <v>12939.38</v>
-      </c>
+      <c r="O51" s="18" t="n">
+        <v>116302.65</v>
+      </c>
+      <c r="P51" s="18" t="n">
+        <v>116194.1</v>
+      </c>
+      <c r="R51" s="9" t="n"/>
+      <c r="W51" s="9" t="n"/>
+      <c r="Y51" s="5" t="n"/>
       <c r="Z51" s="10" t="n"/>
       <c r="AA51" s="10" t="n"/>
       <c r="AB51" s="11" t="n"/>
@@ -19088,37 +19288,37 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>기타포괄이익누계액</t>
+          <t>단기투자자산(공정가치)</t>
         </is>
       </c>
       <c r="H52" s="9" t="n"/>
       <c r="M52" s="9" t="n"/>
       <c r="Q52" s="18" t="n">
-        <v>59696.31</v>
+        <v>2687.53</v>
       </c>
       <c r="R52" s="37" t="n">
-        <v>59696.31</v>
+        <v>2687.53</v>
       </c>
       <c r="S52" s="18" t="n">
-        <v>59696.31</v>
+        <v>2687.53</v>
       </c>
       <c r="T52" s="18" t="n">
-        <v>59696.31</v>
+        <v>2687.53</v>
       </c>
       <c r="U52" s="18" t="n">
-        <v>59696.31</v>
+        <v>2687.53</v>
       </c>
       <c r="V52" s="18" t="n">
-        <v>55451.44</v>
+        <v>2887.42</v>
       </c>
       <c r="W52" s="37" t="n">
-        <v>55451.44</v>
+        <v>2887.42</v>
       </c>
       <c r="X52" s="18" t="n">
-        <v>55451.44</v>
+        <v>2887.42</v>
       </c>
       <c r="Y52" s="19" t="n">
-        <v>55451.44</v>
+        <v>2887.42</v>
       </c>
       <c r="Z52" s="10" t="n"/>
       <c r="AA52" s="10" t="n"/>
@@ -19140,15 +19340,37 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>단기금융부채(face)</t>
+          <t>이연법인세부채</t>
         </is>
       </c>
       <c r="H53" s="9" t="n"/>
       <c r="M53" s="9" t="n"/>
-      <c r="R53" s="9" t="n"/>
-      <c r="W53" s="9" t="n"/>
+      <c r="Q53" s="18" t="n">
+        <v>11480.74</v>
+      </c>
+      <c r="R53" s="37" t="n">
+        <v>11480.74</v>
+      </c>
+      <c r="S53" s="18" t="n">
+        <v>11480.74</v>
+      </c>
+      <c r="T53" s="18" t="n">
+        <v>11555.1</v>
+      </c>
+      <c r="U53" s="18" t="n">
+        <v>11555.1</v>
+      </c>
+      <c r="V53" s="18" t="n">
+        <v>14160.66</v>
+      </c>
+      <c r="W53" s="37" t="n">
+        <v>14160.66</v>
+      </c>
+      <c r="X53" s="18" t="n">
+        <v>14160.66</v>
+      </c>
       <c r="Y53" s="19" t="n">
-        <v>123207.83</v>
+        <v>12939.38</v>
       </c>
       <c r="Z53" s="10" t="n"/>
       <c r="AA53" s="10" t="n"/>
@@ -19170,15 +19392,37 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>장기금융부채(face)</t>
+          <t>기타포괄이익누계액</t>
         </is>
       </c>
       <c r="H54" s="9" t="n"/>
       <c r="M54" s="9" t="n"/>
-      <c r="R54" s="9" t="n"/>
-      <c r="W54" s="9" t="n"/>
+      <c r="Q54" s="18" t="n">
+        <v>59696.31</v>
+      </c>
+      <c r="R54" s="37" t="n">
+        <v>59696.31</v>
+      </c>
+      <c r="S54" s="18" t="n">
+        <v>59696.31</v>
+      </c>
+      <c r="T54" s="18" t="n">
+        <v>59696.31</v>
+      </c>
+      <c r="U54" s="18" t="n">
+        <v>59696.31</v>
+      </c>
+      <c r="V54" s="18" t="n">
+        <v>55451.44</v>
+      </c>
+      <c r="W54" s="37" t="n">
+        <v>55451.44</v>
+      </c>
+      <c r="X54" s="18" t="n">
+        <v>55451.44</v>
+      </c>
       <c r="Y54" s="19" t="n">
-        <v>0</v>
+        <v>55451.44</v>
       </c>
       <c r="Z54" s="10" t="n"/>
       <c r="AA54" s="10" t="n"/>
@@ -19200,69 +19444,15 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>매출액(수익)</t>
-        </is>
-      </c>
-      <c r="E55" s="18" t="n">
-        <v>14618.22</v>
-      </c>
-      <c r="F55" s="18" t="n">
-        <v>14250.55</v>
-      </c>
-      <c r="G55" s="18" t="n">
-        <v>13316.03</v>
+          <t>단기금융부채(face)</t>
+        </is>
       </c>
       <c r="H55" s="9" t="n"/>
-      <c r="I55" s="18" t="n">
-        <v>8857.17</v>
-      </c>
-      <c r="J55" s="18" t="n">
-        <v>10247.32</v>
-      </c>
-      <c r="K55" s="18" t="n">
-        <v>3960.77</v>
-      </c>
-      <c r="L55" s="18" t="n">
-        <v>7450.42</v>
-      </c>
-      <c r="M55" s="37" t="n">
-        <v>30515.68</v>
-      </c>
-      <c r="N55" s="18" t="n">
-        <v>6719.84</v>
-      </c>
-      <c r="O55" s="18" t="n">
-        <v>9194.01</v>
-      </c>
-      <c r="P55" s="18" t="n">
-        <v>11000.03</v>
-      </c>
-      <c r="Q55" s="18" t="n">
-        <v>9280.799999999999</v>
-      </c>
-      <c r="R55" s="37" t="n">
-        <v>36194.68</v>
-      </c>
-      <c r="S55" s="18" t="n">
-        <v>10446.45</v>
-      </c>
-      <c r="T55" s="18" t="n">
-        <v>7061.17</v>
-      </c>
-      <c r="U55" s="18" t="n">
-        <v>10398.92</v>
-      </c>
-      <c r="V55" s="18" t="n">
-        <v>15454.55</v>
-      </c>
-      <c r="W55" s="37" t="n">
-        <v>43361.09</v>
-      </c>
-      <c r="X55" s="18" t="n">
-        <v>5053.88</v>
-      </c>
+      <c r="M55" s="9" t="n"/>
+      <c r="R55" s="9" t="n"/>
+      <c r="W55" s="9" t="n"/>
       <c r="Y55" s="19" t="n">
-        <v>17824.99</v>
+        <v>123207.83</v>
       </c>
       <c r="Z55" s="10" t="n"/>
       <c r="AA55" s="10" t="n"/>
@@ -19284,69 +19474,15 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>매출원가</t>
-        </is>
-      </c>
-      <c r="E56" s="18" t="n">
-        <v>12331.31</v>
-      </c>
-      <c r="F56" s="18" t="n">
-        <v>12489.73</v>
-      </c>
-      <c r="G56" s="18" t="n">
-        <v>14102.88</v>
+          <t>장기금융부채(face)</t>
+        </is>
       </c>
       <c r="H56" s="9" t="n"/>
-      <c r="I56" s="18" t="n">
-        <v>8001.8</v>
-      </c>
-      <c r="J56" s="18" t="n">
-        <v>10646.51</v>
-      </c>
-      <c r="K56" s="18" t="n">
-        <v>4815.57</v>
-      </c>
-      <c r="L56" s="18" t="n">
-        <v>8731.35</v>
-      </c>
-      <c r="M56" s="37" t="n">
-        <v>32195.23</v>
-      </c>
-      <c r="N56" s="18" t="n">
-        <v>6447.46</v>
-      </c>
-      <c r="O56" s="18" t="n">
-        <v>6693.01</v>
-      </c>
-      <c r="P56" s="18" t="n">
-        <v>8828.98</v>
-      </c>
-      <c r="Q56" s="18" t="n">
-        <v>7973.61</v>
-      </c>
-      <c r="R56" s="37" t="n">
-        <v>29943.06</v>
-      </c>
-      <c r="S56" s="18" t="n">
-        <v>8736.040000000001</v>
-      </c>
-      <c r="T56" s="18" t="n">
-        <v>5738.35</v>
-      </c>
-      <c r="U56" s="18" t="n">
-        <v>8500.41</v>
-      </c>
-      <c r="V56" s="18" t="n">
-        <v>14952.79</v>
-      </c>
-      <c r="W56" s="37" t="n">
-        <v>37927.59</v>
-      </c>
-      <c r="X56" s="18" t="n">
-        <v>6362.33</v>
-      </c>
+      <c r="M56" s="9" t="n"/>
+      <c r="R56" s="9" t="n"/>
+      <c r="W56" s="9" t="n"/>
       <c r="Y56" s="19" t="n">
-        <v>19527.47</v>
+        <v>0</v>
       </c>
       <c r="Z56" s="10" t="n"/>
       <c r="AA56" s="10" t="n"/>
@@ -19368,69 +19504,69 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>매출총이익</t>
+          <t>매출액(수익)</t>
         </is>
       </c>
       <c r="E57" s="18" t="n">
-        <v>2286.91</v>
+        <v>14618.22</v>
       </c>
       <c r="F57" s="18" t="n">
-        <v>1760.83</v>
+        <v>14250.55</v>
       </c>
       <c r="G57" s="18" t="n">
-        <v>-786.86</v>
+        <v>13316.03</v>
       </c>
       <c r="H57" s="9" t="n"/>
       <c r="I57" s="18" t="n">
-        <v>855.36</v>
+        <v>8857.17</v>
       </c>
       <c r="J57" s="18" t="n">
-        <v>-399.19</v>
+        <v>10247.32</v>
       </c>
       <c r="K57" s="18" t="n">
-        <v>-854.8</v>
+        <v>3960.77</v>
       </c>
       <c r="L57" s="18" t="n">
-        <v>-1280.93</v>
+        <v>7450.42</v>
       </c>
       <c r="M57" s="37" t="n">
-        <v>-1679.56</v>
+        <v>30515.68</v>
       </c>
       <c r="N57" s="18" t="n">
-        <v>272.38</v>
+        <v>6719.84</v>
       </c>
       <c r="O57" s="18" t="n">
-        <v>2500.99</v>
+        <v>9194.01</v>
       </c>
       <c r="P57" s="18" t="n">
-        <v>2171.05</v>
+        <v>11000.03</v>
       </c>
       <c r="Q57" s="18" t="n">
-        <v>1307.2</v>
+        <v>9280.799999999999</v>
       </c>
       <c r="R57" s="37" t="n">
-        <v>6251.62</v>
+        <v>36194.68</v>
       </c>
       <c r="S57" s="18" t="n">
-        <v>1710.41</v>
+        <v>10446.45</v>
       </c>
       <c r="T57" s="18" t="n">
-        <v>1322.81</v>
+        <v>7061.17</v>
       </c>
       <c r="U57" s="18" t="n">
-        <v>1898.51</v>
+        <v>10398.92</v>
       </c>
       <c r="V57" s="18" t="n">
-        <v>501.76</v>
+        <v>15454.55</v>
       </c>
       <c r="W57" s="37" t="n">
-        <v>5433.49</v>
+        <v>43361.09</v>
       </c>
       <c r="X57" s="18" t="n">
-        <v>-1308.45</v>
+        <v>5053.88</v>
       </c>
       <c r="Y57" s="19" t="n">
-        <v>-1702.47</v>
+        <v>17824.99</v>
       </c>
       <c r="Z57" s="10" t="n"/>
       <c r="AA57" s="10" t="n"/>
@@ -19452,69 +19588,69 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>판관비</t>
+          <t>매출원가</t>
         </is>
       </c>
       <c r="E58" s="18" t="n">
-        <v>1357.12</v>
+        <v>12331.31</v>
       </c>
       <c r="F58" s="18" t="n">
-        <v>742.53</v>
+        <v>12489.73</v>
       </c>
       <c r="G58" s="18" t="n">
-        <v>1004.27</v>
+        <v>14102.88</v>
       </c>
       <c r="H58" s="9" t="n"/>
       <c r="I58" s="18" t="n">
-        <v>755.28</v>
+        <v>8001.8</v>
       </c>
       <c r="J58" s="18" t="n">
-        <v>986.3099999999999</v>
+        <v>10646.51</v>
       </c>
       <c r="K58" s="18" t="n">
-        <v>1053.68</v>
+        <v>4815.57</v>
       </c>
       <c r="L58" s="18" t="n">
-        <v>571.29</v>
+        <v>8731.35</v>
       </c>
       <c r="M58" s="37" t="n">
-        <v>3366.56</v>
+        <v>32195.23</v>
       </c>
       <c r="N58" s="18" t="n">
-        <v>775.45</v>
+        <v>6447.46</v>
       </c>
       <c r="O58" s="18" t="n">
-        <v>722.48</v>
+        <v>6693.01</v>
       </c>
       <c r="P58" s="18" t="n">
-        <v>575.24</v>
+        <v>8828.98</v>
       </c>
       <c r="Q58" s="18" t="n">
-        <v>921.61</v>
+        <v>7973.61</v>
       </c>
       <c r="R58" s="37" t="n">
-        <v>2994.78</v>
+        <v>29943.06</v>
       </c>
       <c r="S58" s="18" t="n">
-        <v>757.99</v>
+        <v>8736.040000000001</v>
       </c>
       <c r="T58" s="18" t="n">
-        <v>820.71</v>
+        <v>5738.35</v>
       </c>
       <c r="U58" s="18" t="n">
-        <v>702.8</v>
+        <v>8500.41</v>
       </c>
       <c r="V58" s="18" t="n">
-        <v>855.3200000000001</v>
+        <v>14952.79</v>
       </c>
       <c r="W58" s="37" t="n">
-        <v>3136.82</v>
+        <v>37927.59</v>
       </c>
       <c r="X58" s="18" t="n">
-        <v>755.96</v>
+        <v>6362.33</v>
       </c>
       <c r="Y58" s="19" t="n">
-        <v>851.85</v>
+        <v>19527.47</v>
       </c>
       <c r="Z58" s="10" t="n"/>
       <c r="AA58" s="10" t="n"/>
@@ -19536,69 +19672,69 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>영업이익</t>
+          <t>매출총이익</t>
         </is>
       </c>
       <c r="E59" s="18" t="n">
-        <v>929.79</v>
+        <v>2286.91</v>
       </c>
       <c r="F59" s="18" t="n">
-        <v>1018.3</v>
+        <v>1760.83</v>
       </c>
       <c r="G59" s="18" t="n">
-        <v>-1791.12</v>
+        <v>-786.86</v>
       </c>
       <c r="H59" s="9" t="n"/>
       <c r="I59" s="18" t="n">
-        <v>100.09</v>
+        <v>855.36</v>
       </c>
       <c r="J59" s="18" t="n">
-        <v>-1385.5</v>
+        <v>-399.19</v>
       </c>
       <c r="K59" s="18" t="n">
-        <v>-1908.48</v>
+        <v>-854.8</v>
       </c>
       <c r="L59" s="18" t="n">
-        <v>-1852.22</v>
+        <v>-1280.93</v>
       </c>
       <c r="M59" s="37" t="n">
-        <v>-5046.11</v>
+        <v>-1679.56</v>
       </c>
       <c r="N59" s="18" t="n">
-        <v>-503.08</v>
+        <v>272.38</v>
       </c>
       <c r="O59" s="18" t="n">
-        <v>1778.52</v>
+        <v>2500.99</v>
       </c>
       <c r="P59" s="18" t="n">
-        <v>1595.81</v>
+        <v>2171.05</v>
       </c>
       <c r="Q59" s="18" t="n">
-        <v>385.58</v>
+        <v>1307.2</v>
       </c>
       <c r="R59" s="37" t="n">
-        <v>3256.83</v>
+        <v>6251.62</v>
       </c>
       <c r="S59" s="18" t="n">
-        <v>952.4299999999999</v>
+        <v>1710.41</v>
       </c>
       <c r="T59" s="18" t="n">
-        <v>502.1</v>
+        <v>1322.81</v>
       </c>
       <c r="U59" s="18" t="n">
-        <v>1195.71</v>
+        <v>1898.51</v>
       </c>
       <c r="V59" s="18" t="n">
-        <v>-353.57</v>
+        <v>501.76</v>
       </c>
       <c r="W59" s="37" t="n">
-        <v>2296.67</v>
+        <v>5433.49</v>
       </c>
       <c r="X59" s="18" t="n">
-        <v>-2064.41</v>
+        <v>-1308.45</v>
       </c>
       <c r="Y59" s="19" t="n">
-        <v>-2554.32</v>
+        <v>-1702.47</v>
       </c>
       <c r="Z59" s="10" t="n"/>
       <c r="AA59" s="10" t="n"/>
@@ -19620,69 +19756,69 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>금융수익</t>
+          <t>판관비</t>
         </is>
       </c>
       <c r="E60" s="18" t="n">
-        <v>27.46</v>
+        <v>1357.12</v>
       </c>
       <c r="F60" s="18" t="n">
-        <v>1164.81</v>
+        <v>742.53</v>
       </c>
       <c r="G60" s="18" t="n">
-        <v>264.42</v>
+        <v>1004.27</v>
       </c>
       <c r="H60" s="9" t="n"/>
       <c r="I60" s="18" t="n">
-        <v>829.59</v>
+        <v>755.28</v>
       </c>
       <c r="J60" s="18" t="n">
-        <v>577.14</v>
+        <v>986.3099999999999</v>
       </c>
       <c r="K60" s="18" t="n">
-        <v>502.66</v>
+        <v>1053.68</v>
       </c>
       <c r="L60" s="18" t="n">
-        <v>501.33</v>
+        <v>571.29</v>
       </c>
       <c r="M60" s="37" t="n">
-        <v>2410.72</v>
+        <v>3366.56</v>
       </c>
       <c r="N60" s="18" t="n">
-        <v>386.53</v>
+        <v>775.45</v>
       </c>
       <c r="O60" s="18" t="n">
-        <v>250.95</v>
+        <v>722.48</v>
       </c>
       <c r="P60" s="18" t="n">
-        <v>321.1</v>
+        <v>575.24</v>
       </c>
       <c r="Q60" s="18" t="n">
-        <v>740.97</v>
+        <v>921.61</v>
       </c>
       <c r="R60" s="37" t="n">
-        <v>1699.55</v>
+        <v>2994.78</v>
       </c>
       <c r="S60" s="18" t="n">
-        <v>525.6</v>
+        <v>757.99</v>
       </c>
       <c r="T60" s="18" t="n">
-        <v>559.24</v>
+        <v>820.71</v>
       </c>
       <c r="U60" s="18" t="n">
-        <v>515.7</v>
+        <v>702.8</v>
       </c>
       <c r="V60" s="18" t="n">
-        <v>6310.63</v>
+        <v>855.3200000000001</v>
       </c>
       <c r="W60" s="37" t="n">
-        <v>7911.17</v>
+        <v>3136.82</v>
       </c>
       <c r="X60" s="18" t="n">
-        <v>559.8200000000001</v>
+        <v>755.96</v>
       </c>
       <c r="Y60" s="19" t="n">
-        <v>1103.7</v>
+        <v>851.85</v>
       </c>
       <c r="Z60" s="10" t="n"/>
       <c r="AA60" s="10" t="n"/>
@@ -19704,69 +19840,69 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>금융비용</t>
+          <t>영업이익</t>
         </is>
       </c>
       <c r="E61" s="18" t="n">
-        <v>49.68</v>
+        <v>929.79</v>
       </c>
       <c r="F61" s="18" t="n">
-        <v>67.2</v>
+        <v>1018.3</v>
       </c>
       <c r="G61" s="18" t="n">
-        <v>45.63</v>
+        <v>-1791.12</v>
       </c>
       <c r="H61" s="9" t="n"/>
       <c r="I61" s="18" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="J61" s="18" t="n">
-        <v>84.34999999999999</v>
+        <v>-1385.5</v>
       </c>
       <c r="K61" s="18" t="n">
-        <v>92.44</v>
+        <v>-1908.48</v>
       </c>
       <c r="L61" s="18" t="n">
-        <v>93.06</v>
+        <v>-1852.22</v>
       </c>
       <c r="M61" s="37" t="n">
-        <v>335.52</v>
+        <v>-5046.11</v>
       </c>
       <c r="N61" s="18" t="n">
-        <v>397.65</v>
+        <v>-503.08</v>
       </c>
       <c r="O61" s="18" t="n">
-        <v>961</v>
+        <v>1778.52</v>
       </c>
       <c r="P61" s="18" t="n">
-        <v>976.61</v>
+        <v>1595.81</v>
       </c>
       <c r="Q61" s="18" t="n">
-        <v>1702.75</v>
+        <v>385.58</v>
       </c>
       <c r="R61" s="37" t="n">
-        <v>4038.01</v>
+        <v>3256.83</v>
       </c>
       <c r="S61" s="18" t="n">
-        <v>1230.89</v>
+        <v>952.4299999999999</v>
       </c>
       <c r="T61" s="18" t="n">
-        <v>1149.21</v>
+        <v>502.1</v>
       </c>
       <c r="U61" s="18" t="n">
-        <v>1089.08</v>
+        <v>1195.71</v>
       </c>
       <c r="V61" s="18" t="n">
-        <v>4040.45</v>
+        <v>-353.57</v>
       </c>
       <c r="W61" s="37" t="n">
-        <v>7509.63</v>
+        <v>2296.67</v>
       </c>
       <c r="X61" s="18" t="n">
-        <v>1607.99</v>
+        <v>-2064.41</v>
       </c>
       <c r="Y61" s="19" t="n">
-        <v>1885.45</v>
+        <v>-2554.32</v>
       </c>
       <c r="Z61" s="10" t="n"/>
       <c r="AA61" s="10" t="n"/>
@@ -19788,69 +19924,69 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>기타영업외수익</t>
+          <t>금융수익</t>
         </is>
       </c>
       <c r="E62" s="18" t="n">
-        <v>10.22</v>
+        <v>27.46</v>
       </c>
       <c r="F62" s="18" t="n">
-        <v>86.06999999999999</v>
+        <v>1164.81</v>
       </c>
       <c r="G62" s="18" t="n">
-        <v>125.49</v>
+        <v>264.42</v>
       </c>
       <c r="H62" s="9" t="n"/>
       <c r="I62" s="18" t="n">
-        <v>33.6</v>
+        <v>829.59</v>
       </c>
       <c r="J62" s="18" t="n">
-        <v>52.36</v>
+        <v>577.14</v>
       </c>
       <c r="K62" s="18" t="n">
-        <v>68.69</v>
+        <v>502.66</v>
       </c>
       <c r="L62" s="18" t="n">
-        <v>29.36</v>
+        <v>501.33</v>
       </c>
       <c r="M62" s="37" t="n">
-        <v>184.01</v>
+        <v>2410.72</v>
       </c>
       <c r="N62" s="18" t="n">
-        <v>31.9</v>
+        <v>386.53</v>
       </c>
       <c r="O62" s="18" t="n">
-        <v>72</v>
+        <v>250.95</v>
       </c>
       <c r="P62" s="18" t="n">
-        <v>15</v>
+        <v>321.1</v>
       </c>
       <c r="Q62" s="18" t="n">
-        <v>64.42</v>
+        <v>740.97</v>
       </c>
       <c r="R62" s="37" t="n">
-        <v>183.32</v>
+        <v>1699.55</v>
       </c>
       <c r="S62" s="18" t="n">
-        <v>6.11</v>
+        <v>525.6</v>
       </c>
       <c r="T62" s="18" t="n">
-        <v>22.84</v>
+        <v>559.24</v>
       </c>
       <c r="U62" s="18" t="n">
-        <v>18.78</v>
+        <v>515.7</v>
       </c>
       <c r="V62" s="18" t="n">
-        <v>19.39</v>
+        <v>6310.63</v>
       </c>
       <c r="W62" s="37" t="n">
-        <v>67.12</v>
+        <v>7911.17</v>
       </c>
       <c r="X62" s="18" t="n">
-        <v>1611.55</v>
+        <v>559.8200000000001</v>
       </c>
       <c r="Y62" s="19" t="n">
-        <v>-1144.73</v>
+        <v>1103.7</v>
       </c>
       <c r="Z62" s="10" t="n"/>
       <c r="AA62" s="10" t="n"/>
@@ -19872,69 +20008,69 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>기타영업외비용</t>
+          <t>금융비용</t>
         </is>
       </c>
       <c r="E63" s="18" t="n">
-        <v>135.28</v>
+        <v>49.68</v>
       </c>
       <c r="F63" s="18" t="n">
-        <v>241.17</v>
+        <v>67.2</v>
       </c>
       <c r="G63" s="18" t="n">
-        <v>63.92</v>
+        <v>45.63</v>
       </c>
       <c r="H63" s="9" t="n"/>
       <c r="I63" s="18" t="n">
-        <v>167.14</v>
+        <v>65.67</v>
       </c>
       <c r="J63" s="18" t="n">
-        <v>73.73999999999999</v>
+        <v>84.34999999999999</v>
       </c>
       <c r="K63" s="18" t="n">
-        <v>44.75</v>
+        <v>92.44</v>
       </c>
       <c r="L63" s="18" t="n">
-        <v>84.42</v>
+        <v>93.06</v>
       </c>
       <c r="M63" s="37" t="n">
-        <v>370.05</v>
+        <v>335.52</v>
       </c>
       <c r="N63" s="18" t="n">
-        <v>16.99</v>
+        <v>397.65</v>
       </c>
       <c r="O63" s="18" t="n">
-        <v>59.23</v>
+        <v>961</v>
       </c>
       <c r="P63" s="18" t="n">
-        <v>10.19</v>
+        <v>976.61</v>
       </c>
       <c r="Q63" s="18" t="n">
-        <v>20.97</v>
+        <v>1702.75</v>
       </c>
       <c r="R63" s="37" t="n">
-        <v>107.38</v>
+        <v>4038.01</v>
       </c>
       <c r="S63" s="18" t="n">
-        <v>61.13</v>
+        <v>1230.89</v>
       </c>
       <c r="T63" s="18" t="n">
-        <v>23.29</v>
+        <v>1149.21</v>
       </c>
       <c r="U63" s="18" t="n">
-        <v>45.79</v>
+        <v>1089.08</v>
       </c>
       <c r="V63" s="18" t="n">
-        <v>94.84999999999999</v>
+        <v>4040.45</v>
       </c>
       <c r="W63" s="37" t="n">
-        <v>225.06</v>
+        <v>7509.63</v>
       </c>
       <c r="X63" s="18" t="n">
-        <v>88.53</v>
+        <v>1607.99</v>
       </c>
       <c r="Y63" s="19" t="n">
-        <v>17.93</v>
+        <v>1885.45</v>
       </c>
       <c r="Z63" s="10" t="n"/>
       <c r="AA63" s="10" t="n"/>
@@ -19956,69 +20092,69 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>법인세비용차감전계속사업이익</t>
+          <t>기타영업외수익</t>
         </is>
       </c>
       <c r="E64" s="18" t="n">
-        <v>782.51</v>
+        <v>10.22</v>
       </c>
       <c r="F64" s="18" t="n">
-        <v>1960.81</v>
+        <v>86.06999999999999</v>
       </c>
       <c r="G64" s="18" t="n">
-        <v>-1510.76</v>
+        <v>125.49</v>
       </c>
       <c r="H64" s="9" t="n"/>
       <c r="I64" s="18" t="n">
-        <v>730.48</v>
+        <v>33.6</v>
       </c>
       <c r="J64" s="18" t="n">
-        <v>-914.1</v>
+        <v>52.36</v>
       </c>
       <c r="K64" s="18" t="n">
-        <v>-1474.32</v>
+        <v>68.69</v>
       </c>
       <c r="L64" s="18" t="n">
-        <v>-1499.01</v>
+        <v>29.36</v>
       </c>
       <c r="M64" s="37" t="n">
-        <v>-3156.95</v>
+        <v>184.01</v>
       </c>
       <c r="N64" s="18" t="n">
-        <v>-499.29</v>
+        <v>31.9</v>
       </c>
       <c r="O64" s="18" t="n">
-        <v>1081.23</v>
+        <v>72</v>
       </c>
       <c r="P64" s="18" t="n">
-        <v>945.12</v>
+        <v>15</v>
       </c>
       <c r="Q64" s="18" t="n">
-        <v>-532.73</v>
+        <v>64.42</v>
       </c>
       <c r="R64" s="37" t="n">
-        <v>994.33</v>
+        <v>183.32</v>
       </c>
       <c r="S64" s="18" t="n">
-        <v>192.11</v>
+        <v>6.11</v>
       </c>
       <c r="T64" s="18" t="n">
-        <v>-88.31999999999999</v>
+        <v>22.84</v>
       </c>
       <c r="U64" s="18" t="n">
-        <v>595.33</v>
+        <v>18.78</v>
       </c>
       <c r="V64" s="18" t="n">
-        <v>1841.14</v>
+        <v>19.39</v>
       </c>
       <c r="W64" s="37" t="n">
-        <v>2540.26</v>
+        <v>67.12</v>
       </c>
       <c r="X64" s="18" t="n">
-        <v>-1589.56</v>
+        <v>1611.55</v>
       </c>
       <c r="Y64" s="19" t="n">
-        <v>-4498.72</v>
+        <v>-1144.73</v>
       </c>
       <c r="Z64" s="10" t="n"/>
       <c r="AA64" s="10" t="n"/>
@@ -20040,69 +20176,69 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>법인세비용</t>
+          <t>기타영업외비용</t>
         </is>
       </c>
       <c r="E65" s="18" t="n">
-        <v>126.12</v>
+        <v>135.28</v>
       </c>
       <c r="F65" s="18" t="n">
-        <v>556.6900000000001</v>
+        <v>241.17</v>
       </c>
       <c r="G65" s="18" t="n">
-        <v>-763.98</v>
+        <v>63.92</v>
       </c>
       <c r="H65" s="9" t="n"/>
       <c r="I65" s="18" t="n">
-        <v>141.34</v>
+        <v>167.14</v>
       </c>
       <c r="J65" s="18" t="n">
-        <v>-514.41</v>
+        <v>73.73999999999999</v>
       </c>
       <c r="K65" s="18" t="n">
-        <v>0</v>
+        <v>44.75</v>
       </c>
       <c r="L65" s="18" t="n">
-        <v>-542.73</v>
+        <v>84.42</v>
       </c>
       <c r="M65" s="37" t="n">
-        <v>-915.8</v>
+        <v>370.05</v>
       </c>
       <c r="N65" s="18" t="n">
-        <v>0</v>
+        <v>16.99</v>
       </c>
       <c r="O65" s="18" t="n">
-        <v>133.04</v>
+        <v>59.23</v>
       </c>
       <c r="P65" s="18" t="n">
-        <v>0</v>
+        <v>10.19</v>
       </c>
       <c r="Q65" s="18" t="n">
-        <v>-478.9</v>
+        <v>20.97</v>
       </c>
       <c r="R65" s="37" t="n">
-        <v>-345.86</v>
+        <v>107.38</v>
       </c>
       <c r="S65" s="18" t="n">
-        <v>0</v>
+        <v>61.13</v>
       </c>
       <c r="T65" s="18" t="n">
-        <v>74.37</v>
+        <v>23.29</v>
       </c>
       <c r="U65" s="18" t="n">
-        <v>0</v>
+        <v>45.79</v>
       </c>
       <c r="V65" s="18" t="n">
-        <v>-109.42</v>
+        <v>94.84999999999999</v>
       </c>
       <c r="W65" s="37" t="n">
-        <v>-35.05</v>
+        <v>225.06</v>
       </c>
       <c r="X65" s="18" t="n">
-        <v>0</v>
+        <v>88.53</v>
       </c>
       <c r="Y65" s="19" t="n">
-        <v>-1198.64</v>
+        <v>17.93</v>
       </c>
       <c r="Z65" s="10" t="n"/>
       <c r="AA65" s="10" t="n"/>
@@ -20124,69 +20260,69 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>당기순이익</t>
+          <t>법인세비용차감전계속사업이익</t>
         </is>
       </c>
       <c r="E66" s="18" t="n">
-        <v>656.39</v>
+        <v>782.51</v>
       </c>
       <c r="F66" s="18" t="n">
-        <v>1404.11</v>
+        <v>1960.81</v>
       </c>
       <c r="G66" s="18" t="n">
-        <v>-746.78</v>
+        <v>-1510.76</v>
       </c>
       <c r="H66" s="9" t="n"/>
       <c r="I66" s="18" t="n">
-        <v>589.14</v>
+        <v>730.48</v>
       </c>
       <c r="J66" s="18" t="n">
-        <v>-399.69</v>
+        <v>-914.1</v>
       </c>
       <c r="K66" s="18" t="n">
         <v>-1474.32</v>
       </c>
       <c r="L66" s="18" t="n">
-        <v>-956.28</v>
+        <v>-1499.01</v>
       </c>
       <c r="M66" s="37" t="n">
-        <v>-2241.15</v>
+        <v>-3156.95</v>
       </c>
       <c r="N66" s="18" t="n">
         <v>-499.29</v>
       </c>
       <c r="O66" s="18" t="n">
-        <v>948.1900000000001</v>
+        <v>1081.23</v>
       </c>
       <c r="P66" s="18" t="n">
         <v>945.12</v>
       </c>
       <c r="Q66" s="18" t="n">
-        <v>-53.83</v>
+        <v>-532.73</v>
       </c>
       <c r="R66" s="37" t="n">
-        <v>1340.19</v>
+        <v>994.33</v>
       </c>
       <c r="S66" s="18" t="n">
         <v>192.11</v>
       </c>
       <c r="T66" s="18" t="n">
-        <v>-162.69</v>
+        <v>-88.31999999999999</v>
       </c>
       <c r="U66" s="18" t="n">
         <v>595.33</v>
       </c>
       <c r="V66" s="18" t="n">
-        <v>1950.57</v>
+        <v>1841.14</v>
       </c>
       <c r="W66" s="37" t="n">
-        <v>2575.32</v>
+        <v>2540.26</v>
       </c>
       <c r="X66" s="18" t="n">
         <v>-1589.56</v>
       </c>
       <c r="Y66" s="19" t="n">
-        <v>-3300.08</v>
+        <v>-4498.72</v>
       </c>
       <c r="Z66" s="10" t="n"/>
       <c r="AA66" s="10" t="n"/>
@@ -20208,69 +20344,69 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>총포괄손익</t>
+          <t>법인세비용</t>
         </is>
       </c>
       <c r="E67" s="18" t="n">
-        <v>656.39</v>
+        <v>126.12</v>
       </c>
       <c r="F67" s="18" t="n">
-        <v>1404.11</v>
+        <v>556.6900000000001</v>
       </c>
       <c r="G67" s="18" t="n">
-        <v>-457.25</v>
+        <v>-763.98</v>
       </c>
       <c r="H67" s="9" t="n"/>
       <c r="I67" s="18" t="n">
-        <v>589.14</v>
+        <v>141.34</v>
       </c>
       <c r="J67" s="18" t="n">
-        <v>-399.69</v>
+        <v>-514.41</v>
       </c>
       <c r="K67" s="18" t="n">
-        <v>-1474.32</v>
+        <v>0</v>
       </c>
       <c r="L67" s="18" t="n">
-        <v>-999.1</v>
+        <v>-542.73</v>
       </c>
       <c r="M67" s="37" t="n">
-        <v>-2283.97</v>
+        <v>-915.8</v>
       </c>
       <c r="N67" s="18" t="n">
-        <v>-499.29</v>
+        <v>0</v>
       </c>
       <c r="O67" s="18" t="n">
-        <v>948.1900000000001</v>
+        <v>133.04</v>
       </c>
       <c r="P67" s="18" t="n">
-        <v>945.12</v>
+        <v>0</v>
       </c>
       <c r="Q67" s="18" t="n">
-        <v>59252.09</v>
+        <v>-478.9</v>
       </c>
       <c r="R67" s="37" t="n">
-        <v>60646.11</v>
+        <v>-345.86</v>
       </c>
       <c r="S67" s="18" t="n">
-        <v>192.11</v>
+        <v>0</v>
       </c>
       <c r="T67" s="18" t="n">
-        <v>-162.69</v>
+        <v>74.37</v>
       </c>
       <c r="U67" s="18" t="n">
-        <v>595.33</v>
+        <v>0</v>
       </c>
       <c r="V67" s="18" t="n">
-        <v>-2389.8</v>
+        <v>-109.42</v>
       </c>
       <c r="W67" s="37" t="n">
-        <v>-1765.05</v>
+        <v>-35.05</v>
       </c>
       <c r="X67" s="18" t="n">
-        <v>-1589.56</v>
+        <v>0</v>
       </c>
       <c r="Y67" s="19" t="n">
-        <v>-3300.08</v>
+        <v>-1198.64</v>
       </c>
       <c r="Z67" s="10" t="n"/>
       <c r="AA67" s="10" t="n"/>
@@ -20292,69 +20428,69 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>금융손익</t>
+          <t>당기순이익</t>
         </is>
       </c>
       <c r="E68" s="18" t="n">
-        <v>-22.22</v>
+        <v>656.39</v>
       </c>
       <c r="F68" s="18" t="n">
-        <v>1097.61</v>
+        <v>1404.11</v>
       </c>
       <c r="G68" s="18" t="n">
-        <v>218.79</v>
+        <v>-746.78</v>
       </c>
       <c r="H68" s="9" t="n"/>
       <c r="I68" s="18" t="n">
-        <v>763.92</v>
+        <v>589.14</v>
       </c>
       <c r="J68" s="18" t="n">
-        <v>492.79</v>
+        <v>-399.69</v>
       </c>
       <c r="K68" s="18" t="n">
-        <v>410.22</v>
+        <v>-1474.32</v>
       </c>
       <c r="L68" s="18" t="n">
-        <v>408.27</v>
+        <v>-956.28</v>
       </c>
       <c r="M68" s="37" t="n">
-        <v>2075.2</v>
+        <v>-2241.15</v>
       </c>
       <c r="N68" s="18" t="n">
-        <v>-11.12</v>
+        <v>-499.29</v>
       </c>
       <c r="O68" s="18" t="n">
-        <v>-710.05</v>
+        <v>948.1900000000001</v>
       </c>
       <c r="P68" s="18" t="n">
-        <v>-655.51</v>
+        <v>945.12</v>
       </c>
       <c r="Q68" s="18" t="n">
-        <v>-961.78</v>
+        <v>-53.83</v>
       </c>
       <c r="R68" s="37" t="n">
-        <v>-2338.46</v>
+        <v>1340.19</v>
       </c>
       <c r="S68" s="18" t="n">
-        <v>-705.29</v>
+        <v>192.11</v>
       </c>
       <c r="T68" s="18" t="n">
-        <v>-589.97</v>
+        <v>-162.69</v>
       </c>
       <c r="U68" s="18" t="n">
-        <v>-573.38</v>
+        <v>595.33</v>
       </c>
       <c r="V68" s="18" t="n">
-        <v>2270.18</v>
+        <v>1950.57</v>
       </c>
       <c r="W68" s="37" t="n">
-        <v>401.54</v>
+        <v>2575.32</v>
       </c>
       <c r="X68" s="18" t="n">
-        <v>-1048.17</v>
+        <v>-1589.56</v>
       </c>
       <c r="Y68" s="19" t="n">
-        <v>-781.75</v>
+        <v>-3300.08</v>
       </c>
       <c r="Z68" s="10" t="n"/>
       <c r="AA68" s="10" t="n"/>
@@ -20376,69 +20512,69 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>기타영업외손익</t>
+          <t>총포괄손익</t>
         </is>
       </c>
       <c r="E69" s="18" t="n">
-        <v>-125.06</v>
+        <v>656.39</v>
       </c>
       <c r="F69" s="18" t="n">
-        <v>-155.1</v>
+        <v>1404.11</v>
       </c>
       <c r="G69" s="18" t="n">
-        <v>61.57</v>
+        <v>-457.25</v>
       </c>
       <c r="H69" s="9" t="n"/>
       <c r="I69" s="18" t="n">
-        <v>-133.54</v>
+        <v>589.14</v>
       </c>
       <c r="J69" s="18" t="n">
-        <v>-21.38</v>
+        <v>-399.69</v>
       </c>
       <c r="K69" s="18" t="n">
-        <v>23.94</v>
+        <v>-1474.32</v>
       </c>
       <c r="L69" s="18" t="n">
-        <v>-55.06</v>
+        <v>-999.1</v>
       </c>
       <c r="M69" s="37" t="n">
-        <v>-186.04</v>
+        <v>-2283.97</v>
       </c>
       <c r="N69" s="18" t="n">
-        <v>14.91</v>
+        <v>-499.29</v>
       </c>
       <c r="O69" s="18" t="n">
-        <v>12.77</v>
+        <v>948.1900000000001</v>
       </c>
       <c r="P69" s="18" t="n">
-        <v>4.81</v>
+        <v>945.12</v>
       </c>
       <c r="Q69" s="18" t="n">
-        <v>43.45</v>
+        <v>59252.09</v>
       </c>
       <c r="R69" s="37" t="n">
-        <v>75.94</v>
+        <v>60646.11</v>
       </c>
       <c r="S69" s="18" t="n">
-        <v>-55.02</v>
+        <v>192.11</v>
       </c>
       <c r="T69" s="18" t="n">
-        <v>-0.45</v>
+        <v>-162.69</v>
       </c>
       <c r="U69" s="18" t="n">
-        <v>-27.01</v>
+        <v>595.33</v>
       </c>
       <c r="V69" s="18" t="n">
-        <v>-75.45999999999999</v>
+        <v>-2389.8</v>
       </c>
       <c r="W69" s="37" t="n">
-        <v>-157.94</v>
+        <v>-1765.05</v>
       </c>
       <c r="X69" s="18" t="n">
-        <v>1523.02</v>
+        <v>-1589.56</v>
       </c>
       <c r="Y69" s="19" t="n">
-        <v>-1162.66</v>
+        <v>-3300.08</v>
       </c>
       <c r="Z69" s="10" t="n"/>
       <c r="AA69" s="10" t="n"/>
@@ -20460,69 +20596,69 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>(지배주주지분)당기순이익</t>
+          <t>금융손익</t>
         </is>
       </c>
       <c r="E70" s="18" t="n">
-        <v>656.39</v>
+        <v>-22.22</v>
       </c>
       <c r="F70" s="18" t="n">
-        <v>1404.11</v>
+        <v>1097.61</v>
       </c>
       <c r="G70" s="18" t="n">
-        <v>-746.78</v>
+        <v>218.79</v>
       </c>
       <c r="H70" s="9" t="n"/>
       <c r="I70" s="18" t="n">
-        <v>589.14</v>
+        <v>763.92</v>
       </c>
       <c r="J70" s="18" t="n">
-        <v>-399.69</v>
+        <v>492.79</v>
       </c>
       <c r="K70" s="18" t="n">
-        <v>-1474.32</v>
+        <v>410.22</v>
       </c>
       <c r="L70" s="18" t="n">
-        <v>-956.28</v>
+        <v>408.27</v>
       </c>
       <c r="M70" s="37" t="n">
-        <v>-2241.15</v>
+        <v>2075.2</v>
       </c>
       <c r="N70" s="18" t="n">
-        <v>-499.29</v>
+        <v>-11.12</v>
       </c>
       <c r="O70" s="18" t="n">
-        <v>948.1900000000001</v>
+        <v>-710.05</v>
       </c>
       <c r="P70" s="18" t="n">
-        <v>945.12</v>
+        <v>-655.51</v>
       </c>
       <c r="Q70" s="18" t="n">
-        <v>-53.83</v>
+        <v>-961.78</v>
       </c>
       <c r="R70" s="37" t="n">
-        <v>1340.19</v>
+        <v>-2338.46</v>
       </c>
       <c r="S70" s="18" t="n">
-        <v>192.11</v>
+        <v>-705.29</v>
       </c>
       <c r="T70" s="18" t="n">
-        <v>-162.69</v>
+        <v>-589.97</v>
       </c>
       <c r="U70" s="18" t="n">
-        <v>595.33</v>
+        <v>-573.38</v>
       </c>
       <c r="V70" s="18" t="n">
-        <v>1950.57</v>
+        <v>2270.18</v>
       </c>
       <c r="W70" s="37" t="n">
-        <v>2575.32</v>
+        <v>401.54</v>
       </c>
       <c r="X70" s="18" t="n">
-        <v>-1589.56</v>
+        <v>-1048.17</v>
       </c>
       <c r="Y70" s="19" t="n">
-        <v>-3300.08</v>
+        <v>-781.75</v>
       </c>
       <c r="Z70" s="10" t="n"/>
       <c r="AA70" s="10" t="n"/>
@@ -20544,69 +20680,69 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>계속사업이익</t>
+          <t>기타영업외손익</t>
         </is>
       </c>
       <c r="E71" s="18" t="n">
-        <v>656.39</v>
+        <v>-125.06</v>
       </c>
       <c r="F71" s="18" t="n">
-        <v>1404.11</v>
+        <v>-155.1</v>
       </c>
       <c r="G71" s="18" t="n">
-        <v>-746.78</v>
+        <v>61.57</v>
       </c>
       <c r="H71" s="9" t="n"/>
       <c r="I71" s="18" t="n">
-        <v>589.14</v>
+        <v>-133.54</v>
       </c>
       <c r="J71" s="18" t="n">
-        <v>-399.69</v>
+        <v>-21.38</v>
       </c>
       <c r="K71" s="18" t="n">
-        <v>-1474.32</v>
+        <v>23.94</v>
       </c>
       <c r="L71" s="18" t="n">
-        <v>-956.28</v>
+        <v>-55.06</v>
       </c>
       <c r="M71" s="37" t="n">
-        <v>-2241.15</v>
+        <v>-186.04</v>
       </c>
       <c r="N71" s="18" t="n">
-        <v>-499.29</v>
+        <v>14.91</v>
       </c>
       <c r="O71" s="18" t="n">
-        <v>948.1900000000001</v>
+        <v>12.77</v>
       </c>
       <c r="P71" s="18" t="n">
-        <v>945.12</v>
+        <v>4.81</v>
       </c>
       <c r="Q71" s="18" t="n">
-        <v>-53.83</v>
+        <v>43.45</v>
       </c>
       <c r="R71" s="37" t="n">
-        <v>1340.19</v>
+        <v>75.94</v>
       </c>
       <c r="S71" s="18" t="n">
-        <v>192.11</v>
+        <v>-55.02</v>
       </c>
       <c r="T71" s="18" t="n">
-        <v>-162.69</v>
+        <v>-0.45</v>
       </c>
       <c r="U71" s="18" t="n">
-        <v>595.33</v>
+        <v>-27.01</v>
       </c>
       <c r="V71" s="18" t="n">
-        <v>1950.57</v>
+        <v>-75.45999999999999</v>
       </c>
       <c r="W71" s="37" t="n">
-        <v>2575.32</v>
+        <v>-157.94</v>
       </c>
       <c r="X71" s="18" t="n">
-        <v>-1589.56</v>
+        <v>1523.02</v>
       </c>
       <c r="Y71" s="19" t="n">
-        <v>-3300.08</v>
+        <v>-1162.66</v>
       </c>
       <c r="Z71" s="10" t="n"/>
       <c r="AA71" s="10" t="n"/>
@@ -20628,32 +20764,70 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>이자수익</t>
+          <t>(지배주주지분)당기순이익</t>
         </is>
       </c>
       <c r="E72" s="18" t="n">
-        <v>27.46</v>
+        <v>656.39</v>
       </c>
       <c r="F72" s="18" t="n">
-        <v>1164.81</v>
+        <v>1404.11</v>
       </c>
       <c r="G72" s="18" t="n">
-        <v>258.66</v>
+        <v>-746.78</v>
       </c>
       <c r="H72" s="9" t="n"/>
       <c r="I72" s="18" t="n">
-        <v>810.0599999999999</v>
+        <v>589.14</v>
       </c>
       <c r="J72" s="18" t="n">
-        <v>577.14</v>
+        <v>-399.69</v>
       </c>
       <c r="K72" s="18" t="n">
-        <v>502.66</v>
-      </c>
-      <c r="M72" s="9" t="n"/>
-      <c r="R72" s="9" t="n"/>
-      <c r="W72" s="9" t="n"/>
-      <c r="Y72" s="5" t="n"/>
+        <v>-1474.32</v>
+      </c>
+      <c r="L72" s="18" t="n">
+        <v>-956.28</v>
+      </c>
+      <c r="M72" s="37" t="n">
+        <v>-2241.15</v>
+      </c>
+      <c r="N72" s="18" t="n">
+        <v>-499.29</v>
+      </c>
+      <c r="O72" s="18" t="n">
+        <v>948.1900000000001</v>
+      </c>
+      <c r="P72" s="18" t="n">
+        <v>945.12</v>
+      </c>
+      <c r="Q72" s="18" t="n">
+        <v>-53.83</v>
+      </c>
+      <c r="R72" s="37" t="n">
+        <v>1340.19</v>
+      </c>
+      <c r="S72" s="18" t="n">
+        <v>192.11</v>
+      </c>
+      <c r="T72" s="18" t="n">
+        <v>-162.69</v>
+      </c>
+      <c r="U72" s="18" t="n">
+        <v>595.33</v>
+      </c>
+      <c r="V72" s="18" t="n">
+        <v>1950.57</v>
+      </c>
+      <c r="W72" s="37" t="n">
+        <v>2575.32</v>
+      </c>
+      <c r="X72" s="18" t="n">
+        <v>-1589.56</v>
+      </c>
+      <c r="Y72" s="19" t="n">
+        <v>-3300.08</v>
+      </c>
       <c r="Z72" s="10" t="n"/>
       <c r="AA72" s="10" t="n"/>
       <c r="AB72" s="11" t="n"/>
@@ -20674,32 +20848,70 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>이자비용</t>
+          <t>계속사업이익</t>
         </is>
       </c>
       <c r="E73" s="18" t="n">
-        <v>49.68</v>
+        <v>656.39</v>
       </c>
       <c r="F73" s="18" t="n">
-        <v>67.2</v>
+        <v>1404.11</v>
       </c>
       <c r="G73" s="18" t="n">
-        <v>28.72</v>
+        <v>-746.78</v>
       </c>
       <c r="H73" s="9" t="n"/>
       <c r="I73" s="18" t="n">
-        <v>65.67</v>
+        <v>589.14</v>
       </c>
       <c r="J73" s="18" t="n">
-        <v>84.34999999999999</v>
+        <v>-399.69</v>
       </c>
       <c r="K73" s="18" t="n">
-        <v>92.44</v>
-      </c>
-      <c r="M73" s="9" t="n"/>
-      <c r="R73" s="9" t="n"/>
-      <c r="W73" s="9" t="n"/>
-      <c r="Y73" s="5" t="n"/>
+        <v>-1474.32</v>
+      </c>
+      <c r="L73" s="18" t="n">
+        <v>-956.28</v>
+      </c>
+      <c r="M73" s="37" t="n">
+        <v>-2241.15</v>
+      </c>
+      <c r="N73" s="18" t="n">
+        <v>-499.29</v>
+      </c>
+      <c r="O73" s="18" t="n">
+        <v>948.1900000000001</v>
+      </c>
+      <c r="P73" s="18" t="n">
+        <v>945.12</v>
+      </c>
+      <c r="Q73" s="18" t="n">
+        <v>-53.83</v>
+      </c>
+      <c r="R73" s="37" t="n">
+        <v>1340.19</v>
+      </c>
+      <c r="S73" s="18" t="n">
+        <v>192.11</v>
+      </c>
+      <c r="T73" s="18" t="n">
+        <v>-162.69</v>
+      </c>
+      <c r="U73" s="18" t="n">
+        <v>595.33</v>
+      </c>
+      <c r="V73" s="18" t="n">
+        <v>1950.57</v>
+      </c>
+      <c r="W73" s="37" t="n">
+        <v>2575.32</v>
+      </c>
+      <c r="X73" s="18" t="n">
+        <v>-1589.56</v>
+      </c>
+      <c r="Y73" s="19" t="n">
+        <v>-3300.08</v>
+      </c>
       <c r="Z73" s="10" t="n"/>
       <c r="AA73" s="10" t="n"/>
       <c r="AB73" s="11" t="n"/>
@@ -20720,27 +20932,27 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>이자손익</t>
+          <t>이자수익</t>
         </is>
       </c>
       <c r="E74" s="18" t="n">
-        <v>-22.22</v>
+        <v>27.46</v>
       </c>
       <c r="F74" s="18" t="n">
-        <v>1097.61</v>
+        <v>1164.81</v>
       </c>
       <c r="G74" s="18" t="n">
-        <v>229.94</v>
+        <v>258.66</v>
       </c>
       <c r="H74" s="9" t="n"/>
       <c r="I74" s="18" t="n">
-        <v>744.39</v>
+        <v>810.0599999999999</v>
       </c>
       <c r="J74" s="18" t="n">
-        <v>492.79</v>
+        <v>577.14</v>
       </c>
       <c r="K74" s="18" t="n">
-        <v>410.22</v>
+        <v>502.66</v>
       </c>
       <c r="M74" s="9" t="n"/>
       <c r="R74" s="9" t="n"/>
@@ -20766,19 +20978,28 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>배당금수익</t>
+          <t>이자비용</t>
         </is>
       </c>
       <c r="E75" s="18" t="n">
-        <v>0</v>
+        <v>49.68</v>
       </c>
       <c r="F75" s="18" t="n">
-        <v>0</v>
+        <v>67.2</v>
       </c>
       <c r="G75" s="18" t="n">
-        <v>0</v>
+        <v>28.72</v>
       </c>
       <c r="H75" s="9" t="n"/>
+      <c r="I75" s="18" t="n">
+        <v>65.67</v>
+      </c>
+      <c r="J75" s="18" t="n">
+        <v>84.34999999999999</v>
+      </c>
+      <c r="K75" s="18" t="n">
+        <v>92.44</v>
+      </c>
       <c r="M75" s="9" t="n"/>
       <c r="R75" s="9" t="n"/>
       <c r="W75" s="9" t="n"/>
@@ -20803,70 +21024,32 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>영업활동으로인한현금흐름</t>
+          <t>이자손익</t>
         </is>
       </c>
       <c r="E76" s="18" t="n">
-        <v>-11070.89</v>
+        <v>-22.22</v>
       </c>
       <c r="F76" s="18" t="n">
-        <v>847.7</v>
+        <v>1097.61</v>
       </c>
       <c r="G76" s="18" t="n">
-        <v>-9356.34</v>
+        <v>229.94</v>
       </c>
       <c r="H76" s="9" t="n"/>
       <c r="I76" s="18" t="n">
-        <v>-10505.62</v>
+        <v>744.39</v>
       </c>
       <c r="J76" s="18" t="n">
-        <v>-4060.75</v>
+        <v>492.79</v>
       </c>
       <c r="K76" s="18" t="n">
-        <v>-7501.56</v>
-      </c>
-      <c r="L76" s="18" t="n">
-        <v>3108.45</v>
-      </c>
-      <c r="M76" s="37" t="n">
-        <v>-18959.48</v>
-      </c>
-      <c r="N76" s="18" t="n">
-        <v>-5099.81</v>
-      </c>
-      <c r="O76" s="18" t="n">
-        <v>18899.4</v>
-      </c>
-      <c r="P76" s="18" t="n">
-        <v>-6049.73</v>
-      </c>
-      <c r="Q76" s="18" t="n">
-        <v>1961.17</v>
-      </c>
-      <c r="R76" s="37" t="n">
-        <v>9711.030000000001</v>
-      </c>
-      <c r="S76" s="18" t="n">
-        <v>1833.13</v>
-      </c>
-      <c r="T76" s="18" t="n">
-        <v>580.72</v>
-      </c>
-      <c r="U76" s="18" t="n">
-        <v>-1565.78</v>
-      </c>
-      <c r="V76" s="18" t="n">
-        <v>21575.54</v>
-      </c>
-      <c r="W76" s="37" t="n">
-        <v>22423.61</v>
-      </c>
-      <c r="X76" s="18" t="n">
-        <v>-17530.12</v>
-      </c>
-      <c r="Y76" s="19" t="n">
-        <v>-2413.17</v>
-      </c>
+        <v>410.22</v>
+      </c>
+      <c r="M76" s="9" t="n"/>
+      <c r="R76" s="9" t="n"/>
+      <c r="W76" s="9" t="n"/>
+      <c r="Y76" s="5" t="n"/>
       <c r="Z76" s="10" t="n"/>
       <c r="AA76" s="10" t="n"/>
       <c r="AB76" s="11" t="n"/>
@@ -20887,70 +21070,23 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>감가상각비</t>
+          <t>배당금수익</t>
         </is>
       </c>
       <c r="E77" s="18" t="n">
-        <v>215.59</v>
+        <v>0</v>
       </c>
       <c r="F77" s="18" t="n">
-        <v>212.95</v>
+        <v>0</v>
       </c>
       <c r="G77" s="18" t="n">
-        <v>272.07</v>
+        <v>0</v>
       </c>
       <c r="H77" s="9" t="n"/>
-      <c r="I77" s="18" t="n">
-        <v>284.13</v>
-      </c>
-      <c r="J77" s="18" t="n">
-        <v>349.77</v>
-      </c>
-      <c r="K77" s="18" t="n">
-        <v>327.61</v>
-      </c>
-      <c r="L77" s="18" t="n">
-        <v>329.67</v>
-      </c>
-      <c r="M77" s="37" t="n">
-        <v>1291.18</v>
-      </c>
-      <c r="N77" s="18" t="n">
-        <v>391.33</v>
-      </c>
-      <c r="O77" s="18" t="n">
-        <v>432.22</v>
-      </c>
-      <c r="P77" s="18" t="n">
-        <v>426.13</v>
-      </c>
-      <c r="Q77" s="18" t="n">
-        <v>418.04</v>
-      </c>
-      <c r="R77" s="37" t="n">
-        <v>1667.72</v>
-      </c>
-      <c r="S77" s="18" t="n">
-        <v>415.02</v>
-      </c>
-      <c r="T77" s="18" t="n">
-        <v>408.33</v>
-      </c>
-      <c r="U77" s="18" t="n">
-        <v>397.63</v>
-      </c>
-      <c r="V77" s="18" t="n">
-        <v>421.01</v>
-      </c>
-      <c r="W77" s="37" t="n">
-        <v>1641.99</v>
-      </c>
-      <c r="X77" s="18" t="n">
-        <v>422.63</v>
-      </c>
-      <c r="Y77" s="19" t="n">
-        <v>440.42</v>
-      </c>
+      <c r="M77" s="9" t="n"/>
+      <c r="R77" s="9" t="n"/>
+      <c r="W77" s="9" t="n"/>
+      <c r="Y77" s="5" t="n"/>
       <c r="Z77" s="10" t="n"/>
       <c r="AA77" s="10" t="n"/>
       <c r="AB77" s="11" t="n"/>
@@ -20971,69 +21107,69 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>무형자산상각비</t>
+          <t>영업활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E78" s="18" t="n">
-        <v>71.04000000000001</v>
+        <v>-11070.89</v>
       </c>
       <c r="F78" s="18" t="n">
-        <v>80.47</v>
+        <v>847.7</v>
       </c>
       <c r="G78" s="18" t="n">
-        <v>81.2</v>
+        <v>-9356.34</v>
       </c>
       <c r="H78" s="9" t="n"/>
       <c r="I78" s="18" t="n">
-        <v>81.23</v>
+        <v>-10505.62</v>
       </c>
       <c r="J78" s="18" t="n">
-        <v>81.13</v>
+        <v>-4060.75</v>
       </c>
       <c r="K78" s="18" t="n">
-        <v>70.84</v>
+        <v>-7501.56</v>
       </c>
       <c r="L78" s="18" t="n">
-        <v>66.12</v>
+        <v>3108.45</v>
       </c>
       <c r="M78" s="37" t="n">
-        <v>299.32</v>
+        <v>-18959.48</v>
       </c>
       <c r="N78" s="18" t="n">
-        <v>66.39</v>
+        <v>-5099.81</v>
       </c>
       <c r="O78" s="18" t="n">
-        <v>68.03</v>
+        <v>18899.4</v>
       </c>
       <c r="P78" s="18" t="n">
-        <v>63.08</v>
+        <v>-6049.73</v>
       </c>
       <c r="Q78" s="18" t="n">
-        <v>153.28</v>
+        <v>1961.17</v>
       </c>
       <c r="R78" s="37" t="n">
-        <v>350.78</v>
+        <v>9711.030000000001</v>
       </c>
       <c r="S78" s="18" t="n">
-        <v>117.2</v>
+        <v>1833.13</v>
       </c>
       <c r="T78" s="18" t="n">
-        <v>107.84</v>
+        <v>580.72</v>
       </c>
       <c r="U78" s="18" t="n">
-        <v>98.63</v>
+        <v>-1565.78</v>
       </c>
       <c r="V78" s="18" t="n">
-        <v>97.88</v>
+        <v>21575.54</v>
       </c>
       <c r="W78" s="37" t="n">
-        <v>421.55</v>
+        <v>22423.61</v>
       </c>
       <c r="X78" s="18" t="n">
-        <v>97.88</v>
+        <v>-17530.12</v>
       </c>
       <c r="Y78" s="19" t="n">
-        <v>97.16</v>
+        <v>-2413.17</v>
       </c>
       <c r="Z78" s="10" t="n"/>
       <c r="AA78" s="10" t="n"/>
@@ -21055,69 +21191,69 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>법인세납부(CF)</t>
+          <t>감가상각비</t>
         </is>
       </c>
       <c r="E79" s="18" t="n">
-        <v>-221.82</v>
+        <v>215.59</v>
       </c>
       <c r="F79" s="18" t="n">
-        <v>-242.77</v>
+        <v>212.95</v>
       </c>
       <c r="G79" s="18" t="n">
-        <v>-245.64</v>
+        <v>272.07</v>
       </c>
       <c r="H79" s="9" t="n"/>
       <c r="I79" s="18" t="n">
-        <v>-88.81999999999999</v>
+        <v>284.13</v>
       </c>
       <c r="J79" s="18" t="n">
-        <v>373.42</v>
+        <v>349.77</v>
       </c>
       <c r="K79" s="18" t="n">
-        <v>-277.87</v>
+        <v>327.61</v>
       </c>
       <c r="L79" s="18" t="n">
-        <v>-56.34</v>
+        <v>329.67</v>
       </c>
       <c r="M79" s="37" t="n">
-        <v>-49.61</v>
+        <v>1291.18</v>
       </c>
       <c r="N79" s="18" t="n">
-        <v>-41.28</v>
+        <v>391.33</v>
       </c>
       <c r="O79" s="18" t="n">
-        <v>384.34</v>
+        <v>432.22</v>
       </c>
       <c r="P79" s="18" t="n">
-        <v>-45.69</v>
+        <v>426.13</v>
       </c>
       <c r="Q79" s="18" t="n">
-        <v>-13.16</v>
+        <v>418.04</v>
       </c>
       <c r="R79" s="37" t="n">
-        <v>284.21</v>
+        <v>1667.72</v>
       </c>
       <c r="S79" s="18" t="n">
-        <v>-20.77</v>
+        <v>415.02</v>
       </c>
       <c r="T79" s="18" t="n">
-        <v>84.87</v>
+        <v>408.33</v>
       </c>
       <c r="U79" s="18" t="n">
-        <v>-72.23999999999999</v>
+        <v>397.63</v>
       </c>
       <c r="V79" s="18" t="n">
-        <v>-101.9</v>
+        <v>421.01</v>
       </c>
       <c r="W79" s="37" t="n">
-        <v>-110.04</v>
+        <v>1641.99</v>
       </c>
       <c r="X79" s="18" t="n">
-        <v>-10.3</v>
+        <v>422.63</v>
       </c>
       <c r="Y79" s="19" t="n">
-        <v>65.53</v>
+        <v>440.42</v>
       </c>
       <c r="Z79" s="10" t="n"/>
       <c r="AA79" s="10" t="n"/>
@@ -21139,69 +21275,69 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>투자활동으로인한현금흐름</t>
+          <t>무형자산상각비</t>
         </is>
       </c>
       <c r="E80" s="18" t="n">
-        <v>-4344.38</v>
+        <v>71.04000000000001</v>
       </c>
       <c r="F80" s="18" t="n">
-        <v>-71443.75</v>
+        <v>80.47</v>
       </c>
       <c r="G80" s="18" t="n">
-        <v>18544.86</v>
+        <v>81.2</v>
       </c>
       <c r="H80" s="9" t="n"/>
       <c r="I80" s="18" t="n">
-        <v>17618.16</v>
+        <v>81.23</v>
       </c>
       <c r="J80" s="18" t="n">
-        <v>-12972.34</v>
+        <v>81.13</v>
       </c>
       <c r="K80" s="18" t="n">
-        <v>27357.36</v>
+        <v>70.84</v>
       </c>
       <c r="L80" s="18" t="n">
-        <v>-12048.05</v>
+        <v>66.12</v>
       </c>
       <c r="M80" s="37" t="n">
-        <v>19955.13</v>
+        <v>299.32</v>
       </c>
       <c r="N80" s="18" t="n">
-        <v>-106758.16</v>
+        <v>66.39</v>
       </c>
       <c r="O80" s="18" t="n">
-        <v>5180.69</v>
+        <v>68.03</v>
       </c>
       <c r="P80" s="18" t="n">
-        <v>-3892.11</v>
+        <v>63.08</v>
       </c>
       <c r="Q80" s="18" t="n">
-        <v>-17600.41</v>
+        <v>153.28</v>
       </c>
       <c r="R80" s="37" t="n">
-        <v>-123069.99</v>
+        <v>350.78</v>
       </c>
       <c r="S80" s="18" t="n">
-        <v>2591.03</v>
+        <v>117.2</v>
       </c>
       <c r="T80" s="18" t="n">
-        <v>-12155.24</v>
+        <v>107.84</v>
       </c>
       <c r="U80" s="18" t="n">
-        <v>-4024.9</v>
+        <v>98.63</v>
       </c>
       <c r="V80" s="18" t="n">
-        <v>187.79</v>
+        <v>97.88</v>
       </c>
       <c r="W80" s="37" t="n">
-        <v>-13401.32</v>
+        <v>421.55</v>
       </c>
       <c r="X80" s="18" t="n">
-        <v>-12964.79</v>
+        <v>97.88</v>
       </c>
       <c r="Y80" s="19" t="n">
-        <v>3825.8</v>
+        <v>97.16</v>
       </c>
       <c r="Z80" s="10" t="n"/>
       <c r="AA80" s="10" t="n"/>
@@ -21223,69 +21359,69 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>재무활동으로인한현금흐름</t>
+          <t>법인세납부(CF)</t>
         </is>
       </c>
       <c r="E81" s="18" t="n">
-        <v>83709.03999999999</v>
+        <v>-221.82</v>
       </c>
       <c r="F81" s="18" t="n">
-        <v>-3103.18</v>
+        <v>-242.77</v>
       </c>
       <c r="G81" s="18" t="n">
-        <v>-2510.08</v>
+        <v>-245.64</v>
       </c>
       <c r="H81" s="9" t="n"/>
       <c r="I81" s="18" t="n">
-        <v>-38.81</v>
+        <v>-88.81999999999999</v>
       </c>
       <c r="J81" s="18" t="n">
-        <v>2830.55</v>
+        <v>373.42</v>
       </c>
       <c r="K81" s="18" t="n">
-        <v>-48.02</v>
+        <v>-277.87</v>
       </c>
       <c r="L81" s="18" t="n">
-        <v>-51.45</v>
+        <v>-56.34</v>
       </c>
       <c r="M81" s="37" t="n">
-        <v>2692.27</v>
+        <v>-49.61</v>
       </c>
       <c r="N81" s="18" t="n">
-        <v>87961.84</v>
+        <v>-41.28</v>
       </c>
       <c r="O81" s="18" t="n">
-        <v>-38.63</v>
+        <v>384.34</v>
       </c>
       <c r="P81" s="18" t="n">
-        <v>-31.64</v>
+        <v>-45.69</v>
       </c>
       <c r="Q81" s="18" t="n">
-        <v>17846.2</v>
+        <v>-13.16</v>
       </c>
       <c r="R81" s="37" t="n">
-        <v>105737.77</v>
+        <v>284.21</v>
       </c>
       <c r="S81" s="18" t="n">
-        <v>1980.51</v>
+        <v>-20.77</v>
       </c>
       <c r="T81" s="18" t="n">
-        <v>-520.45</v>
+        <v>84.87</v>
       </c>
       <c r="U81" s="18" t="n">
-        <v>-270.67</v>
+        <v>-72.23999999999999</v>
       </c>
       <c r="V81" s="18" t="n">
-        <v>16464.5</v>
+        <v>-101.9</v>
       </c>
       <c r="W81" s="37" t="n">
-        <v>17653.89</v>
+        <v>-110.04</v>
       </c>
       <c r="X81" s="18" t="n">
-        <v>3255.33</v>
+        <v>-10.3</v>
       </c>
       <c r="Y81" s="19" t="n">
-        <v>-769.63</v>
+        <v>65.53</v>
       </c>
       <c r="Z81" s="10" t="n"/>
       <c r="AA81" s="10" t="n"/>
@@ -21307,69 +21443,69 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>리스부채의상환</t>
+          <t>투자활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E82" s="18" t="n">
-        <v>40.95</v>
+        <v>-4344.38</v>
       </c>
       <c r="F82" s="18" t="n">
-        <v>40.94</v>
+        <v>-71443.75</v>
       </c>
       <c r="G82" s="18" t="n">
-        <v>28.14</v>
+        <v>18544.86</v>
       </c>
       <c r="H82" s="9" t="n"/>
       <c r="I82" s="18" t="n">
-        <v>38.81</v>
+        <v>17618.16</v>
       </c>
       <c r="J82" s="18" t="n">
-        <v>59.45</v>
+        <v>-12972.34</v>
       </c>
       <c r="K82" s="18" t="n">
-        <v>48.02</v>
+        <v>27357.36</v>
       </c>
       <c r="L82" s="18" t="n">
-        <v>5.7</v>
+        <v>-12048.05</v>
       </c>
       <c r="M82" s="37" t="n">
-        <v>151.98</v>
+        <v>19955.13</v>
       </c>
       <c r="N82" s="18" t="n">
-        <v>38.16</v>
+        <v>-106758.16</v>
       </c>
       <c r="O82" s="18" t="n">
-        <v>38.63</v>
+        <v>5180.69</v>
       </c>
       <c r="P82" s="18" t="n">
-        <v>31.64</v>
+        <v>-3892.11</v>
       </c>
       <c r="Q82" s="18" t="n">
-        <v>20.74</v>
+        <v>-17600.41</v>
       </c>
       <c r="R82" s="37" t="n">
-        <v>129.17</v>
+        <v>-123069.99</v>
       </c>
       <c r="S82" s="18" t="n">
-        <v>19.49</v>
+        <v>2591.03</v>
       </c>
       <c r="T82" s="18" t="n">
-        <v>20.45</v>
+        <v>-12155.24</v>
       </c>
       <c r="U82" s="18" t="n">
-        <v>20.67</v>
+        <v>-4024.9</v>
       </c>
       <c r="V82" s="18" t="n">
-        <v>19.72</v>
+        <v>187.79</v>
       </c>
       <c r="W82" s="37" t="n">
-        <v>80.33</v>
+        <v>-13401.32</v>
       </c>
       <c r="X82" s="18" t="n">
-        <v>19.83</v>
+        <v>-12964.79</v>
       </c>
       <c r="Y82" s="19" t="n">
-        <v>19.63</v>
+        <v>3825.8</v>
       </c>
       <c r="Z82" s="10" t="n"/>
       <c r="AA82" s="10" t="n"/>
@@ -21391,69 +21527,69 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>현금및현금성자산의증감</t>
+          <t>재무활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E83" s="18" t="n">
-        <v>68293.75999999999</v>
+        <v>83709.03999999999</v>
       </c>
       <c r="F83" s="18" t="n">
-        <v>-73699.22</v>
+        <v>-3103.18</v>
       </c>
       <c r="G83" s="18" t="n">
-        <v>6678.44</v>
+        <v>-2510.08</v>
       </c>
       <c r="H83" s="9" t="n"/>
       <c r="I83" s="18" t="n">
-        <v>7073.73</v>
+        <v>-38.81</v>
       </c>
       <c r="J83" s="18" t="n">
-        <v>-14202.54</v>
+        <v>2830.55</v>
       </c>
       <c r="K83" s="18" t="n">
-        <v>19807.78</v>
+        <v>-48.02</v>
       </c>
       <c r="L83" s="18" t="n">
-        <v>-9007.24</v>
+        <v>-51.45</v>
       </c>
       <c r="M83" s="37" t="n">
-        <v>3671.73</v>
+        <v>2692.27</v>
       </c>
       <c r="N83" s="18" t="n">
-        <v>-23878.9</v>
+        <v>87961.84</v>
       </c>
       <c r="O83" s="18" t="n">
-        <v>24024.23</v>
+        <v>-38.63</v>
       </c>
       <c r="P83" s="18" t="n">
-        <v>-9973.469999999999</v>
+        <v>-31.64</v>
       </c>
       <c r="Q83" s="18" t="n">
-        <v>2207.77</v>
+        <v>17846.2</v>
       </c>
       <c r="R83" s="37" t="n">
-        <v>-7620.37</v>
+        <v>105737.77</v>
       </c>
       <c r="S83" s="18" t="n">
-        <v>6406.99</v>
+        <v>1980.51</v>
       </c>
       <c r="T83" s="18" t="n">
-        <v>-12094.81</v>
+        <v>-520.45</v>
       </c>
       <c r="U83" s="18" t="n">
-        <v>-5859.28</v>
+        <v>-270.67</v>
       </c>
       <c r="V83" s="18" t="n">
-        <v>38223.28</v>
+        <v>16464.5</v>
       </c>
       <c r="W83" s="37" t="n">
-        <v>26676.18</v>
+        <v>17653.89</v>
       </c>
       <c r="X83" s="18" t="n">
-        <v>-27239.58</v>
+        <v>3255.33</v>
       </c>
       <c r="Y83" s="19" t="n">
-        <v>965.37</v>
+        <v>-769.63</v>
       </c>
       <c r="Z83" s="10" t="n"/>
       <c r="AA83" s="10" t="n"/>
@@ -21475,69 +21611,69 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>기말현금및현금성자산</t>
+          <t>리스부채의상환</t>
         </is>
       </c>
       <c r="E84" s="18" t="n">
-        <v>68293.77</v>
+        <v>40.95</v>
       </c>
       <c r="F84" s="18" t="n">
-        <v>-73699.23</v>
+        <v>40.94</v>
       </c>
       <c r="G84" s="18" t="n">
-        <v>6678.45</v>
+        <v>28.14</v>
       </c>
       <c r="H84" s="9" t="n"/>
       <c r="I84" s="18" t="n">
-        <v>30031.84</v>
+        <v>38.81</v>
       </c>
       <c r="J84" s="18" t="n">
-        <v>-14202.54</v>
+        <v>59.45</v>
       </c>
       <c r="K84" s="18" t="n">
-        <v>19807.78</v>
+        <v>48.02</v>
       </c>
       <c r="L84" s="18" t="n">
-        <v>-9007.23</v>
+        <v>5.7</v>
       </c>
       <c r="M84" s="37" t="n">
-        <v>26629.85</v>
+        <v>151.98</v>
       </c>
       <c r="N84" s="18" t="n">
-        <v>2750.94</v>
+        <v>38.16</v>
       </c>
       <c r="O84" s="18" t="n">
-        <v>24024.24</v>
+        <v>38.63</v>
       </c>
       <c r="P84" s="18" t="n">
-        <v>-9973.48</v>
+        <v>31.64</v>
       </c>
       <c r="Q84" s="18" t="n">
-        <v>2207.77</v>
+        <v>20.74</v>
       </c>
       <c r="R84" s="37" t="n">
-        <v>19009.47</v>
+        <v>129.17</v>
       </c>
       <c r="S84" s="18" t="n">
-        <v>25416.47</v>
+        <v>19.49</v>
       </c>
       <c r="T84" s="18" t="n">
-        <v>-12094.82</v>
+        <v>20.45</v>
       </c>
       <c r="U84" s="18" t="n">
-        <v>-5859.28</v>
+        <v>20.67</v>
       </c>
       <c r="V84" s="18" t="n">
-        <v>38138.87</v>
+        <v>19.72</v>
       </c>
       <c r="W84" s="37" t="n">
-        <v>45601.24</v>
+        <v>80.33</v>
       </c>
       <c r="X84" s="18" t="n">
-        <v>18696.87</v>
+        <v>19.83</v>
       </c>
       <c r="Y84" s="19" t="n">
-        <v>630.16</v>
+        <v>19.63</v>
       </c>
       <c r="Z84" s="10" t="n"/>
       <c r="AA84" s="10" t="n"/>
@@ -21559,50 +21695,69 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>단기차입금의증가</t>
-        </is>
+          <t>현금및현금성자산의증감</t>
+        </is>
+      </c>
+      <c r="E85" s="18" t="n">
+        <v>68293.75999999999</v>
       </c>
       <c r="F85" s="18" t="n">
-        <v>0</v>
+        <v>-73699.22</v>
       </c>
       <c r="G85" s="18" t="n">
-        <v>0</v>
+        <v>6678.44</v>
       </c>
       <c r="H85" s="9" t="n"/>
+      <c r="I85" s="18" t="n">
+        <v>7073.73</v>
+      </c>
+      <c r="J85" s="18" t="n">
+        <v>-14202.54</v>
+      </c>
       <c r="K85" s="18" t="n">
-        <v>0</v>
+        <v>19807.78</v>
       </c>
       <c r="L85" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M85" s="9" t="n"/>
+        <v>-9007.24</v>
+      </c>
+      <c r="M85" s="37" t="n">
+        <v>3671.73</v>
+      </c>
+      <c r="N85" s="18" t="n">
+        <v>-23878.9</v>
+      </c>
+      <c r="O85" s="18" t="n">
+        <v>24024.23</v>
+      </c>
       <c r="P85" s="18" t="n">
-        <v>0</v>
+        <v>-9973.469999999999</v>
       </c>
       <c r="Q85" s="18" t="n">
-        <v>5000</v>
-      </c>
-      <c r="R85" s="9" t="n"/>
+        <v>2207.77</v>
+      </c>
+      <c r="R85" s="37" t="n">
+        <v>-7620.37</v>
+      </c>
       <c r="S85" s="18" t="n">
-        <v>5000</v>
+        <v>6406.99</v>
       </c>
       <c r="T85" s="18" t="n">
-        <v>0</v>
+        <v>-12094.81</v>
       </c>
       <c r="U85" s="18" t="n">
-        <v>0</v>
+        <v>-5859.28</v>
       </c>
       <c r="V85" s="18" t="n">
-        <v>10000</v>
+        <v>38223.28</v>
       </c>
       <c r="W85" s="37" t="n">
-        <v>15000</v>
+        <v>26676.18</v>
       </c>
       <c r="X85" s="18" t="n">
-        <v>0</v>
+        <v>-27239.58</v>
       </c>
       <c r="Y85" s="19" t="n">
-        <v>0</v>
+        <v>965.37</v>
       </c>
       <c r="Z85" s="10" t="n"/>
       <c r="AA85" s="10" t="n"/>
@@ -21624,50 +21779,69 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>유동성장기부채의감소</t>
-        </is>
+          <t>기말현금및현금성자산</t>
+        </is>
+      </c>
+      <c r="E86" s="18" t="n">
+        <v>68293.77</v>
       </c>
       <c r="F86" s="18" t="n">
-        <v>0</v>
+        <v>-73699.23</v>
       </c>
       <c r="G86" s="18" t="n">
-        <v>0</v>
+        <v>6678.45</v>
       </c>
       <c r="H86" s="9" t="n"/>
+      <c r="I86" s="18" t="n">
+        <v>30031.84</v>
+      </c>
+      <c r="J86" s="18" t="n">
+        <v>-14202.54</v>
+      </c>
       <c r="K86" s="18" t="n">
-        <v>440</v>
+        <v>19807.78</v>
       </c>
       <c r="L86" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M86" s="9" t="n"/>
+        <v>-9007.23</v>
+      </c>
+      <c r="M86" s="37" t="n">
+        <v>26629.85</v>
+      </c>
+      <c r="N86" s="18" t="n">
+        <v>2750.94</v>
+      </c>
+      <c r="O86" s="18" t="n">
+        <v>24024.24</v>
+      </c>
       <c r="P86" s="18" t="n">
-        <v>0</v>
+        <v>-9973.48</v>
       </c>
       <c r="Q86" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R86" s="9" t="n"/>
+        <v>2207.77</v>
+      </c>
+      <c r="R86" s="37" t="n">
+        <v>19009.47</v>
+      </c>
       <c r="S86" s="18" t="n">
-        <v>1000</v>
+        <v>25416.47</v>
       </c>
       <c r="T86" s="18" t="n">
-        <v>0</v>
+        <v>-12094.82</v>
       </c>
       <c r="U86" s="18" t="n">
-        <v>0</v>
+        <v>-5859.28</v>
       </c>
       <c r="V86" s="18" t="n">
-        <v>0</v>
+        <v>38138.87</v>
       </c>
       <c r="W86" s="37" t="n">
-        <v>1000</v>
+        <v>45601.24</v>
       </c>
       <c r="X86" s="18" t="n">
-        <v>0</v>
+        <v>18696.87</v>
       </c>
       <c r="Y86" s="19" t="n">
-        <v>0</v>
+        <v>630.16</v>
       </c>
       <c r="Z86" s="10" t="n"/>
       <c r="AA86" s="10" t="n"/>
@@ -21689,20 +21863,51 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>자기주식의취득</t>
-        </is>
+          <t>단기차입금의증가</t>
+        </is>
+      </c>
+      <c r="F87" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="G87" s="18" t="n">
-        <v>2481.94</v>
+        <v>0</v>
       </c>
       <c r="H87" s="9" t="n"/>
+      <c r="K87" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="L87" s="18" t="n">
-        <v>45.75</v>
+        <v>0</v>
       </c>
       <c r="M87" s="9" t="n"/>
+      <c r="P87" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="18" t="n">
+        <v>5000</v>
+      </c>
       <c r="R87" s="9" t="n"/>
-      <c r="W87" s="9" t="n"/>
-      <c r="Y87" s="5" t="n"/>
+      <c r="S87" s="18" t="n">
+        <v>5000</v>
+      </c>
+      <c r="T87" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U87" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V87" s="18" t="n">
+        <v>10000</v>
+      </c>
+      <c r="W87" s="37" t="n">
+        <v>15000</v>
+      </c>
+      <c r="X87" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y87" s="19" t="n">
+        <v>0</v>
+      </c>
       <c r="Z87" s="10" t="n"/>
       <c r="AA87" s="10" t="n"/>
       <c r="AB87" s="11" t="n"/>
@@ -21723,34 +21928,32 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>장기차입금의증가</t>
-        </is>
+          <t>유동성장기부채의감소</t>
+        </is>
+      </c>
+      <c r="F88" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="H88" s="9" t="n"/>
       <c r="K88" s="18" t="n">
-        <v>2090</v>
+        <v>440</v>
       </c>
       <c r="L88" s="18" t="n">
         <v>0</v>
       </c>
       <c r="M88" s="9" t="n"/>
-      <c r="N88" s="18" t="n">
-        <v>88000</v>
-      </c>
-      <c r="O88" s="18" t="n">
-        <v>0</v>
-      </c>
       <c r="P88" s="18" t="n">
         <v>0</v>
       </c>
       <c r="Q88" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="R88" s="37" t="n">
-        <v>88000</v>
-      </c>
+      <c r="R88" s="9" t="n"/>
       <c r="S88" s="18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T88" s="18" t="n">
         <v>0</v>
@@ -21762,9 +21965,14 @@
         <v>0</v>
       </c>
       <c r="W88" s="37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="X88" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="Y88" s="5" t="n"/>
+      <c r="Y88" s="19" t="n">
+        <v>0</v>
+      </c>
       <c r="Z88" s="10" t="n"/>
       <c r="AA88" s="10" t="n"/>
       <c r="AB88" s="11" t="n"/>
@@ -21785,45 +21993,20 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>단기차입금의감소</t>
-        </is>
+          <t>자기주식의취득</t>
+        </is>
+      </c>
+      <c r="G89" s="18" t="n">
+        <v>2481.94</v>
       </c>
       <c r="H89" s="9" t="n"/>
-      <c r="K89" s="18" t="n">
-        <v>0</v>
-      </c>
       <c r="L89" s="18" t="n">
-        <v>0</v>
+        <v>45.75</v>
       </c>
       <c r="M89" s="9" t="n"/>
-      <c r="P89" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q89" s="18" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" s="9" t="n"/>
-      <c r="S89" s="18" t="n">
-        <v>2000</v>
-      </c>
-      <c r="T89" s="18" t="n">
-        <v>500</v>
-      </c>
-      <c r="U89" s="18" t="n">
-        <v>250</v>
-      </c>
-      <c r="V89" s="18" t="n">
-        <v>250</v>
-      </c>
-      <c r="W89" s="37" t="n">
-        <v>3000</v>
-      </c>
-      <c r="X89" s="18" t="n">
-        <v>3750</v>
-      </c>
-      <c r="Y89" s="19" t="n">
-        <v>750</v>
-      </c>
+      <c r="W89" s="9" t="n"/>
+      <c r="Y89" s="5" t="n"/>
       <c r="Z89" s="10" t="n"/>
       <c r="AA89" s="10" t="n"/>
       <c r="AB89" s="11" t="n"/>
@@ -21844,50 +22027,48 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>이자수취(CF)</t>
+          <t>장기차입금의증가</t>
         </is>
       </c>
       <c r="H90" s="9" t="n"/>
+      <c r="K90" s="18" t="n">
+        <v>2090</v>
+      </c>
       <c r="L90" s="18" t="n">
-        <v>295.85</v>
+        <v>0</v>
       </c>
       <c r="M90" s="9" t="n"/>
       <c r="N90" s="18" t="n">
-        <v>269.72</v>
+        <v>88000</v>
       </c>
       <c r="O90" s="18" t="n">
-        <v>389.12</v>
+        <v>0</v>
       </c>
       <c r="P90" s="18" t="n">
-        <v>321.08</v>
+        <v>0</v>
       </c>
       <c r="Q90" s="18" t="n">
-        <v>141.07</v>
+        <v>0</v>
       </c>
       <c r="R90" s="37" t="n">
-        <v>1120.99</v>
+        <v>88000</v>
       </c>
       <c r="S90" s="18" t="n">
-        <v>135.47</v>
+        <v>0</v>
       </c>
       <c r="T90" s="18" t="n">
-        <v>460.36</v>
+        <v>0</v>
       </c>
       <c r="U90" s="18" t="n">
-        <v>270.13</v>
+        <v>0</v>
       </c>
       <c r="V90" s="18" t="n">
-        <v>877.7</v>
+        <v>0</v>
       </c>
       <c r="W90" s="37" t="n">
-        <v>1743.66</v>
-      </c>
-      <c r="X90" s="18" t="n">
-        <v>67.66</v>
-      </c>
-      <c r="Y90" s="19" t="n">
-        <v>775.63</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y90" s="5" t="n"/>
       <c r="Z90" s="10" t="n"/>
       <c r="AA90" s="10" t="n"/>
       <c r="AB90" s="11" t="n"/>
@@ -21908,49 +22089,44 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>이자지급(CF)</t>
+          <t>단기차입금의감소</t>
         </is>
       </c>
       <c r="H91" s="9" t="n"/>
+      <c r="K91" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="L91" s="18" t="n">
-        <v>-124.77</v>
+        <v>0</v>
       </c>
       <c r="M91" s="9" t="n"/>
-      <c r="N91" s="18" t="n">
-        <v>-367.28</v>
-      </c>
-      <c r="O91" s="18" t="n">
-        <v>-722.79</v>
-      </c>
       <c r="P91" s="18" t="n">
-        <v>-1233.99</v>
+        <v>0</v>
       </c>
       <c r="Q91" s="18" t="n">
-        <v>-996.75</v>
-      </c>
-      <c r="R91" s="37" t="n">
-        <v>-3320.81</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R91" s="9" t="n"/>
       <c r="S91" s="18" t="n">
-        <v>-1006.62</v>
+        <v>2000</v>
       </c>
       <c r="T91" s="18" t="n">
-        <v>-938.64</v>
+        <v>500</v>
       </c>
       <c r="U91" s="18" t="n">
-        <v>-858.09</v>
+        <v>250</v>
       </c>
       <c r="V91" s="18" t="n">
-        <v>-882</v>
+        <v>250</v>
       </c>
       <c r="W91" s="37" t="n">
-        <v>-3685.35</v>
+        <v>3000</v>
       </c>
       <c r="X91" s="18" t="n">
-        <v>-939.37</v>
+        <v>3750</v>
       </c>
       <c r="Y91" s="19" t="n">
-        <v>-951.98</v>
+        <v>750</v>
       </c>
       <c r="Z91" s="10" t="n"/>
       <c r="AA91" s="10" t="n"/>
@@ -21972,20 +22148,50 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>장기차입금의감소</t>
+          <t>이자수취(CF)</t>
         </is>
       </c>
       <c r="H92" s="9" t="n"/>
       <c r="L92" s="18" t="n">
-        <v>0</v>
+        <v>295.85</v>
       </c>
       <c r="M92" s="9" t="n"/>
+      <c r="N92" s="18" t="n">
+        <v>269.72</v>
+      </c>
+      <c r="O92" s="18" t="n">
+        <v>389.12</v>
+      </c>
+      <c r="P92" s="18" t="n">
+        <v>321.08</v>
+      </c>
       <c r="Q92" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R92" s="9" t="n"/>
-      <c r="W92" s="9" t="n"/>
-      <c r="Y92" s="5" t="n"/>
+        <v>141.07</v>
+      </c>
+      <c r="R92" s="37" t="n">
+        <v>1120.99</v>
+      </c>
+      <c r="S92" s="18" t="n">
+        <v>135.47</v>
+      </c>
+      <c r="T92" s="18" t="n">
+        <v>460.36</v>
+      </c>
+      <c r="U92" s="18" t="n">
+        <v>270.13</v>
+      </c>
+      <c r="V92" s="18" t="n">
+        <v>877.7</v>
+      </c>
+      <c r="W92" s="37" t="n">
+        <v>1743.66</v>
+      </c>
+      <c r="X92" s="18" t="n">
+        <v>67.66</v>
+      </c>
+      <c r="Y92" s="19" t="n">
+        <v>775.63</v>
+      </c>
       <c r="Z92" s="10" t="n"/>
       <c r="AA92" s="10" t="n"/>
       <c r="AB92" s="11" t="n"/>
@@ -22006,20 +22212,50 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>배당금수취(CF)</t>
+          <t>이자지급(CF)</t>
         </is>
       </c>
       <c r="H93" s="9" t="n"/>
+      <c r="L93" s="18" t="n">
+        <v>-124.77</v>
+      </c>
       <c r="M93" s="9" t="n"/>
-      <c r="R93" s="9" t="n"/>
+      <c r="N93" s="18" t="n">
+        <v>-367.28</v>
+      </c>
+      <c r="O93" s="18" t="n">
+        <v>-722.79</v>
+      </c>
+      <c r="P93" s="18" t="n">
+        <v>-1233.99</v>
+      </c>
+      <c r="Q93" s="18" t="n">
+        <v>-996.75</v>
+      </c>
+      <c r="R93" s="37" t="n">
+        <v>-3320.81</v>
+      </c>
+      <c r="S93" s="18" t="n">
+        <v>-1006.62</v>
+      </c>
+      <c r="T93" s="18" t="n">
+        <v>-938.64</v>
+      </c>
       <c r="U93" s="18" t="n">
-        <v>0</v>
+        <v>-858.09</v>
       </c>
       <c r="V93" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W93" s="9" t="n"/>
-      <c r="Y93" s="5" t="n"/>
+        <v>-882</v>
+      </c>
+      <c r="W93" s="37" t="n">
+        <v>-3685.35</v>
+      </c>
+      <c r="X93" s="18" t="n">
+        <v>-939.37</v>
+      </c>
+      <c r="Y93" s="19" t="n">
+        <v>-951.98</v>
+      </c>
       <c r="Z93" s="10" t="n"/>
       <c r="AA93" s="10" t="n"/>
       <c r="AB93" s="11" t="n"/>
@@ -22033,6 +22269,74 @@
       <c r="AJ93" s="10" t="n"/>
       <c r="AK93" s="10" t="n"/>
       <c r="AL93" s="11" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>1</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>장기차입금의감소</t>
+        </is>
+      </c>
+      <c r="H94" s="9" t="n"/>
+      <c r="L94" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" s="9" t="n"/>
+      <c r="Q94" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R94" s="9" t="n"/>
+      <c r="W94" s="9" t="n"/>
+      <c r="Y94" s="5" t="n"/>
+      <c r="Z94" s="10" t="n"/>
+      <c r="AA94" s="10" t="n"/>
+      <c r="AB94" s="11" t="n"/>
+      <c r="AC94" s="10" t="n"/>
+      <c r="AD94" s="10" t="n"/>
+      <c r="AE94" s="10" t="n"/>
+      <c r="AF94" s="10" t="n"/>
+      <c r="AG94" s="11" t="n"/>
+      <c r="AH94" s="10" t="n"/>
+      <c r="AI94" s="10" t="n"/>
+      <c r="AJ94" s="10" t="n"/>
+      <c r="AK94" s="10" t="n"/>
+      <c r="AL94" s="11" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>1</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>배당금수취(CF)</t>
+        </is>
+      </c>
+      <c r="H95" s="9" t="n"/>
+      <c r="M95" s="9" t="n"/>
+      <c r="R95" s="9" t="n"/>
+      <c r="U95" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V95" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W95" s="9" t="n"/>
+      <c r="Y95" s="5" t="n"/>
+      <c r="Z95" s="10" t="n"/>
+      <c r="AA95" s="10" t="n"/>
+      <c r="AB95" s="11" t="n"/>
+      <c r="AC95" s="10" t="n"/>
+      <c r="AD95" s="10" t="n"/>
+      <c r="AE95" s="10" t="n"/>
+      <c r="AF95" s="10" t="n"/>
+      <c r="AG95" s="11" t="n"/>
+      <c r="AH95" s="10" t="n"/>
+      <c r="AI95" s="10" t="n"/>
+      <c r="AJ95" s="10" t="n"/>
+      <c r="AK95" s="10" t="n"/>
+      <c r="AL95" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/argus/kship/models/382900_model.xlsx
+++ b/argus/kship/models/382900_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AL$1</definedName>
@@ -4755,35 +4755,35 @@
         <v>1418.75</v>
       </c>
       <c r="AA6" s="16" t="n">
-        <v>1346.2</v>
+        <v>1345.74</v>
       </c>
       <c r="AB6" s="17" t="n">
-        <v>1458.38</v>
+        <v>1457.79</v>
       </c>
       <c r="AC6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AE6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG6" s="11" t="n"/>
       <c r="AH6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AK6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL6" s="11" t="n"/>
     </row>
@@ -4865,35 +4865,35 @@
         <v>1355.4</v>
       </c>
       <c r="AA7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AB7" s="17" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AC7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AE7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG7" s="11" t="n"/>
       <c r="AH7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AK7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL7" s="11" t="n"/>
     </row>
@@ -4975,35 +4975,35 @@
         <v>890.41</v>
       </c>
       <c r="AA8" s="16" t="n">
-        <v>851.8099999999999</v>
+        <v>851.3099999999999</v>
       </c>
       <c r="AB8" s="17" t="n">
-        <v>919.9299999999999</v>
+        <v>919.5700000000001</v>
       </c>
       <c r="AC8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AE8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG8" s="11" t="n"/>
       <c r="AH8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AK8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL8" s="11" t="n"/>
     </row>
@@ -5085,35 +5085,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AA9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AB9" s="17" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AC9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AE9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG9" s="11" t="n"/>
       <c r="AH9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AK9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL9" s="11" t="n"/>
     </row>
@@ -5195,35 +5195,35 @@
         <v>1631.97</v>
       </c>
       <c r="AA10" s="16" t="n">
-        <v>1512.43</v>
+        <v>1510.82</v>
       </c>
       <c r="AB10" s="17" t="n">
-        <v>1691.86</v>
+        <v>1690.9</v>
       </c>
       <c r="AC10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AE10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG10" s="11" t="n"/>
       <c r="AH10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AK10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL10" s="11" t="n"/>
     </row>
@@ -5305,35 +5305,35 @@
         <v>1539.06</v>
       </c>
       <c r="AA11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AB11" s="17" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AC11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AE11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG11" s="11" t="n"/>
       <c r="AH11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AK11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL11" s="11" t="n"/>
     </row>
@@ -5415,35 +5415,35 @@
         <v>210.43</v>
       </c>
       <c r="AA12" s="16" t="n">
-        <v>200.79</v>
+        <v>200.73</v>
       </c>
       <c r="AB12" s="17" t="n">
-        <v>213.89</v>
+        <v>213.82</v>
       </c>
       <c r="AC12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AE12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG12" s="11" t="n"/>
       <c r="AH12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AK12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL12" s="11" t="n"/>
     </row>
@@ -5525,35 +5525,35 @@
         <v>202.16</v>
       </c>
       <c r="AA13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AB13" s="17" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AC13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AE13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG13" s="11" t="n"/>
       <c r="AH13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AK13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL13" s="11" t="n"/>
     </row>
@@ -5652,7 +5652,7 @@
         <v>25050</v>
       </c>
       <c r="AA15" s="20" t="n">
-        <v>24250</v>
+        <v>24400</v>
       </c>
       <c r="AB15" s="11" t="n"/>
       <c r="AC15" s="10" t="n"/>
@@ -5904,7 +5904,7 @@
         <v>18741.1</v>
       </c>
       <c r="AA18" s="20" t="n">
-        <v>25120</v>
+        <v>25150</v>
       </c>
       <c r="AB18" s="11" t="n"/>
       <c r="AC18" s="10" t="n"/>
@@ -8169,11 +8169,11 @@
         </is>
       </c>
       <c r="D40" s="34" t="n">
-        <v>24250</v>
+        <v>24400</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 25,350원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 25,150원)</t>
         </is>
       </c>
       <c r="H40" s="9" t="n"/>
@@ -8475,7 +8475,7 @@
         </is>
       </c>
       <c r="D48" s="36" t="n">
-        <v>0.09373844061392077</v>
+        <v>0.09373844061392075</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -8551,7 +8551,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.04894776875942602</v>
+        <v>0.04894776875943081</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -34768,7 +34768,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>104.62</v>
+        <v>105.05</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/382900_model.xlsx
+++ b/argus/kship/models/382900_model.xlsx
@@ -3934,7 +3934,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
         </is>
       </c>
     </row>
@@ -4755,35 +4755,35 @@
         <v>1418.75</v>
       </c>
       <c r="AA6" s="16" t="n">
-        <v>1345.74</v>
+        <v>1345.14</v>
       </c>
       <c r="AB6" s="17" t="n">
-        <v>1457.79</v>
+        <v>1457.21</v>
       </c>
       <c r="AC6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AE6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG6" s="11" t="n"/>
       <c r="AH6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AK6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL6" s="11" t="n"/>
     </row>
@@ -4865,35 +4865,35 @@
         <v>1355.4</v>
       </c>
       <c r="AA7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AB7" s="17" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AC7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AE7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG7" s="11" t="n"/>
       <c r="AH7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AK7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL7" s="11" t="n"/>
     </row>
@@ -4975,35 +4975,35 @@
         <v>890.41</v>
       </c>
       <c r="AA8" s="16" t="n">
-        <v>851.3099999999999</v>
+        <v>850.79</v>
       </c>
       <c r="AB8" s="17" t="n">
-        <v>919.5700000000001</v>
+        <v>919.21</v>
       </c>
       <c r="AC8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AE8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG8" s="11" t="n"/>
       <c r="AH8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AK8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL8" s="11" t="n"/>
     </row>
@@ -5085,35 +5085,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AA9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AB9" s="17" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AC9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AE9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG9" s="11" t="n"/>
       <c r="AH9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AK9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL9" s="11" t="n"/>
     </row>
@@ -5195,35 +5195,35 @@
         <v>1631.97</v>
       </c>
       <c r="AA10" s="16" t="n">
-        <v>1510.82</v>
+        <v>1509.74</v>
       </c>
       <c r="AB10" s="17" t="n">
-        <v>1690.9</v>
+        <v>1689.95</v>
       </c>
       <c r="AC10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AE10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG10" s="11" t="n"/>
       <c r="AH10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AK10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL10" s="11" t="n"/>
     </row>
@@ -5305,35 +5305,35 @@
         <v>1539.06</v>
       </c>
       <c r="AA11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AB11" s="17" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AC11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AE11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG11" s="11" t="n"/>
       <c r="AH11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AK11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL11" s="11" t="n"/>
     </row>
@@ -5415,35 +5415,35 @@
         <v>210.43</v>
       </c>
       <c r="AA12" s="16" t="n">
-        <v>200.73</v>
+        <v>200.69</v>
       </c>
       <c r="AB12" s="17" t="n">
-        <v>213.82</v>
+        <v>213.75</v>
       </c>
       <c r="AC12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AE12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="11" t="n"/>
       <c r="AH12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AK12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="11" t="n"/>
     </row>
@@ -5525,35 +5525,35 @@
         <v>202.16</v>
       </c>
       <c r="AA13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AB13" s="17" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AC13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="11" t="n"/>
       <c r="AH13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AK13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="11" t="n"/>
     </row>
@@ -9005,7 +9005,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -15115,7 +15115,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/382900_model.xlsx
+++ b/argus/kship/models/382900_model.xlsx
@@ -3934,7 +3934,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
         </is>
       </c>
     </row>
@@ -9005,7 +9005,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -15115,7 +15115,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/382900_model.xlsx
+++ b/argus/kship/models/382900_model.xlsx
@@ -3934,7 +3934,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5652,7 @@
         <v>25050</v>
       </c>
       <c r="AA15" s="20" t="n">
-        <v>24400</v>
+        <v>21450</v>
       </c>
       <c r="AB15" s="11" t="n"/>
       <c r="AC15" s="10" t="n"/>
@@ -5820,7 +5820,7 @@
         <v>11810</v>
       </c>
       <c r="AA17" s="20" t="n">
-        <v>24050</v>
+        <v>21350</v>
       </c>
       <c r="AB17" s="11" t="n"/>
       <c r="AC17" s="10" t="n"/>
@@ -5904,7 +5904,7 @@
         <v>18741.1</v>
       </c>
       <c r="AA18" s="20" t="n">
-        <v>25150</v>
+        <v>24533.3</v>
       </c>
       <c r="AB18" s="11" t="n"/>
       <c r="AC18" s="10" t="n"/>
@@ -8169,7 +8169,7 @@
         </is>
       </c>
       <c r="D40" s="34" t="n">
-        <v>24400</v>
+        <v>21450</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="D41" s="35" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -9005,7 +9005,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -15115,7 +15115,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -28258,7 +28258,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -32827,7 +32827,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34734,7 +34734,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="33">
@@ -34768,7 +34768,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>105.05</v>
+        <v>96.48</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/382900_model.xlsx
+++ b/argus/kship/models/382900_model.xlsx
@@ -3934,7 +3934,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
         </is>
       </c>
     </row>
@@ -4755,35 +4755,35 @@
         <v>1418.75</v>
       </c>
       <c r="AA6" s="16" t="n">
-        <v>1345.14</v>
+        <v>1343.63</v>
       </c>
       <c r="AB6" s="17" t="n">
-        <v>1457.21</v>
+        <v>1456.58</v>
       </c>
       <c r="AC6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AE6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG6" s="11" t="n"/>
       <c r="AH6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AK6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL6" s="11" t="n"/>
     </row>
@@ -4865,35 +4865,35 @@
         <v>1355.4</v>
       </c>
       <c r="AA7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AB7" s="17" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AC7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AE7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG7" s="11" t="n"/>
       <c r="AH7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AK7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL7" s="11" t="n"/>
     </row>
@@ -4975,35 +4975,35 @@
         <v>890.41</v>
       </c>
       <c r="AA8" s="16" t="n">
-        <v>850.79</v>
+        <v>849.51</v>
       </c>
       <c r="AB8" s="17" t="n">
-        <v>919.21</v>
+        <v>918.8099999999999</v>
       </c>
       <c r="AC8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AE8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG8" s="11" t="n"/>
       <c r="AH8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AK8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL8" s="11" t="n"/>
     </row>
@@ -5085,35 +5085,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AA9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AB9" s="17" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AC9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AE9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG9" s="11" t="n"/>
       <c r="AH9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AK9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL9" s="11" t="n"/>
     </row>
@@ -5195,35 +5195,35 @@
         <v>1631.97</v>
       </c>
       <c r="AA10" s="16" t="n">
-        <v>1509.74</v>
+        <v>1507.34</v>
       </c>
       <c r="AB10" s="17" t="n">
-        <v>1689.95</v>
+        <v>1688.95</v>
       </c>
       <c r="AC10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AE10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG10" s="11" t="n"/>
       <c r="AH10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AK10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL10" s="11" t="n"/>
     </row>
@@ -5305,35 +5305,35 @@
         <v>1539.06</v>
       </c>
       <c r="AA11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AB11" s="17" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AC11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AE11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG11" s="11" t="n"/>
       <c r="AH11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AK11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL11" s="11" t="n"/>
     </row>
@@ -5415,35 +5415,35 @@
         <v>210.43</v>
       </c>
       <c r="AA12" s="16" t="n">
-        <v>200.69</v>
+        <v>200.5</v>
       </c>
       <c r="AB12" s="17" t="n">
-        <v>213.75</v>
+        <v>213.68</v>
       </c>
       <c r="AC12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AE12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG12" s="11" t="n"/>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL12" s="11" t="n"/>
     </row>
@@ -5525,35 +5525,35 @@
         <v>202.16</v>
       </c>
       <c r="AA13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AB13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AC13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AE13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG13" s="11" t="n"/>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL13" s="11" t="n"/>
     </row>
@@ -5652,7 +5652,7 @@
         <v>25050</v>
       </c>
       <c r="AA15" s="20" t="n">
-        <v>21450</v>
+        <v>20900</v>
       </c>
       <c r="AB15" s="11" t="n"/>
       <c r="AC15" s="10" t="n"/>
@@ -5820,7 +5820,7 @@
         <v>11810</v>
       </c>
       <c r="AA17" s="20" t="n">
-        <v>21350</v>
+        <v>19810</v>
       </c>
       <c r="AB17" s="11" t="n"/>
       <c r="AC17" s="10" t="n"/>
@@ -5904,7 +5904,7 @@
         <v>18741.1</v>
       </c>
       <c r="AA18" s="20" t="n">
-        <v>24533.3</v>
+        <v>23964.3</v>
       </c>
       <c r="AB18" s="11" t="n"/>
       <c r="AC18" s="10" t="n"/>
@@ -8169,11 +8169,11 @@
         </is>
       </c>
       <c r="D40" s="34" t="n">
-        <v>21450</v>
+        <v>20900</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 25,150원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 24,300원)</t>
         </is>
       </c>
       <c r="H40" s="9" t="n"/>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="D41" s="35" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -9005,7 +9005,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -15115,7 +15115,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -28258,7 +28258,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -32827,7 +32827,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34734,7 +34734,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="33">
@@ -34768,7 +34768,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>96.48</v>
+        <v>94.89</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/382900_model.xlsx
+++ b/argus/kship/models/382900_model.xlsx
@@ -3934,7 +3934,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -4755,35 +4755,35 @@
         <v>1418.75</v>
       </c>
       <c r="AA6" s="16" t="n">
-        <v>1343.63</v>
+        <v>1343.39</v>
       </c>
       <c r="AB6" s="17" t="n">
-        <v>1456.58</v>
+        <v>1456.01</v>
       </c>
       <c r="AC6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AE6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG6" s="11" t="n"/>
       <c r="AH6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AK6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL6" s="11" t="n"/>
     </row>
@@ -4865,35 +4865,35 @@
         <v>1355.4</v>
       </c>
       <c r="AA7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AB7" s="17" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AC7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AE7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG7" s="11" t="n"/>
       <c r="AH7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AK7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL7" s="11" t="n"/>
     </row>
@@ -4975,35 +4975,35 @@
         <v>890.41</v>
       </c>
       <c r="AA8" s="16" t="n">
-        <v>849.51</v>
+        <v>849.39</v>
       </c>
       <c r="AB8" s="17" t="n">
-        <v>918.8099999999999</v>
+        <v>918.46</v>
       </c>
       <c r="AC8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AE8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG8" s="11" t="n"/>
       <c r="AH8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AK8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL8" s="11" t="n"/>
     </row>
@@ -5085,35 +5085,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AA9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AB9" s="17" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AC9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AE9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG9" s="11" t="n"/>
       <c r="AH9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AK9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL9" s="11" t="n"/>
     </row>
@@ -5195,35 +5195,35 @@
         <v>1631.97</v>
       </c>
       <c r="AA10" s="16" t="n">
-        <v>1507.34</v>
+        <v>1506.62</v>
       </c>
       <c r="AB10" s="17" t="n">
-        <v>1688.95</v>
+        <v>1688.01</v>
       </c>
       <c r="AC10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AE10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG10" s="11" t="n"/>
       <c r="AH10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AK10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL10" s="11" t="n"/>
     </row>
@@ -5305,35 +5305,35 @@
         <v>1539.06</v>
       </c>
       <c r="AA11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AB11" s="17" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AC11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AE11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG11" s="11" t="n"/>
       <c r="AH11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AK11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL11" s="11" t="n"/>
     </row>
@@ -5415,35 +5415,35 @@
         <v>210.43</v>
       </c>
       <c r="AA12" s="16" t="n">
-        <v>200.5</v>
+        <v>200.49</v>
       </c>
       <c r="AB12" s="17" t="n">
-        <v>213.68</v>
+        <v>213.61</v>
       </c>
       <c r="AC12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AE12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG12" s="11" t="n"/>
       <c r="AH12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AK12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL12" s="11" t="n"/>
     </row>
@@ -5525,35 +5525,35 @@
         <v>202.16</v>
       </c>
       <c r="AA13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AB13" s="17" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AC13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AE13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG13" s="11" t="n"/>
       <c r="AH13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AK13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL13" s="11" t="n"/>
     </row>
@@ -5652,7 +5652,7 @@
         <v>25050</v>
       </c>
       <c r="AA15" s="20" t="n">
-        <v>20900</v>
+        <v>21650</v>
       </c>
       <c r="AB15" s="11" t="n"/>
       <c r="AC15" s="10" t="n"/>
@@ -5904,7 +5904,7 @@
         <v>18741.1</v>
       </c>
       <c r="AA18" s="20" t="n">
-        <v>23964.3</v>
+        <v>23693.8</v>
       </c>
       <c r="AB18" s="11" t="n"/>
       <c r="AC18" s="10" t="n"/>
@@ -8169,11 +8169,11 @@
         </is>
       </c>
       <c r="D40" s="34" t="n">
-        <v>20900</v>
+        <v>21650</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 24,300원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 21,600원)</t>
         </is>
       </c>
       <c r="H40" s="9" t="n"/>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="D41" s="35" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -9005,7 +9005,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -15115,7 +15115,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -28258,7 +28258,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -32827,7 +32827,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34734,7 +34734,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="33">
@@ -34768,7 +34768,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>94.89</v>
+        <v>97.06999999999999</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/382900_model.xlsx
+++ b/argus/kship/models/382900_model.xlsx
@@ -3934,7 +3934,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
         </is>
       </c>
     </row>
@@ -4755,35 +4755,35 @@
         <v>1418.75</v>
       </c>
       <c r="AA6" s="16" t="n">
-        <v>1343.39</v>
+        <v>1342.11</v>
       </c>
       <c r="AB6" s="17" t="n">
-        <v>1456.01</v>
+        <v>1454.27</v>
       </c>
       <c r="AC6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AE6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG6" s="11" t="n"/>
       <c r="AH6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AK6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL6" s="11" t="n"/>
     </row>
@@ -4865,35 +4865,35 @@
         <v>1355.4</v>
       </c>
       <c r="AA7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AB7" s="17" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AC7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AE7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG7" s="11" t="n"/>
       <c r="AH7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AK7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL7" s="11" t="n"/>
     </row>
@@ -4975,35 +4975,35 @@
         <v>890.41</v>
       </c>
       <c r="AA8" s="16" t="n">
-        <v>849.39</v>
+        <v>848.59</v>
       </c>
       <c r="AB8" s="17" t="n">
-        <v>918.46</v>
+        <v>917.39</v>
       </c>
       <c r="AC8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AE8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG8" s="11" t="n"/>
       <c r="AH8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AK8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL8" s="11" t="n"/>
     </row>
@@ -5085,35 +5085,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AA9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AB9" s="17" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AC9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AE9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG9" s="11" t="n"/>
       <c r="AH9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AK9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL9" s="11" t="n"/>
     </row>
@@ -5195,35 +5195,35 @@
         <v>1631.97</v>
       </c>
       <c r="AA10" s="16" t="n">
-        <v>1506.62</v>
+        <v>1505.3</v>
       </c>
       <c r="AB10" s="17" t="n">
-        <v>1688.01</v>
+        <v>1685.25</v>
       </c>
       <c r="AC10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AE10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG10" s="11" t="n"/>
       <c r="AH10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AK10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL10" s="11" t="n"/>
     </row>
@@ -5305,35 +5305,35 @@
         <v>1539.06</v>
       </c>
       <c r="AA11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AB11" s="17" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AC11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AE11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG11" s="11" t="n"/>
       <c r="AH11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AK11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL11" s="11" t="n"/>
     </row>
@@ -5415,35 +5415,35 @@
         <v>210.43</v>
       </c>
       <c r="AA12" s="16" t="n">
-        <v>200.49</v>
+        <v>200.38</v>
       </c>
       <c r="AB12" s="17" t="n">
-        <v>213.61</v>
+        <v>213.41</v>
       </c>
       <c r="AC12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AE12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG12" s="11" t="n"/>
       <c r="AH12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AK12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL12" s="11" t="n"/>
     </row>
@@ -5525,35 +5525,35 @@
         <v>202.16</v>
       </c>
       <c r="AA13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AB13" s="17" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AC13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AE13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG13" s="11" t="n"/>
       <c r="AH13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AK13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL13" s="11" t="n"/>
     </row>
@@ -5652,7 +5652,7 @@
         <v>25050</v>
       </c>
       <c r="AA15" s="20" t="n">
-        <v>21650</v>
+        <v>21700</v>
       </c>
       <c r="AB15" s="11" t="n"/>
       <c r="AC15" s="10" t="n"/>
@@ -5820,7 +5820,7 @@
         <v>11810</v>
       </c>
       <c r="AA17" s="20" t="n">
-        <v>19810</v>
+        <v>18800</v>
       </c>
       <c r="AB17" s="11" t="n"/>
       <c r="AC17" s="10" t="n"/>
@@ -5904,7 +5904,7 @@
         <v>18741.1</v>
       </c>
       <c r="AA18" s="20" t="n">
-        <v>23693.8</v>
+        <v>22809.1</v>
       </c>
       <c r="AB18" s="11" t="n"/>
       <c r="AC18" s="10" t="n"/>
@@ -8169,11 +8169,11 @@
         </is>
       </c>
       <c r="D40" s="34" t="n">
-        <v>21650</v>
+        <v>21700</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 21,600원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 19,620원)</t>
         </is>
       </c>
       <c r="H40" s="9" t="n"/>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="D41" s="35" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -9005,7 +9005,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -15115,7 +15115,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -28258,7 +28258,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -32827,7 +32827,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34768,7 +34768,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>97.06999999999999</v>
+        <v>97.20999999999999</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/382900_model.xlsx
+++ b/argus/kship/models/382900_model.xlsx
@@ -3934,7 +3934,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -4755,35 +4755,35 @@
         <v>1418.75</v>
       </c>
       <c r="AA6" s="16" t="n">
-        <v>1342.11</v>
+        <v>1337.49</v>
       </c>
       <c r="AB6" s="17" t="n">
-        <v>1454.27</v>
+        <v>1451.19</v>
       </c>
       <c r="AC6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AE6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG6" s="11" t="n"/>
       <c r="AH6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AK6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL6" s="11" t="n"/>
     </row>
@@ -4865,35 +4865,35 @@
         <v>1355.4</v>
       </c>
       <c r="AA7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AB7" s="17" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AC7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AE7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG7" s="11" t="n"/>
       <c r="AH7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AK7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL7" s="11" t="n"/>
     </row>
@@ -4975,35 +4975,35 @@
         <v>890.41</v>
       </c>
       <c r="AA8" s="16" t="n">
-        <v>848.59</v>
+        <v>846.51</v>
       </c>
       <c r="AB8" s="17" t="n">
-        <v>917.39</v>
+        <v>915.5700000000001</v>
       </c>
       <c r="AC8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AE8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG8" s="11" t="n"/>
       <c r="AH8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AK8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL8" s="11" t="n"/>
     </row>
@@ -5085,35 +5085,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AA9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AB9" s="17" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AC9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AE9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG9" s="11" t="n"/>
       <c r="AH9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AK9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL9" s="11" t="n"/>
     </row>
@@ -5195,35 +5195,35 @@
         <v>1631.97</v>
       </c>
       <c r="AA10" s="16" t="n">
-        <v>1505.3</v>
+        <v>1500.06</v>
       </c>
       <c r="AB10" s="17" t="n">
-        <v>1685.25</v>
+        <v>1680.5</v>
       </c>
       <c r="AC10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AE10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG10" s="11" t="n"/>
       <c r="AH10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AK10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL10" s="11" t="n"/>
     </row>
@@ -5305,35 +5305,35 @@
         <v>1539.06</v>
       </c>
       <c r="AA11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AB11" s="17" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AC11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AE11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG11" s="11" t="n"/>
       <c r="AH11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AK11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL11" s="11" t="n"/>
     </row>
@@ -5415,35 +5415,35 @@
         <v>210.43</v>
       </c>
       <c r="AA12" s="16" t="n">
-        <v>200.38</v>
+        <v>199.88</v>
       </c>
       <c r="AB12" s="17" t="n">
-        <v>213.41</v>
+        <v>213.06</v>
       </c>
       <c r="AC12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AE12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG12" s="11" t="n"/>
       <c r="AH12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AK12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL12" s="11" t="n"/>
     </row>
@@ -5525,35 +5525,35 @@
         <v>202.16</v>
       </c>
       <c r="AA13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AB13" s="17" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AC13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AE13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG13" s="11" t="n"/>
       <c r="AH13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AK13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL13" s="11" t="n"/>
     </row>
@@ -5652,7 +5652,7 @@
         <v>25050</v>
       </c>
       <c r="AA15" s="20" t="n">
-        <v>21700</v>
+        <v>17920</v>
       </c>
       <c r="AB15" s="11" t="n"/>
       <c r="AC15" s="10" t="n"/>
@@ -5820,7 +5820,7 @@
         <v>11810</v>
       </c>
       <c r="AA17" s="20" t="n">
-        <v>18800</v>
+        <v>17910</v>
       </c>
       <c r="AB17" s="11" t="n"/>
       <c r="AC17" s="10" t="n"/>
@@ -5904,7 +5904,7 @@
         <v>18741.1</v>
       </c>
       <c r="AA18" s="20" t="n">
-        <v>22809.1</v>
+        <v>21820</v>
       </c>
       <c r="AB18" s="11" t="n"/>
       <c r="AC18" s="10" t="n"/>
@@ -8169,11 +8169,11 @@
         </is>
       </c>
       <c r="D40" s="34" t="n">
-        <v>21700</v>
+        <v>17920</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 19,620원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 20,200원)</t>
         </is>
       </c>
       <c r="H40" s="9" t="n"/>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="D41" s="35" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -9005,7 +9005,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -15115,7 +15115,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -28258,7 +28258,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -32827,7 +32827,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34734,7 +34734,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.19</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="33">
@@ -34768,7 +34768,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>97.20999999999999</v>
+        <v>86.23</v>
       </c>
     </row>
     <row r="37">
